--- a/Hoàng/SALE/MẪU BÁO GIÁ CẠNH TRANH/BÁO GIÁ CẠNH TRANH 2025.xlsx
+++ b/Hoàng/SALE/MẪU BÁO GIÁ CẠNH TRANH/BÁO GIÁ CẠNH TRANH 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\LÀM VIỆC\DATA_TN\Hoàng\SALE\MẪU BÁO GIÁ CẠNH TRANH\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA-TN\Hoàng\SALE\MẪU BÁO GIÁ CẠNH TRANH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301F338B-873D-4ACE-97B7-B0427FDA6DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3A3C74-26CB-4D60-B2E7-7A58A52A759A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoà Khánh" sheetId="5" r:id="rId1"/>
@@ -601,7 +601,7 @@
         <b/>
         <u/>
         <sz val="15"/>
-        <rFont val="Calibri Light"/>
+        <rFont val="Times New Roman"/>
         <family val="1"/>
         <scheme val="major"/>
       </rPr>
@@ -611,7 +611,7 @@
       <rPr>
         <b/>
         <sz val="15"/>
-        <rFont val="Calibri Light"/>
+        <rFont val="Times New Roman"/>
         <family val="1"/>
         <scheme val="major"/>
       </rPr>
@@ -647,7 +647,7 @@
       <rPr>
         <sz val="14"/>
         <color indexed="8"/>
-        <rFont val="Calibri Light"/>
+        <rFont val="Times New Roman"/>
         <family val="1"/>
         <scheme val="major"/>
       </rPr>
@@ -1127,7 +1127,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -1135,7 +1135,7 @@
     <font>
       <b/>
       <sz val="14"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1143,28 +1143,28 @@
       <b/>
       <sz val="13"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="17"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1172,21 +1172,21 @@
       <b/>
       <u/>
       <sz val="15"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="13"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1204,7 +1204,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1212,7 +1212,7 @@
       <b/>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1233,14 +1233,14 @@
     <font>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1248,7 +1248,7 @@
       <i/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1256,7 +1256,7 @@
       <i/>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1268,7 +1268,7 @@
     <font>
       <b/>
       <sz val="26"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1276,14 +1276,14 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="14"/>
       <color indexed="8"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1291,14 +1291,14 @@
       <b/>
       <sz val="16"/>
       <color rgb="FF000000"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1306,21 +1306,21 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="16"/>
       <color rgb="FF000000"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1328,20 +1328,20 @@
       <b/>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="16"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1349,7 +1349,7 @@
       <b/>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1357,7 +1357,7 @@
       <b/>
       <sz val="20"/>
       <color rgb="FF000000"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1366,7 +1366,7 @@
       <i/>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1374,7 +1374,7 @@
       <b/>
       <sz val="13"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1383,7 +1383,7 @@
       <u/>
       <sz val="13"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1391,21 +1391,21 @@
       <u/>
       <sz val="13"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="13"/>
       <color rgb="FF002060"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF002060"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1413,7 +1413,7 @@
       <b/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri Light"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -2513,56 +2513,197 @@
     <xf numFmtId="0" fontId="77" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="12" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="26" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="2" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="10" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="5" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="4" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="5" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="81" fillId="11" borderId="15" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="8" applyFont="1"/>
+    <xf numFmtId="0" fontId="83" fillId="11" borderId="15" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="18" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="15" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="84" fillId="0" borderId="18" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="12" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="84" fillId="0" borderId="15" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="82" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="84" fillId="0" borderId="15" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="4" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="85" fillId="0" borderId="15" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="4" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="10" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="4" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="13" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="4" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="5" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="18" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="18" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="18" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="15" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="84" fillId="0" borderId="16" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="84" fillId="0" borderId="17" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="84" fillId="0" borderId="18" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="17" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="84" fillId="0" borderId="15" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="19" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="7" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="4" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="19" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="11" borderId="16" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="11" borderId="18" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="11" borderId="22" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="11" borderId="27" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="11" borderId="28" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="11" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="81" fillId="11" borderId="15" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="10" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="13" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="61" fillId="0" borderId="16" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="61" fillId="0" borderId="18" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="67" fillId="0" borderId="16" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="67" fillId="0" borderId="18" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2601,7 +2742,13 @@
     <xf numFmtId="0" fontId="65" fillId="4" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="61" fillId="0" borderId="16" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="61" fillId="0" borderId="17" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="61" fillId="0" borderId="18" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="65" fillId="0" borderId="16" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2619,116 +2766,241 @@
     <xf numFmtId="0" fontId="66" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="67" fillId="0" borderId="16" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="67" fillId="0" borderId="18" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="12" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="12" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="4" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="4" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="4" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="13" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="13" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="10" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="27" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="32" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="32" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="32" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="32" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2743,104 +3015,47 @@
     <xf numFmtId="0" fontId="31" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="32" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="32" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="32" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="31" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="31" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="31" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="27" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2851,15 +3066,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2934,212 +3140,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="19" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="26" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="2" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="10" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="7" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="4" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="5" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="19" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="4" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="5" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="11" borderId="16" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="11" borderId="22" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="11" borderId="27" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="81" fillId="11" borderId="15" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="8" applyFont="1"/>
-    <xf numFmtId="0" fontId="81" fillId="11" borderId="18" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="11" borderId="28" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="11" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="81" fillId="11" borderId="15" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="11" borderId="15" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="18" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="18" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="4" borderId="18" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="84" fillId="0" borderId="16" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="4" borderId="15" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="84" fillId="0" borderId="17" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="84" fillId="0" borderId="18" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="4" borderId="15" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="84" fillId="0" borderId="18" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="84" fillId="0" borderId="15" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="82" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="17" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="84" fillId="0" borderId="15" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="84" fillId="0" borderId="15" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="18" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="85" fillId="0" borderId="15" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="10" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="4" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="5" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -3801,353 +3801,360 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF4B47C1-996F-4F19-A70A-25FB3DB67440}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="6" style="390" customWidth="1"/>
-    <col min="2" max="2" width="18" style="390" customWidth="1"/>
-    <col min="3" max="3" width="44.625" style="390" customWidth="1"/>
-    <col min="4" max="4" width="10.875" style="390" customWidth="1"/>
-    <col min="5" max="5" width="9.125" style="390" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8" style="390"/>
+    <col min="1" max="1" width="6" style="229" customWidth="1"/>
+    <col min="2" max="2" width="18" style="229" customWidth="1"/>
+    <col min="3" max="3" width="44.58203125" style="229" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" style="229" customWidth="1"/>
+    <col min="5" max="5" width="9.08203125" style="229" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8" style="229"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="371" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A1" s="368" t="s">
+    <row r="1" spans="1:6" s="218" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A1" s="262" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="369"/>
-      <c r="C1" s="369"/>
-      <c r="D1" s="369"/>
-      <c r="E1" s="369"/>
-      <c r="F1" s="370"/>
-    </row>
-    <row r="2" spans="1:6" s="372" customFormat="1" ht="16.5">
-      <c r="A2" s="368"/>
-      <c r="B2" s="369"/>
-      <c r="C2" s="369"/>
-      <c r="D2" s="369"/>
-      <c r="E2" s="369"/>
-      <c r="F2" s="370"/>
-    </row>
-    <row r="3" spans="1:6" s="372" customFormat="1" ht="16.5">
-      <c r="A3" s="368"/>
-      <c r="B3" s="369"/>
-      <c r="C3" s="369"/>
-      <c r="D3" s="369"/>
-      <c r="E3" s="369"/>
-      <c r="F3" s="370"/>
-    </row>
-    <row r="4" spans="1:6" s="372" customFormat="1" ht="16.5">
-      <c r="A4" s="368"/>
-      <c r="B4" s="369"/>
-      <c r="C4" s="369"/>
-      <c r="D4" s="369"/>
-      <c r="E4" s="369"/>
-      <c r="F4" s="370"/>
-    </row>
-    <row r="5" spans="1:6" s="372" customFormat="1" ht="16.5">
-      <c r="A5" s="373"/>
-      <c r="B5" s="374"/>
-      <c r="C5" s="374"/>
-      <c r="D5" s="374"/>
-      <c r="E5" s="374"/>
-      <c r="F5" s="375"/>
-    </row>
-    <row r="6" spans="1:6" s="372" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A6" s="376" t="s">
+      <c r="B1" s="263"/>
+      <c r="C1" s="263"/>
+      <c r="D1" s="263"/>
+      <c r="E1" s="263"/>
+      <c r="F1" s="217"/>
+    </row>
+    <row r="2" spans="1:6" s="219" customFormat="1" ht="16">
+      <c r="A2" s="262"/>
+      <c r="B2" s="263"/>
+      <c r="C2" s="263"/>
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="217"/>
+    </row>
+    <row r="3" spans="1:6" s="219" customFormat="1" ht="16">
+      <c r="A3" s="262"/>
+      <c r="B3" s="263"/>
+      <c r="C3" s="263"/>
+      <c r="D3" s="263"/>
+      <c r="E3" s="263"/>
+      <c r="F3" s="217"/>
+    </row>
+    <row r="4" spans="1:6" s="219" customFormat="1" ht="16">
+      <c r="A4" s="262"/>
+      <c r="B4" s="263"/>
+      <c r="C4" s="263"/>
+      <c r="D4" s="263"/>
+      <c r="E4" s="263"/>
+      <c r="F4" s="217"/>
+    </row>
+    <row r="5" spans="1:6" s="219" customFormat="1" ht="16">
+      <c r="A5" s="220"/>
+      <c r="B5" s="221"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="221"/>
+      <c r="E5" s="221"/>
+      <c r="F5" s="222"/>
+    </row>
+    <row r="6" spans="1:6" s="219" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A6" s="264" t="s">
         <v>204</v>
       </c>
-      <c r="B6" s="377"/>
-      <c r="C6" s="377"/>
-      <c r="D6" s="378"/>
-      <c r="E6" s="378"/>
-      <c r="F6" s="379"/>
-    </row>
-    <row r="7" spans="1:6" s="372" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A7" s="380" t="s">
+      <c r="B6" s="265"/>
+      <c r="C6" s="265"/>
+      <c r="D6" s="266"/>
+      <c r="E6" s="266"/>
+      <c r="F6" s="223"/>
+    </row>
+    <row r="7" spans="1:6" s="219" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A7" s="267" t="s">
         <v>205</v>
       </c>
-      <c r="B7" s="381"/>
-      <c r="C7" s="381"/>
-      <c r="D7" s="382"/>
-      <c r="E7" s="382"/>
-      <c r="F7" s="383"/>
-    </row>
-    <row r="8" spans="1:6" s="385" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A8" s="381" t="s">
+      <c r="B7" s="268"/>
+      <c r="C7" s="268"/>
+      <c r="D7" s="224"/>
+      <c r="E7" s="224"/>
+      <c r="F7" s="225"/>
+    </row>
+    <row r="8" spans="1:6" s="227" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A8" s="268" t="s">
         <v>206</v>
       </c>
-      <c r="B8" s="381"/>
-      <c r="C8" s="381"/>
-      <c r="D8" s="384"/>
-      <c r="E8" s="384"/>
-      <c r="F8" s="384"/>
+      <c r="B8" s="268"/>
+      <c r="C8" s="268"/>
+      <c r="D8" s="226"/>
+      <c r="E8" s="226"/>
+      <c r="F8" s="226"/>
     </row>
     <row r="9" spans="1:6" ht="15">
-      <c r="A9" s="386" t="s">
+      <c r="A9" s="269" t="s">
         <v>207</v>
       </c>
-      <c r="B9" s="387" t="s">
+      <c r="B9" s="271" t="s">
         <v>161</v>
       </c>
-      <c r="C9" s="388"/>
-      <c r="D9" s="389" t="s">
+      <c r="C9" s="272"/>
+      <c r="D9" s="275" t="s">
         <v>208</v>
       </c>
-      <c r="E9" s="389"/>
+      <c r="E9" s="275"/>
     </row>
     <row r="10" spans="1:6" ht="15">
-      <c r="A10" s="391"/>
-      <c r="B10" s="392"/>
-      <c r="C10" s="393"/>
-      <c r="D10" s="394" t="s">
+      <c r="A10" s="270"/>
+      <c r="B10" s="273"/>
+      <c r="C10" s="274"/>
+      <c r="D10" s="228" t="s">
         <v>209</v>
       </c>
-      <c r="E10" s="395" t="s">
+      <c r="E10" s="230" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A11" s="396">
+      <c r="A11" s="250">
         <v>1</v>
       </c>
-      <c r="B11" s="397" t="s">
+      <c r="B11" s="252" t="s">
         <v>165</v>
       </c>
-      <c r="C11" s="398" t="s">
+      <c r="C11" s="254" t="s">
         <v>211</v>
       </c>
-      <c r="D11" s="399">
+      <c r="D11" s="256">
         <v>250000</v>
       </c>
-      <c r="E11" s="399">
+      <c r="E11" s="256">
         <f>D11</f>
         <v>250000</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A12" s="400"/>
-      <c r="B12" s="401"/>
-      <c r="C12" s="402"/>
-      <c r="D12" s="403"/>
-      <c r="E12" s="403"/>
+      <c r="A12" s="251"/>
+      <c r="B12" s="253"/>
+      <c r="C12" s="255"/>
+      <c r="D12" s="257"/>
+      <c r="E12" s="257"/>
     </row>
     <row r="13" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A13" s="400"/>
-      <c r="B13" s="401"/>
-      <c r="C13" s="402"/>
-      <c r="D13" s="403"/>
-      <c r="E13" s="403"/>
+      <c r="A13" s="251"/>
+      <c r="B13" s="253"/>
+      <c r="C13" s="255"/>
+      <c r="D13" s="257"/>
+      <c r="E13" s="257"/>
     </row>
     <row r="14" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A14" s="400"/>
-      <c r="B14" s="401"/>
-      <c r="C14" s="402"/>
-      <c r="D14" s="403"/>
-      <c r="E14" s="403"/>
+      <c r="A14" s="251"/>
+      <c r="B14" s="253"/>
+      <c r="C14" s="255"/>
+      <c r="D14" s="257"/>
+      <c r="E14" s="257"/>
     </row>
     <row r="15" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A15" s="400"/>
-      <c r="B15" s="401"/>
-      <c r="C15" s="402"/>
-      <c r="D15" s="404"/>
-      <c r="E15" s="404"/>
+      <c r="A15" s="251"/>
+      <c r="B15" s="253"/>
+      <c r="C15" s="255"/>
+      <c r="D15" s="258"/>
+      <c r="E15" s="258"/>
     </row>
     <row r="16" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A16" s="405">
+      <c r="A16" s="232">
         <v>2</v>
       </c>
-      <c r="B16" s="406" t="s">
+      <c r="B16" s="233" t="s">
         <v>212</v>
       </c>
-      <c r="C16" s="407" t="s">
+      <c r="C16" s="234" t="s">
         <v>213</v>
       </c>
-      <c r="D16" s="408">
+      <c r="D16" s="235">
         <v>120000</v>
       </c>
-      <c r="E16" s="408">
+      <c r="E16" s="235">
         <v>120000</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15">
-      <c r="A17" s="409">
+      <c r="A17" s="236">
         <v>2</v>
       </c>
-      <c r="B17" s="406" t="s">
+      <c r="B17" s="233" t="s">
         <v>214</v>
       </c>
-      <c r="C17" s="410" t="s">
+      <c r="C17" s="237" t="s">
         <v>215</v>
       </c>
-      <c r="D17" s="411">
+      <c r="D17" s="238">
         <v>100000</v>
       </c>
-      <c r="E17" s="411">
+      <c r="E17" s="238">
         <f>D17</f>
         <v>100000</v>
       </c>
-      <c r="F17" s="412"/>
+      <c r="F17" s="239"/>
     </row>
     <row r="18" spans="1:6" ht="15">
-      <c r="A18" s="409">
+      <c r="A18" s="236">
         <v>3</v>
       </c>
-      <c r="B18" s="406" t="s">
+      <c r="B18" s="233" t="s">
         <v>169</v>
       </c>
-      <c r="C18" s="410" t="s">
+      <c r="C18" s="237" t="s">
         <v>216</v>
       </c>
-      <c r="D18" s="411">
+      <c r="D18" s="238">
         <v>50000</v>
       </c>
-      <c r="E18" s="411">
+      <c r="E18" s="238">
         <f t="shared" ref="E18:E20" si="0">D18</f>
         <v>50000</v>
       </c>
-      <c r="F18" s="412"/>
+      <c r="F18" s="239"/>
     </row>
     <row r="19" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A19" s="413">
+      <c r="A19" s="259">
         <v>4</v>
       </c>
-      <c r="B19" s="406" t="s">
+      <c r="B19" s="233" t="s">
         <v>171</v>
       </c>
-      <c r="C19" s="410" t="s">
+      <c r="C19" s="237" t="s">
         <v>172</v>
       </c>
-      <c r="D19" s="411">
+      <c r="D19" s="238">
         <v>75000</v>
       </c>
-      <c r="E19" s="411">
+      <c r="E19" s="238">
         <f t="shared" si="0"/>
         <v>75000</v>
       </c>
-      <c r="F19" s="412"/>
+      <c r="F19" s="239"/>
     </row>
     <row r="20" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A20" s="414">
+      <c r="A20" s="260">
         <v>3.2580645161290298</v>
       </c>
-      <c r="B20" s="406" t="s">
+      <c r="B20" s="233" t="s">
         <v>173</v>
       </c>
-      <c r="C20" s="415" t="s">
+      <c r="C20" s="240" t="s">
         <v>217</v>
       </c>
-      <c r="D20" s="411">
+      <c r="D20" s="238">
         <v>25000</v>
       </c>
-      <c r="E20" s="411">
+      <c r="E20" s="238">
         <f t="shared" si="0"/>
         <v>25000</v>
       </c>
-      <c r="F20" s="412"/>
+      <c r="F20" s="239"/>
     </row>
     <row r="21" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A21" s="414">
+      <c r="A21" s="260">
         <v>3.54838709677419</v>
       </c>
-      <c r="B21" s="401" t="s">
+      <c r="B21" s="253" t="s">
         <v>175</v>
       </c>
-      <c r="C21" s="410" t="s">
+      <c r="C21" s="237" t="s">
         <v>218</v>
       </c>
-      <c r="D21" s="416">
+      <c r="D21" s="261">
         <v>60000</v>
       </c>
-      <c r="E21" s="416">
+      <c r="E21" s="261">
         <f>D21</f>
         <v>60000</v>
       </c>
-      <c r="F21" s="412"/>
+      <c r="F21" s="239"/>
     </row>
     <row r="22" spans="1:6" ht="15">
-      <c r="A22" s="414">
+      <c r="A22" s="260">
         <v>3.8387096774193501</v>
       </c>
-      <c r="B22" s="401"/>
-      <c r="C22" s="410" t="s">
+      <c r="B22" s="253"/>
+      <c r="C22" s="237" t="s">
         <v>177</v>
       </c>
-      <c r="D22" s="416"/>
-      <c r="E22" s="416"/>
-      <c r="F22" s="412"/>
+      <c r="D22" s="261"/>
+      <c r="E22" s="261"/>
+      <c r="F22" s="239"/>
     </row>
     <row r="23" spans="1:6" ht="30">
-      <c r="A23" s="396">
+      <c r="A23" s="250">
         <v>4.1290322580645098</v>
       </c>
-      <c r="B23" s="406" t="s">
+      <c r="B23" s="233" t="s">
         <v>178</v>
       </c>
-      <c r="C23" s="410" t="s">
+      <c r="C23" s="237" t="s">
         <v>219</v>
       </c>
-      <c r="D23" s="417">
+      <c r="D23" s="241">
         <v>40000</v>
       </c>
-      <c r="E23" s="417">
+      <c r="E23" s="241">
         <f>D23</f>
         <v>40000</v>
       </c>
-      <c r="F23" s="412"/>
+      <c r="F23" s="239"/>
     </row>
     <row r="24" spans="1:6" ht="15">
-      <c r="A24" s="418">
+      <c r="A24" s="231">
         <v>5</v>
       </c>
-      <c r="B24" s="406" t="s">
+      <c r="B24" s="233" t="s">
         <v>220</v>
       </c>
-      <c r="C24" s="410" t="s">
+      <c r="C24" s="237" t="s">
         <v>221</v>
       </c>
-      <c r="E24" s="417">
+      <c r="E24" s="241">
         <v>120000</v>
       </c>
-      <c r="F24" s="412"/>
+      <c r="F24" s="239"/>
     </row>
     <row r="25" spans="1:6" ht="15">
-      <c r="A25" s="419" t="s">
+      <c r="A25" s="243" t="s">
         <v>201</v>
       </c>
-      <c r="B25" s="419"/>
-      <c r="C25" s="419"/>
-      <c r="D25" s="420">
+      <c r="B25" s="243"/>
+      <c r="C25" s="243"/>
+      <c r="D25" s="242">
         <f>SUM(D11:D24)</f>
         <v>720000</v>
       </c>
-      <c r="E25" s="420">
+      <c r="E25" s="242">
         <f>SUM(E11:E24)</f>
         <v>840000</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16.5">
-      <c r="A27" s="421" t="s">
+    <row r="27" spans="1:6" ht="16">
+      <c r="A27" s="244" t="s">
         <v>222</v>
       </c>
-      <c r="B27" s="422"/>
-      <c r="C27" s="422"/>
-      <c r="D27" s="422"/>
-      <c r="E27" s="422"/>
-      <c r="F27" s="423"/>
-    </row>
-    <row r="28" spans="1:6" ht="16.5">
-      <c r="A28" s="424" t="s">
+      <c r="B27" s="245"/>
+      <c r="C27" s="245"/>
+      <c r="D27" s="245"/>
+      <c r="E27" s="245"/>
+      <c r="F27" s="246"/>
+    </row>
+    <row r="28" spans="1:6" ht="16">
+      <c r="A28" s="247" t="s">
         <v>223</v>
       </c>
-      <c r="B28" s="425"/>
-      <c r="C28" s="425"/>
-      <c r="D28" s="425"/>
-      <c r="E28" s="425"/>
-      <c r="F28" s="426"/>
+      <c r="B28" s="248"/>
+      <c r="C28" s="248"/>
+      <c r="D28" s="248"/>
+      <c r="E28" s="248"/>
+      <c r="F28" s="249"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:E4"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:C10"/>
+    <mergeCell ref="D9:E9"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A28:F28"/>
@@ -4160,13 +4167,6 @@
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="D21:D22"/>
     <mergeCell ref="E21:E22"/>
-    <mergeCell ref="A1:E4"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:C10"/>
-    <mergeCell ref="D9:E9"/>
   </mergeCells>
   <pageMargins left="0.37" right="0.28999999999999998" top="0.28999999999999998" bottom="0.12" header="0.3" footer="0.15"/>
   <pageSetup scale="89" orientation="portrait" r:id="rId1"/>
@@ -4177,63 +4177,63 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12780C8E-2D48-477A-B557-84E3E8932DCA}">
   <dimension ref="A1:H236"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="7.375" style="142" customWidth="1"/>
-    <col min="2" max="2" width="58.625" style="213" customWidth="1"/>
-    <col min="3" max="3" width="96.125" style="142" customWidth="1"/>
-    <col min="4" max="4" width="13.875" style="214" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.875" style="215" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" style="142" customWidth="1"/>
+    <col min="2" max="2" width="58.58203125" style="213" customWidth="1"/>
+    <col min="3" max="3" width="96.08203125" style="142" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" style="214" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" style="215" customWidth="1"/>
     <col min="6" max="6" width="17.5" style="215" customWidth="1"/>
-    <col min="7" max="7" width="9.875" style="216" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" style="216" customWidth="1"/>
     <col min="8" max="8" width="17.25" style="142" customWidth="1"/>
-    <col min="9" max="9" width="8.625" style="142" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.58203125" style="142" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="8" style="142"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="135" customFormat="1" ht="35.25" customHeight="1">
       <c r="A1" s="133"/>
       <c r="B1" s="134"/>
-      <c r="C1" s="252" t="s">
+      <c r="C1" s="277" t="s">
         <v>152</v>
       </c>
-      <c r="D1" s="252"/>
-      <c r="E1" s="252"/>
-      <c r="F1" s="252"/>
-      <c r="G1" s="252"/>
-    </row>
-    <row r="2" spans="1:8" s="135" customFormat="1" ht="19.5">
+      <c r="D1" s="277"/>
+      <c r="E1" s="277"/>
+      <c r="F1" s="277"/>
+      <c r="G1" s="277"/>
+    </row>
+    <row r="2" spans="1:8" s="135" customFormat="1" ht="19">
       <c r="A2" s="133"/>
       <c r="B2" s="134"/>
-      <c r="C2" s="253" t="s">
+      <c r="C2" s="278" t="s">
         <v>153</v>
       </c>
-      <c r="D2" s="253"/>
-      <c r="E2" s="253"/>
-      <c r="F2" s="253"/>
-      <c r="G2" s="253"/>
-    </row>
-    <row r="3" spans="1:8" s="135" customFormat="1" ht="19.5">
+      <c r="D2" s="278"/>
+      <c r="E2" s="278"/>
+      <c r="F2" s="278"/>
+      <c r="G2" s="278"/>
+    </row>
+    <row r="3" spans="1:8" s="135" customFormat="1" ht="19">
       <c r="A3" s="133"/>
       <c r="B3" s="134"/>
-      <c r="C3" s="253" t="s">
+      <c r="C3" s="278" t="s">
         <v>154</v>
       </c>
-      <c r="D3" s="253"/>
-      <c r="E3" s="253"/>
-      <c r="F3" s="253"/>
-      <c r="G3" s="253"/>
+      <c r="D3" s="278"/>
+      <c r="E3" s="278"/>
+      <c r="F3" s="278"/>
+      <c r="G3" s="278"/>
     </row>
     <row r="4" spans="1:8" s="135" customFormat="1" ht="39.75" customHeight="1">
       <c r="A4" s="133"/>
       <c r="B4" s="134"/>
-      <c r="C4" s="254" t="s">
+      <c r="C4" s="279" t="s">
         <v>155</v>
       </c>
-      <c r="D4" s="255"/>
-      <c r="E4" s="255"/>
-      <c r="F4" s="255"/>
-      <c r="G4" s="255"/>
+      <c r="D4" s="280"/>
+      <c r="E4" s="280"/>
+      <c r="F4" s="280"/>
+      <c r="G4" s="280"/>
     </row>
     <row r="5" spans="1:8" s="135" customFormat="1">
       <c r="A5" s="136"/>
@@ -4247,58 +4247,58 @@
       <c r="C6" s="136"/>
       <c r="D6" s="136"/>
     </row>
-    <row r="7" spans="1:8" s="135" customFormat="1" ht="19.5">
+    <row r="7" spans="1:8" s="135" customFormat="1" ht="19">
       <c r="A7" s="136"/>
       <c r="B7" s="137"/>
       <c r="C7" s="136"/>
-      <c r="D7" s="256" t="s">
+      <c r="D7" s="281" t="s">
         <v>156</v>
       </c>
-      <c r="E7" s="256"/>
-      <c r="F7" s="256"/>
-      <c r="G7" s="256"/>
+      <c r="E7" s="281"/>
+      <c r="F7" s="281"/>
+      <c r="G7" s="281"/>
     </row>
     <row r="8" spans="1:8" s="135" customFormat="1" ht="35.25" customHeight="1">
-      <c r="A8" s="257" t="s">
+      <c r="A8" s="276" t="s">
         <v>157</v>
       </c>
-      <c r="B8" s="257"/>
-      <c r="C8" s="257"/>
-      <c r="D8" s="257"/>
-      <c r="E8" s="257"/>
-      <c r="F8" s="257"/>
-      <c r="G8" s="257"/>
+      <c r="B8" s="276"/>
+      <c r="C8" s="276"/>
+      <c r="D8" s="276"/>
+      <c r="E8" s="276"/>
+      <c r="F8" s="276"/>
+      <c r="G8" s="276"/>
     </row>
     <row r="9" spans="1:8" s="135" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A9" s="237" t="s">
+      <c r="A9" s="285" t="s">
         <v>158</v>
       </c>
-      <c r="B9" s="237"/>
-      <c r="C9" s="237"/>
-      <c r="D9" s="237"/>
-      <c r="E9" s="237"/>
-      <c r="F9" s="237"/>
-      <c r="G9" s="237"/>
+      <c r="B9" s="285"/>
+      <c r="C9" s="285"/>
+      <c r="D9" s="285"/>
+      <c r="E9" s="285"/>
+      <c r="F9" s="285"/>
+      <c r="G9" s="285"/>
     </row>
     <row r="10" spans="1:8" s="135" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A10" s="238" t="s">
+      <c r="A10" s="286" t="s">
         <v>159</v>
       </c>
-      <c r="B10" s="238"/>
-      <c r="C10" s="238"/>
-      <c r="D10" s="238"/>
-      <c r="E10" s="238"/>
-      <c r="F10" s="238"/>
-      <c r="G10" s="238"/>
+      <c r="B10" s="286"/>
+      <c r="C10" s="286"/>
+      <c r="D10" s="286"/>
+      <c r="E10" s="286"/>
+      <c r="F10" s="286"/>
+      <c r="G10" s="286"/>
     </row>
     <row r="11" spans="1:8" ht="67.5" customHeight="1">
       <c r="A11" s="138" t="s">
         <v>160</v>
       </c>
-      <c r="B11" s="239" t="s">
+      <c r="B11" s="287" t="s">
         <v>161</v>
       </c>
-      <c r="C11" s="239"/>
+      <c r="C11" s="287"/>
       <c r="D11" s="139" t="s">
         <v>162</v>
       </c>
@@ -4314,79 +4314,79 @@
       <c r="H11" s="141"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="240">
+      <c r="A12" s="288">
         <v>1</v>
       </c>
-      <c r="B12" s="242" t="s">
+      <c r="B12" s="290" t="s">
         <v>165</v>
       </c>
-      <c r="C12" s="244" t="s">
+      <c r="C12" s="292" t="s">
         <v>166</v>
       </c>
-      <c r="D12" s="228">
+      <c r="D12" s="294">
         <v>130000</v>
       </c>
-      <c r="E12" s="247">
+      <c r="E12" s="297">
         <v>380</v>
       </c>
-      <c r="F12" s="247">
+      <c r="F12" s="297">
         <f>D12*E12</f>
         <v>49400000</v>
       </c>
-      <c r="G12" s="250"/>
+      <c r="G12" s="300"/>
       <c r="H12" s="145"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="241"/>
-      <c r="B13" s="243"/>
-      <c r="C13" s="245"/>
-      <c r="D13" s="246"/>
-      <c r="E13" s="248"/>
-      <c r="F13" s="248"/>
-      <c r="G13" s="251"/>
+      <c r="A13" s="289"/>
+      <c r="B13" s="291"/>
+      <c r="C13" s="293"/>
+      <c r="D13" s="295"/>
+      <c r="E13" s="298"/>
+      <c r="F13" s="298"/>
+      <c r="G13" s="301"/>
       <c r="H13" s="145"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="241"/>
-      <c r="B14" s="243"/>
-      <c r="C14" s="245"/>
-      <c r="D14" s="246"/>
-      <c r="E14" s="248"/>
-      <c r="F14" s="248"/>
-      <c r="G14" s="251"/>
+      <c r="A14" s="289"/>
+      <c r="B14" s="291"/>
+      <c r="C14" s="293"/>
+      <c r="D14" s="295"/>
+      <c r="E14" s="298"/>
+      <c r="F14" s="298"/>
+      <c r="G14" s="301"/>
       <c r="H14" s="145"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="241"/>
-      <c r="B15" s="243"/>
-      <c r="C15" s="245"/>
-      <c r="D15" s="246"/>
-      <c r="E15" s="248"/>
-      <c r="F15" s="248"/>
-      <c r="G15" s="251"/>
+      <c r="A15" s="289"/>
+      <c r="B15" s="291"/>
+      <c r="C15" s="293"/>
+      <c r="D15" s="295"/>
+      <c r="E15" s="298"/>
+      <c r="F15" s="298"/>
+      <c r="G15" s="301"/>
       <c r="H15" s="145"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="241"/>
-      <c r="B16" s="243"/>
-      <c r="C16" s="245"/>
-      <c r="D16" s="246"/>
-      <c r="E16" s="248"/>
-      <c r="F16" s="248"/>
-      <c r="G16" s="251"/>
+      <c r="A16" s="289"/>
+      <c r="B16" s="291"/>
+      <c r="C16" s="293"/>
+      <c r="D16" s="295"/>
+      <c r="E16" s="298"/>
+      <c r="F16" s="298"/>
+      <c r="G16" s="301"/>
       <c r="H16" s="146"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="241"/>
-      <c r="B17" s="243"/>
-      <c r="C17" s="245"/>
-      <c r="D17" s="229"/>
-      <c r="E17" s="249"/>
-      <c r="F17" s="249"/>
-      <c r="G17" s="251"/>
+      <c r="A17" s="289"/>
+      <c r="B17" s="291"/>
+      <c r="C17" s="293"/>
+      <c r="D17" s="296"/>
+      <c r="E17" s="299"/>
+      <c r="F17" s="299"/>
+      <c r="G17" s="301"/>
       <c r="H17" s="146"/>
     </row>
-    <row r="18" spans="1:8" ht="21">
+    <row r="18" spans="1:8" ht="20.5">
       <c r="A18" s="147">
         <v>2</v>
       </c>
@@ -4409,7 +4409,7 @@
       <c r="G18" s="151"/>
       <c r="H18" s="146"/>
     </row>
-    <row r="19" spans="1:8" ht="21">
+    <row r="19" spans="1:8" ht="20.5">
       <c r="A19" s="147">
         <v>3</v>
       </c>
@@ -4432,7 +4432,7 @@
       <c r="G19" s="151"/>
       <c r="H19" s="146"/>
     </row>
-    <row r="20" spans="1:8" ht="21">
+    <row r="20" spans="1:8" ht="20.5">
       <c r="A20" s="147">
         <v>4</v>
       </c>
@@ -4455,7 +4455,7 @@
       <c r="G20" s="151"/>
       <c r="H20" s="146"/>
     </row>
-    <row r="21" spans="1:8" ht="21">
+    <row r="21" spans="1:8" ht="20.5">
       <c r="A21" s="147">
         <v>5</v>
       </c>
@@ -4478,44 +4478,44 @@
       <c r="G21" s="151"/>
       <c r="H21" s="146"/>
     </row>
-    <row r="22" spans="1:8" ht="21">
+    <row r="22" spans="1:8" ht="20.5">
       <c r="A22" s="147">
         <v>6</v>
       </c>
-      <c r="B22" s="227" t="s">
+      <c r="B22" s="302" t="s">
         <v>175</v>
       </c>
       <c r="C22" s="149" t="s">
         <v>176</v>
       </c>
-      <c r="D22" s="228">
+      <c r="D22" s="294">
         <v>50000</v>
       </c>
-      <c r="E22" s="230">
+      <c r="E22" s="303">
         <v>380</v>
       </c>
-      <c r="F22" s="230">
+      <c r="F22" s="303">
         <f>E22*D22</f>
         <v>19000000</v>
       </c>
-      <c r="G22" s="232"/>
+      <c r="G22" s="305"/>
       <c r="H22" s="146"/>
     </row>
-    <row r="23" spans="1:8" ht="21">
+    <row r="23" spans="1:8" ht="20.5">
       <c r="A23" s="147">
         <v>7</v>
       </c>
-      <c r="B23" s="227"/>
+      <c r="B23" s="302"/>
       <c r="C23" s="149" t="s">
         <v>177</v>
       </c>
-      <c r="D23" s="229"/>
-      <c r="E23" s="231"/>
-      <c r="F23" s="231"/>
-      <c r="G23" s="233"/>
+      <c r="D23" s="296"/>
+      <c r="E23" s="304"/>
+      <c r="F23" s="304"/>
+      <c r="G23" s="306"/>
       <c r="H23" s="146"/>
     </row>
-    <row r="24" spans="1:8" ht="21">
+    <row r="24" spans="1:8" ht="20.5">
       <c r="A24" s="147">
         <v>8</v>
       </c>
@@ -4538,7 +4538,7 @@
       <c r="G24" s="151"/>
       <c r="H24" s="146"/>
     </row>
-    <row r="25" spans="1:8" ht="21">
+    <row r="25" spans="1:8" ht="20.5">
       <c r="A25" s="147">
         <v>9</v>
       </c>
@@ -4561,7 +4561,7 @@
       <c r="G25" s="151"/>
       <c r="H25" s="146"/>
     </row>
-    <row r="26" spans="1:8" ht="21">
+    <row r="26" spans="1:8" ht="20.5">
       <c r="A26" s="147">
         <v>10</v>
       </c>
@@ -4584,7 +4584,7 @@
       <c r="G26" s="151"/>
       <c r="H26" s="146"/>
     </row>
-    <row r="27" spans="1:8" ht="21">
+    <row r="27" spans="1:8" ht="20.5">
       <c r="A27" s="147">
         <v>11</v>
       </c>
@@ -4607,11 +4607,11 @@
       <c r="G27" s="153"/>
       <c r="H27" s="146"/>
     </row>
-    <row r="28" spans="1:8" ht="21">
+    <row r="28" spans="1:8" ht="20.5">
       <c r="A28" s="147">
         <v>12</v>
       </c>
-      <c r="B28" s="234" t="s">
+      <c r="B28" s="282" t="s">
         <v>185</v>
       </c>
       <c r="C28" s="149" t="s">
@@ -4627,14 +4627,14 @@
         <f t="shared" si="1"/>
         <v>14440000</v>
       </c>
-      <c r="G28" s="235"/>
+      <c r="G28" s="283"/>
       <c r="H28" s="146"/>
     </row>
-    <row r="29" spans="1:8" ht="21">
+    <row r="29" spans="1:8" ht="20.5">
       <c r="A29" s="147">
         <v>13</v>
       </c>
-      <c r="B29" s="234"/>
+      <c r="B29" s="282"/>
       <c r="C29" s="149" t="s">
         <v>186</v>
       </c>
@@ -4648,10 +4648,10 @@
         <f t="shared" si="1"/>
         <v>14440000</v>
       </c>
-      <c r="G29" s="236"/>
+      <c r="G29" s="284"/>
       <c r="H29" s="146"/>
     </row>
-    <row r="30" spans="1:8" ht="21">
+    <row r="30" spans="1:8" ht="20.5">
       <c r="A30" s="147">
         <v>14</v>
       </c>
@@ -4674,7 +4674,7 @@
       <c r="G30" s="156"/>
       <c r="H30" s="157"/>
     </row>
-    <row r="31" spans="1:8" ht="21">
+    <row r="31" spans="1:8" ht="20.5">
       <c r="A31" s="147">
         <v>15</v>
       </c>
@@ -4695,7 +4695,7 @@
       <c r="G31" s="156"/>
       <c r="H31" s="157"/>
     </row>
-    <row r="32" spans="1:8" ht="21">
+    <row r="32" spans="1:8" ht="20.5">
       <c r="A32" s="147">
         <v>16</v>
       </c>
@@ -4716,7 +4716,7 @@
       <c r="G32" s="151"/>
       <c r="H32" s="146"/>
     </row>
-    <row r="33" spans="1:8" ht="21">
+    <row r="33" spans="1:8" ht="20.5">
       <c r="A33" s="147">
         <v>17</v>
       </c>
@@ -4737,7 +4737,7 @@
       <c r="G33" s="151"/>
       <c r="H33" s="146"/>
     </row>
-    <row r="34" spans="1:8" ht="21">
+    <row r="34" spans="1:8" ht="20.5">
       <c r="A34" s="147">
         <v>18</v>
       </c>
@@ -4758,12 +4758,12 @@
       <c r="G34" s="151"/>
       <c r="H34" s="146"/>
     </row>
-    <row r="35" spans="1:8" s="165" customFormat="1" ht="21">
-      <c r="A35" s="217" t="s">
+    <row r="35" spans="1:8" s="165" customFormat="1" ht="20">
+      <c r="A35" s="307" t="s">
         <v>192</v>
       </c>
-      <c r="B35" s="218"/>
-      <c r="C35" s="218"/>
+      <c r="B35" s="308"/>
+      <c r="C35" s="308"/>
       <c r="D35" s="162">
         <f>SUM(D12:D34)</f>
         <v>1080000</v>
@@ -4776,19 +4776,19 @@
       <c r="G35" s="163"/>
       <c r="H35" s="164"/>
     </row>
-    <row r="36" spans="1:8" s="167" customFormat="1" ht="26.25">
-      <c r="A36" s="219" t="s">
+    <row r="36" spans="1:8" s="167" customFormat="1" ht="25">
+      <c r="A36" s="309" t="s">
         <v>193</v>
       </c>
-      <c r="B36" s="220"/>
-      <c r="C36" s="220"/>
-      <c r="D36" s="220"/>
-      <c r="E36" s="220"/>
-      <c r="F36" s="220"/>
-      <c r="G36" s="221"/>
+      <c r="B36" s="310"/>
+      <c r="C36" s="310"/>
+      <c r="D36" s="310"/>
+      <c r="E36" s="310"/>
+      <c r="F36" s="310"/>
+      <c r="G36" s="311"/>
       <c r="H36" s="166"/>
     </row>
-    <row r="37" spans="1:8" ht="21">
+    <row r="37" spans="1:8" ht="20.5">
       <c r="A37" s="147">
         <v>19</v>
       </c>
@@ -4811,7 +4811,7 @@
       <c r="G37" s="151"/>
       <c r="H37" s="146"/>
     </row>
-    <row r="38" spans="1:8" ht="21">
+    <row r="38" spans="1:8" ht="20.5">
       <c r="A38" s="147">
         <v>20</v>
       </c>
@@ -4834,7 +4834,7 @@
       <c r="G38" s="151"/>
       <c r="H38" s="146"/>
     </row>
-    <row r="39" spans="1:8" ht="21">
+    <row r="39" spans="1:8" ht="20.5">
       <c r="A39" s="147">
         <v>21</v>
       </c>
@@ -4857,12 +4857,12 @@
       <c r="G39" s="151"/>
       <c r="H39" s="146"/>
     </row>
-    <row r="40" spans="1:8" s="165" customFormat="1" ht="21">
-      <c r="A40" s="217" t="s">
+    <row r="40" spans="1:8" s="165" customFormat="1" ht="20">
+      <c r="A40" s="307" t="s">
         <v>200</v>
       </c>
-      <c r="B40" s="218"/>
-      <c r="C40" s="218"/>
+      <c r="B40" s="308"/>
+      <c r="C40" s="308"/>
       <c r="D40" s="162">
         <f>SUM(D37:D39)</f>
         <v>346000</v>
@@ -4875,12 +4875,12 @@
       <c r="G40" s="163"/>
       <c r="H40" s="164"/>
     </row>
-    <row r="41" spans="1:8" s="165" customFormat="1" ht="21">
-      <c r="A41" s="222" t="s">
+    <row r="41" spans="1:8" s="165" customFormat="1" ht="20">
+      <c r="A41" s="312" t="s">
         <v>201</v>
       </c>
-      <c r="B41" s="223"/>
-      <c r="C41" s="223"/>
+      <c r="B41" s="313"/>
+      <c r="C41" s="313"/>
       <c r="D41" s="171">
         <f t="shared" ref="D41" si="3">D40+D35</f>
         <v>1426000</v>
@@ -4893,7 +4893,7 @@
       <c r="G41" s="172"/>
       <c r="H41" s="164"/>
     </row>
-    <row r="42" spans="1:8" s="178" customFormat="1" ht="21">
+    <row r="42" spans="1:8" s="178" customFormat="1" ht="20">
       <c r="A42" s="173"/>
       <c r="B42" s="174"/>
       <c r="C42" s="173"/>
@@ -4904,15 +4904,15 @@
       <c r="H42" s="177"/>
     </row>
     <row r="43" spans="1:8" s="165" customFormat="1" ht="51.75" customHeight="1">
-      <c r="A43" s="224" t="s">
+      <c r="A43" s="314" t="s">
         <v>202</v>
       </c>
-      <c r="B43" s="225"/>
-      <c r="C43" s="225"/>
-      <c r="D43" s="226"/>
-      <c r="E43" s="226"/>
-      <c r="F43" s="226"/>
-      <c r="G43" s="226"/>
+      <c r="B43" s="315"/>
+      <c r="C43" s="315"/>
+      <c r="D43" s="316"/>
+      <c r="E43" s="316"/>
+      <c r="F43" s="316"/>
+      <c r="G43" s="316"/>
       <c r="H43" s="164"/>
     </row>
     <row r="44" spans="1:8" s="165" customFormat="1" ht="29.25" customHeight="1">
@@ -5260,12 +5260,13 @@
     <row r="236" ht="15.75" hidden="1" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D43:G43"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A41:C41"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="G28:G29"/>
     <mergeCell ref="A9:G9"/>
@@ -5282,13 +5283,12 @@
     <mergeCell ref="D22:D23"/>
     <mergeCell ref="E22:E23"/>
     <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D43:G43"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="D7:G7"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C4" r:id="rId1" xr:uid="{E029C6F9-2DED-4FB9-8BAE-C279498AA88D}"/>
@@ -5304,57 +5304,57 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I79"/>
-  <sheetFormatPr defaultColWidth="33.625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="33.58203125" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="9.125" customWidth="1"/>
+    <col min="1" max="1" width="9.08203125" customWidth="1"/>
     <col min="2" max="2" width="44.5" customWidth="1"/>
     <col min="3" max="3" width="56" customWidth="1"/>
     <col min="4" max="4" width="14.25" customWidth="1"/>
-    <col min="5" max="5" width="15.375" customWidth="1"/>
-    <col min="6" max="6" width="14.375" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="266" t="s">
+      <c r="C1" s="317" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="266"/>
-      <c r="E1" s="266"/>
-      <c r="F1" s="266"/>
+      <c r="D1" s="317"/>
+      <c r="E1" s="317"/>
+      <c r="F1" s="317"/>
     </row>
     <row r="2" spans="1:9" s="4" customFormat="1" ht="16.5">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
-      <c r="C2" s="267"/>
-      <c r="D2" s="267"/>
-      <c r="E2" s="267"/>
-      <c r="F2" s="267"/>
+      <c r="C2" s="318"/>
+      <c r="D2" s="318"/>
+      <c r="E2" s="318"/>
+      <c r="F2" s="318"/>
     </row>
     <row r="3" spans="1:9" s="4" customFormat="1" ht="16.5">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="267"/>
-      <c r="D3" s="267"/>
-      <c r="E3" s="267"/>
-      <c r="F3" s="267"/>
+      <c r="C3" s="318"/>
+      <c r="D3" s="318"/>
+      <c r="E3" s="318"/>
+      <c r="F3" s="318"/>
     </row>
     <row r="4" spans="1:9" s="4" customFormat="1" ht="16.5">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
-      <c r="C4" s="267"/>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
+      <c r="C4" s="318"/>
+      <c r="D4" s="318"/>
+      <c r="E4" s="318"/>
+      <c r="F4" s="318"/>
     </row>
     <row r="5" spans="1:9" s="4" customFormat="1" ht="16.5">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
-      <c r="C5" s="267"/>
-      <c r="D5" s="267"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
+      <c r="C5" s="318"/>
+      <c r="D5" s="318"/>
+      <c r="E5" s="318"/>
+      <c r="F5" s="318"/>
     </row>
     <row r="6" spans="1:9" s="4" customFormat="1" ht="16.5">
       <c r="A6" s="5"/>
@@ -5364,15 +5364,15 @@
       <c r="E6" s="7"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:9" s="4" customFormat="1" ht="20.25">
-      <c r="A7" s="268" t="s">
+    <row r="7" spans="1:9" s="4" customFormat="1" ht="20">
+      <c r="A7" s="319" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="268"/>
-      <c r="C7" s="268"/>
-      <c r="D7" s="268"/>
-      <c r="E7" s="268"/>
-      <c r="F7" s="268"/>
+      <c r="B7" s="319"/>
+      <c r="C7" s="319"/>
+      <c r="D7" s="319"/>
+      <c r="E7" s="319"/>
+      <c r="F7" s="319"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
@@ -5390,36 +5390,36 @@
     </row>
     <row r="9" spans="1:9" s="4" customFormat="1" ht="16.5" customHeight="1">
       <c r="A9" s="10"/>
-      <c r="B9" s="269" t="s">
+      <c r="B9" s="320" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="270"/>
-      <c r="D9" s="270"/>
-      <c r="E9" s="270"/>
-      <c r="F9" s="271"/>
+      <c r="C9" s="321"/>
+      <c r="D9" s="321"/>
+      <c r="E9" s="321"/>
+      <c r="F9" s="322"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
     </row>
     <row r="10" spans="1:9" s="4" customFormat="1">
-      <c r="A10" s="272" t="s">
+      <c r="A10" s="323" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="273"/>
-      <c r="C10" s="273"/>
-      <c r="D10" s="273"/>
-      <c r="E10" s="273"/>
-      <c r="F10" s="274"/>
+      <c r="B10" s="324"/>
+      <c r="C10" s="324"/>
+      <c r="D10" s="324"/>
+      <c r="E10" s="324"/>
+      <c r="F10" s="325"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
     </row>
     <row r="11" spans="1:9" s="4" customFormat="1">
-      <c r="A11" s="275"/>
-      <c r="B11" s="276"/>
-      <c r="C11" s="276"/>
-      <c r="D11" s="276"/>
-      <c r="E11" s="276"/>
-      <c r="F11" s="277"/>
+      <c r="A11" s="326"/>
+      <c r="B11" s="327"/>
+      <c r="C11" s="327"/>
+      <c r="D11" s="327"/>
+      <c r="E11" s="327"/>
+      <c r="F11" s="328"/>
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
@@ -5456,12 +5456,12 @@
       </c>
     </row>
     <row r="14" spans="1:9" s="65" customFormat="1" ht="16.5">
-      <c r="A14" s="261" t="s">
+      <c r="A14" s="345" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="262"/>
-      <c r="C14" s="262"/>
-      <c r="D14" s="262"/>
+      <c r="B14" s="346"/>
+      <c r="C14" s="346"/>
+      <c r="D14" s="346"/>
       <c r="E14" s="66">
         <f>SUM(E15:E35)</f>
         <v>1163000</v>
@@ -5472,85 +5472,85 @@
       </c>
     </row>
     <row r="15" spans="1:9" s="52" customFormat="1" ht="33">
-      <c r="A15" s="282">
+      <c r="A15" s="333">
         <v>1</v>
       </c>
-      <c r="B15" s="280" t="s">
+      <c r="B15" s="331" t="s">
         <v>138</v>
       </c>
       <c r="C15" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="282">
+      <c r="D15" s="333">
         <v>214</v>
       </c>
-      <c r="E15" s="278">
+      <c r="E15" s="329">
         <v>200000</v>
       </c>
-      <c r="F15" s="278">
+      <c r="F15" s="329">
         <f>E15*D15</f>
         <v>42800000</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="52" customFormat="1" ht="16.5">
-      <c r="A16" s="286"/>
-      <c r="B16" s="287"/>
+      <c r="A16" s="337"/>
+      <c r="B16" s="338"/>
       <c r="C16" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="286"/>
-      <c r="E16" s="288"/>
-      <c r="F16" s="288"/>
+      <c r="D16" s="337"/>
+      <c r="E16" s="339"/>
+      <c r="F16" s="339"/>
     </row>
     <row r="17" spans="1:6" s="52" customFormat="1" ht="33">
-      <c r="A17" s="286"/>
-      <c r="B17" s="287"/>
+      <c r="A17" s="337"/>
+      <c r="B17" s="338"/>
       <c r="C17" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="286"/>
-      <c r="E17" s="288"/>
-      <c r="F17" s="288"/>
+      <c r="D17" s="337"/>
+      <c r="E17" s="339"/>
+      <c r="F17" s="339"/>
     </row>
     <row r="18" spans="1:6" s="52" customFormat="1" ht="33">
-      <c r="A18" s="286"/>
-      <c r="B18" s="287"/>
+      <c r="A18" s="337"/>
+      <c r="B18" s="338"/>
       <c r="C18" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="286"/>
-      <c r="E18" s="288"/>
-      <c r="F18" s="288"/>
+      <c r="D18" s="337"/>
+      <c r="E18" s="339"/>
+      <c r="F18" s="339"/>
     </row>
     <row r="19" spans="1:6" s="52" customFormat="1" ht="16.5">
-      <c r="A19" s="286"/>
-      <c r="B19" s="287"/>
+      <c r="A19" s="337"/>
+      <c r="B19" s="338"/>
       <c r="C19" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="286"/>
-      <c r="E19" s="288"/>
-      <c r="F19" s="288"/>
+      <c r="D19" s="337"/>
+      <c r="E19" s="339"/>
+      <c r="F19" s="339"/>
     </row>
     <row r="20" spans="1:6" s="52" customFormat="1" ht="16.5">
-      <c r="A20" s="286"/>
-      <c r="B20" s="287"/>
+      <c r="A20" s="337"/>
+      <c r="B20" s="338"/>
       <c r="C20" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="286"/>
-      <c r="E20" s="288"/>
-      <c r="F20" s="288"/>
+      <c r="D20" s="337"/>
+      <c r="E20" s="339"/>
+      <c r="F20" s="339"/>
     </row>
     <row r="21" spans="1:6" s="52" customFormat="1" ht="16.5">
-      <c r="A21" s="283"/>
-      <c r="B21" s="281"/>
+      <c r="A21" s="334"/>
+      <c r="B21" s="332"/>
       <c r="C21" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="283"/>
-      <c r="E21" s="279"/>
-      <c r="F21" s="279"/>
+      <c r="D21" s="334"/>
+      <c r="E21" s="330"/>
+      <c r="F21" s="330"/>
     </row>
     <row r="22" spans="1:6" s="52" customFormat="1" ht="33">
       <c r="A22" s="53">
@@ -5573,7 +5573,7 @@
         <v>21828000</v>
       </c>
     </row>
-    <row r="23" spans="1:6" s="52" customFormat="1" ht="47.25">
+    <row r="23" spans="1:6" s="52" customFormat="1" ht="46.5">
       <c r="A23" s="53">
         <v>3</v>
       </c>
@@ -5657,7 +5657,7 @@
         <v>5778000</v>
       </c>
     </row>
-    <row r="27" spans="1:6" s="52" customFormat="1" ht="31.5">
+    <row r="27" spans="1:6" s="52" customFormat="1" ht="31">
       <c r="A27" s="53">
         <v>7</v>
       </c>
@@ -5678,7 +5678,7 @@
         <v>10058000</v>
       </c>
     </row>
-    <row r="28" spans="1:6" s="52" customFormat="1" ht="31.5">
+    <row r="28" spans="1:6" s="52" customFormat="1" ht="31">
       <c r="A28" s="53">
         <v>8</v>
       </c>
@@ -5699,7 +5699,7 @@
         <v>8774000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" s="52" customFormat="1" ht="31.5">
+    <row r="29" spans="1:6" s="52" customFormat="1" ht="31">
       <c r="A29" s="53">
         <v>9</v>
       </c>
@@ -5720,7 +5720,7 @@
         <v>8774000</v>
       </c>
     </row>
-    <row r="30" spans="1:6" s="52" customFormat="1" ht="31.5">
+    <row r="30" spans="1:6" s="52" customFormat="1" ht="31">
       <c r="A30" s="53">
         <v>10</v>
       </c>
@@ -5741,38 +5741,38 @@
         <v>12626000</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="52" customFormat="1" ht="31.5">
+    <row r="31" spans="1:6" s="52" customFormat="1" ht="31">
       <c r="A31" s="53">
         <v>11</v>
       </c>
       <c r="B31" s="60" t="s">
         <v>85</v>
       </c>
-      <c r="C31" s="280" t="s">
+      <c r="C31" s="331" t="s">
         <v>21</v>
       </c>
-      <c r="D31" s="282">
+      <c r="D31" s="333">
         <v>214</v>
       </c>
-      <c r="E31" s="284">
+      <c r="E31" s="335">
         <v>60000</v>
       </c>
-      <c r="F31" s="278">
+      <c r="F31" s="329">
         <f>D31*E31</f>
         <v>12840000</v>
       </c>
     </row>
-    <row r="32" spans="1:6" s="52" customFormat="1" ht="31.5">
+    <row r="32" spans="1:6" s="52" customFormat="1" ht="31">
       <c r="A32" s="53">
         <v>12</v>
       </c>
       <c r="B32" s="60" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="281"/>
-      <c r="D32" s="283"/>
-      <c r="E32" s="285"/>
-      <c r="F32" s="279"/>
+      <c r="C32" s="332"/>
+      <c r="D32" s="334"/>
+      <c r="E32" s="336"/>
+      <c r="F32" s="330"/>
     </row>
     <row r="33" spans="1:7" s="52" customFormat="1" ht="33">
       <c r="A33" s="53">
@@ -5838,12 +5838,12 @@
       </c>
     </row>
     <row r="36" spans="1:7" s="65" customFormat="1" ht="16.5">
-      <c r="A36" s="261" t="s">
+      <c r="A36" s="345" t="s">
         <v>90</v>
       </c>
-      <c r="B36" s="262"/>
-      <c r="C36" s="262"/>
-      <c r="D36" s="262"/>
+      <c r="B36" s="346"/>
+      <c r="C36" s="346"/>
+      <c r="D36" s="346"/>
       <c r="E36" s="66">
         <f>SUM(E37:E40)</f>
         <v>769000</v>
@@ -5853,7 +5853,7 @@
         <v>17687000</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="52" customFormat="1" ht="31.5">
+    <row r="37" spans="1:7" s="52" customFormat="1" ht="31">
       <c r="A37" s="53">
         <v>16</v>
       </c>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="G37" s="68"/>
     </row>
-    <row r="38" spans="1:7" s="52" customFormat="1" ht="31.5">
+    <row r="38" spans="1:7" s="52" customFormat="1" ht="31">
       <c r="A38" s="53">
         <v>17</v>
       </c>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="G39" s="68"/>
     </row>
-    <row r="40" spans="1:7" s="52" customFormat="1" ht="31.5">
+    <row r="40" spans="1:7" s="52" customFormat="1" ht="31">
       <c r="A40" s="53">
         <v>19</v>
       </c>
@@ -5941,12 +5941,12 @@
       <c r="G40" s="68"/>
     </row>
     <row r="41" spans="1:7" s="65" customFormat="1" ht="16.5">
-      <c r="A41" s="261" t="s">
+      <c r="A41" s="345" t="s">
         <v>134</v>
       </c>
-      <c r="B41" s="262"/>
-      <c r="C41" s="262"/>
-      <c r="D41" s="262"/>
+      <c r="B41" s="346"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
       <c r="E41" s="66">
         <f>SUM(E42:E48)</f>
         <v>1450000</v>
@@ -5956,7 +5956,7 @@
         <v>259509000</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="52" customFormat="1" ht="31.5">
+    <row r="42" spans="1:7" s="52" customFormat="1" ht="31">
       <c r="A42" s="53">
         <v>20</v>
       </c>
@@ -5977,7 +5977,7 @@
         <v>49220000</v>
       </c>
     </row>
-    <row r="43" spans="1:7" s="52" customFormat="1" ht="31.5">
+    <row r="43" spans="1:7" s="52" customFormat="1" ht="31">
       <c r="A43" s="53">
         <v>21</v>
       </c>
@@ -5998,7 +5998,7 @@
         <v>37236000</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="52" customFormat="1" ht="31.5">
+    <row r="44" spans="1:7" s="52" customFormat="1" ht="31">
       <c r="A44" s="53">
         <v>22</v>
       </c>
@@ -6019,7 +6019,7 @@
         <v>25894000</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="52" customFormat="1" ht="31.5">
+    <row r="45" spans="1:7" s="52" customFormat="1" ht="31">
       <c r="A45" s="53">
         <v>23</v>
       </c>
@@ -6040,7 +6040,7 @@
         <v>49434000</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="52" customFormat="1" ht="31.5">
+    <row r="46" spans="1:7" s="52" customFormat="1" ht="31">
       <c r="A46" s="53">
         <v>24</v>
       </c>
@@ -6061,7 +6061,7 @@
         <v>37022000</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="52" customFormat="1" ht="31.5">
+    <row r="47" spans="1:7" s="52" customFormat="1" ht="31">
       <c r="A47" s="53">
         <v>25</v>
       </c>
@@ -6082,7 +6082,7 @@
         <v>55390000</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="52" customFormat="1" ht="31.5">
+    <row r="48" spans="1:7" s="52" customFormat="1" ht="31">
       <c r="A48" s="53">
         <v>26</v>
       </c>
@@ -6122,12 +6122,12 @@
       </c>
     </row>
     <row r="50" spans="1:6" s="65" customFormat="1" ht="16.5">
-      <c r="A50" s="261" t="s">
+      <c r="A50" s="345" t="s">
         <v>110</v>
       </c>
-      <c r="B50" s="262"/>
-      <c r="C50" s="262"/>
-      <c r="D50" s="262"/>
+      <c r="B50" s="346"/>
+      <c r="C50" s="346"/>
+      <c r="D50" s="346"/>
       <c r="E50" s="66">
         <f>SUM(E51:E54)</f>
         <v>454000</v>
@@ -6137,7 +6137,7 @@
         <v>2270000</v>
       </c>
     </row>
-    <row r="51" spans="1:6" s="52" customFormat="1" ht="31.5">
+    <row r="51" spans="1:6" s="52" customFormat="1" ht="31">
       <c r="A51" s="53">
         <v>27</v>
       </c>
@@ -6215,7 +6215,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="17.25">
+    <row r="55" spans="1:6" ht="16.5">
       <c r="A55" s="21"/>
       <c r="B55" s="19" t="s">
         <v>32</v>
@@ -6228,7 +6228,7 @@
         <v>528348000</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="17.25" hidden="1">
+    <row r="56" spans="1:6" ht="16.5" hidden="1">
       <c r="A56" s="21"/>
       <c r="B56" s="19" t="s">
         <v>33</v>
@@ -6241,7 +6241,7 @@
         <v>3537400</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="17.25" hidden="1">
+    <row r="57" spans="1:6" ht="16.5" hidden="1">
       <c r="A57" s="21"/>
       <c r="B57" s="19" t="s">
         <v>139</v>
@@ -6265,11 +6265,11 @@
     <row r="59" spans="1:6" ht="16.5">
       <c r="A59" s="23"/>
       <c r="B59" s="23"/>
-      <c r="D59" s="258" t="s">
+      <c r="D59" s="343" t="s">
         <v>136</v>
       </c>
-      <c r="E59" s="258"/>
-      <c r="F59" s="258"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="60" spans="1:6" ht="16.5">
       <c r="A60" s="23"/>
@@ -6283,34 +6283,34 @@
       <c r="A61" s="23"/>
       <c r="B61" s="23"/>
       <c r="C61" s="23"/>
-      <c r="D61" s="260" t="s">
+      <c r="D61" s="344" t="s">
         <v>135</v>
       </c>
-      <c r="E61" s="260"/>
-      <c r="F61" s="260"/>
+      <c r="E61" s="344"/>
+      <c r="F61" s="344"/>
     </row>
     <row r="62" spans="1:6" ht="16.5">
       <c r="A62" s="23"/>
       <c r="B62" s="23"/>
       <c r="C62" s="23"/>
-      <c r="D62" s="258"/>
-      <c r="E62" s="258"/>
+      <c r="D62" s="343"/>
+      <c r="E62" s="343"/>
       <c r="F62" s="23"/>
     </row>
     <row r="63" spans="1:6" ht="16.5">
       <c r="A63" s="23"/>
       <c r="B63" s="23"/>
       <c r="C63" s="23"/>
-      <c r="D63" s="258"/>
-      <c r="E63" s="258"/>
+      <c r="D63" s="343"/>
+      <c r="E63" s="343"/>
       <c r="F63" s="23"/>
     </row>
     <row r="64" spans="1:6" ht="16.5">
       <c r="A64" s="23"/>
       <c r="B64" s="23"/>
       <c r="C64" s="23"/>
-      <c r="D64" s="258"/>
-      <c r="E64" s="258"/>
+      <c r="D64" s="343"/>
+      <c r="E64" s="343"/>
       <c r="F64" s="23"/>
     </row>
     <row r="65" spans="1:6" ht="16.5">
@@ -6325,79 +6325,79 @@
       <c r="A66" s="23"/>
       <c r="B66" s="23"/>
       <c r="C66" s="23"/>
-      <c r="D66" s="258"/>
-      <c r="E66" s="258"/>
+      <c r="D66" s="343"/>
+      <c r="E66" s="343"/>
       <c r="F66" s="23"/>
     </row>
     <row r="67" spans="1:6" ht="16.5">
       <c r="A67" s="23"/>
       <c r="B67" s="23"/>
       <c r="C67" s="23"/>
-      <c r="D67" s="259" t="s">
+      <c r="D67" s="347" t="s">
         <v>137</v>
       </c>
-      <c r="E67" s="259"/>
-      <c r="F67" s="259"/>
+      <c r="E67" s="347"/>
+      <c r="F67" s="347"/>
     </row>
     <row r="68" spans="1:6" s="25" customFormat="1" ht="16.5">
-      <c r="A68" s="264" t="s">
+      <c r="A68" s="341" t="s">
         <v>35</v>
       </c>
-      <c r="B68" s="264"/>
-      <c r="C68" s="264"/>
-      <c r="D68" s="264"/>
+      <c r="B68" s="341"/>
+      <c r="C68" s="341"/>
+      <c r="D68" s="341"/>
       <c r="E68" s="7"/>
       <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" s="25" customFormat="1" ht="16.5">
       <c r="A69" s="26"/>
-      <c r="B69" s="263" t="s">
+      <c r="B69" s="340" t="s">
         <v>36</v>
       </c>
-      <c r="C69" s="263"/>
-      <c r="D69" s="263"/>
-      <c r="E69" s="263"/>
-      <c r="F69" s="263"/>
+      <c r="C69" s="340"/>
+      <c r="D69" s="340"/>
+      <c r="E69" s="340"/>
+      <c r="F69" s="340"/>
     </row>
     <row r="70" spans="1:6" s="25" customFormat="1" ht="16.5">
       <c r="A70" s="26"/>
-      <c r="B70" s="263" t="s">
+      <c r="B70" s="340" t="s">
         <v>37</v>
       </c>
-      <c r="C70" s="263"/>
-      <c r="D70" s="263"/>
-      <c r="E70" s="263"/>
-      <c r="F70" s="263"/>
+      <c r="C70" s="340"/>
+      <c r="D70" s="340"/>
+      <c r="E70" s="340"/>
+      <c r="F70" s="340"/>
     </row>
     <row r="71" spans="1:6" s="28" customFormat="1" ht="33.75" customHeight="1">
       <c r="A71" s="27"/>
-      <c r="B71" s="263" t="s">
+      <c r="B71" s="340" t="s">
         <v>38</v>
       </c>
-      <c r="C71" s="263"/>
-      <c r="D71" s="263"/>
-      <c r="E71" s="263"/>
-      <c r="F71" s="263"/>
+      <c r="C71" s="340"/>
+      <c r="D71" s="340"/>
+      <c r="E71" s="340"/>
+      <c r="F71" s="340"/>
     </row>
     <row r="72" spans="1:6" s="30" customFormat="1" ht="36" customHeight="1">
       <c r="A72" s="29"/>
-      <c r="B72" s="265" t="s">
+      <c r="B72" s="342" t="s">
         <v>39</v>
       </c>
-      <c r="C72" s="265"/>
-      <c r="D72" s="265"/>
-      <c r="E72" s="265"/>
-      <c r="F72" s="265"/>
+      <c r="C72" s="342"/>
+      <c r="D72" s="342"/>
+      <c r="E72" s="342"/>
+      <c r="F72" s="342"/>
     </row>
     <row r="73" spans="1:6" s="4" customFormat="1" ht="16.5">
       <c r="A73" s="24"/>
-      <c r="B73" s="263" t="s">
+      <c r="B73" s="340" t="s">
         <v>40</v>
       </c>
-      <c r="C73" s="263"/>
-      <c r="D73" s="263"/>
-      <c r="E73" s="263"/>
-      <c r="F73" s="263"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" s="4" customFormat="1" ht="16.5">
       <c r="A74" s="24"/>
@@ -6461,6 +6461,23 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="B72:F72"/>
     <mergeCell ref="C1:F5"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="B9:F9"/>
@@ -6474,23 +6491,6 @@
     <mergeCell ref="D15:D21"/>
     <mergeCell ref="E15:E21"/>
     <mergeCell ref="F15:F21"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B70:F70"/>
-    <mergeCell ref="B71:F71"/>
-    <mergeCell ref="B72:F72"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="D64:E64"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.2" top="0.4" bottom="0.2" header="0.3" footer="0.3"/>
   <pageSetup scale="61" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -6507,472 +6507,472 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G102"/>
-  <sheetFormatPr defaultColWidth="49.875" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="49.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="6.125" style="86" customWidth="1"/>
-    <col min="2" max="2" width="41.125" style="86" customWidth="1"/>
+    <col min="1" max="1" width="6.08203125" style="86" customWidth="1"/>
+    <col min="2" max="2" width="41.08203125" style="86" customWidth="1"/>
     <col min="3" max="3" width="45.25" style="86" customWidth="1"/>
-    <col min="4" max="4" width="9.125" style="86" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.125" style="86" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.08203125" style="86" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.08203125" style="86" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.5" style="86" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.125" style="86" customWidth="1"/>
-    <col min="8" max="255" width="49.875" style="86"/>
-    <col min="256" max="256" width="6.125" style="86" customWidth="1"/>
-    <col min="257" max="257" width="22.125" style="86" customWidth="1"/>
+    <col min="7" max="7" width="19.08203125" style="86" customWidth="1"/>
+    <col min="8" max="255" width="49.83203125" style="86"/>
+    <col min="256" max="256" width="6.08203125" style="86" customWidth="1"/>
+    <col min="257" max="257" width="22.08203125" style="86" customWidth="1"/>
     <col min="258" max="258" width="45.25" style="86" customWidth="1"/>
-    <col min="259" max="261" width="12.375" style="86" customWidth="1"/>
+    <col min="259" max="261" width="12.33203125" style="86" customWidth="1"/>
     <col min="262" max="262" width="15.75" style="86" customWidth="1"/>
-    <col min="263" max="511" width="49.875" style="86"/>
-    <col min="512" max="512" width="6.125" style="86" customWidth="1"/>
-    <col min="513" max="513" width="22.125" style="86" customWidth="1"/>
+    <col min="263" max="511" width="49.83203125" style="86"/>
+    <col min="512" max="512" width="6.08203125" style="86" customWidth="1"/>
+    <col min="513" max="513" width="22.08203125" style="86" customWidth="1"/>
     <col min="514" max="514" width="45.25" style="86" customWidth="1"/>
-    <col min="515" max="517" width="12.375" style="86" customWidth="1"/>
+    <col min="515" max="517" width="12.33203125" style="86" customWidth="1"/>
     <col min="518" max="518" width="15.75" style="86" customWidth="1"/>
-    <col min="519" max="767" width="49.875" style="86"/>
-    <col min="768" max="768" width="6.125" style="86" customWidth="1"/>
-    <col min="769" max="769" width="22.125" style="86" customWidth="1"/>
+    <col min="519" max="767" width="49.83203125" style="86"/>
+    <col min="768" max="768" width="6.08203125" style="86" customWidth="1"/>
+    <col min="769" max="769" width="22.08203125" style="86" customWidth="1"/>
     <col min="770" max="770" width="45.25" style="86" customWidth="1"/>
-    <col min="771" max="773" width="12.375" style="86" customWidth="1"/>
+    <col min="771" max="773" width="12.33203125" style="86" customWidth="1"/>
     <col min="774" max="774" width="15.75" style="86" customWidth="1"/>
-    <col min="775" max="1023" width="49.875" style="86"/>
-    <col min="1024" max="1024" width="6.125" style="86" customWidth="1"/>
-    <col min="1025" max="1025" width="22.125" style="86" customWidth="1"/>
+    <col min="775" max="1023" width="49.83203125" style="86"/>
+    <col min="1024" max="1024" width="6.08203125" style="86" customWidth="1"/>
+    <col min="1025" max="1025" width="22.08203125" style="86" customWidth="1"/>
     <col min="1026" max="1026" width="45.25" style="86" customWidth="1"/>
-    <col min="1027" max="1029" width="12.375" style="86" customWidth="1"/>
+    <col min="1027" max="1029" width="12.33203125" style="86" customWidth="1"/>
     <col min="1030" max="1030" width="15.75" style="86" customWidth="1"/>
-    <col min="1031" max="1279" width="49.875" style="86"/>
-    <col min="1280" max="1280" width="6.125" style="86" customWidth="1"/>
-    <col min="1281" max="1281" width="22.125" style="86" customWidth="1"/>
+    <col min="1031" max="1279" width="49.83203125" style="86"/>
+    <col min="1280" max="1280" width="6.08203125" style="86" customWidth="1"/>
+    <col min="1281" max="1281" width="22.08203125" style="86" customWidth="1"/>
     <col min="1282" max="1282" width="45.25" style="86" customWidth="1"/>
-    <col min="1283" max="1285" width="12.375" style="86" customWidth="1"/>
+    <col min="1283" max="1285" width="12.33203125" style="86" customWidth="1"/>
     <col min="1286" max="1286" width="15.75" style="86" customWidth="1"/>
-    <col min="1287" max="1535" width="49.875" style="86"/>
-    <col min="1536" max="1536" width="6.125" style="86" customWidth="1"/>
-    <col min="1537" max="1537" width="22.125" style="86" customWidth="1"/>
+    <col min="1287" max="1535" width="49.83203125" style="86"/>
+    <col min="1536" max="1536" width="6.08203125" style="86" customWidth="1"/>
+    <col min="1537" max="1537" width="22.08203125" style="86" customWidth="1"/>
     <col min="1538" max="1538" width="45.25" style="86" customWidth="1"/>
-    <col min="1539" max="1541" width="12.375" style="86" customWidth="1"/>
+    <col min="1539" max="1541" width="12.33203125" style="86" customWidth="1"/>
     <col min="1542" max="1542" width="15.75" style="86" customWidth="1"/>
-    <col min="1543" max="1791" width="49.875" style="86"/>
-    <col min="1792" max="1792" width="6.125" style="86" customWidth="1"/>
-    <col min="1793" max="1793" width="22.125" style="86" customWidth="1"/>
+    <col min="1543" max="1791" width="49.83203125" style="86"/>
+    <col min="1792" max="1792" width="6.08203125" style="86" customWidth="1"/>
+    <col min="1793" max="1793" width="22.08203125" style="86" customWidth="1"/>
     <col min="1794" max="1794" width="45.25" style="86" customWidth="1"/>
-    <col min="1795" max="1797" width="12.375" style="86" customWidth="1"/>
+    <col min="1795" max="1797" width="12.33203125" style="86" customWidth="1"/>
     <col min="1798" max="1798" width="15.75" style="86" customWidth="1"/>
-    <col min="1799" max="2047" width="49.875" style="86"/>
-    <col min="2048" max="2048" width="6.125" style="86" customWidth="1"/>
-    <col min="2049" max="2049" width="22.125" style="86" customWidth="1"/>
+    <col min="1799" max="2047" width="49.83203125" style="86"/>
+    <col min="2048" max="2048" width="6.08203125" style="86" customWidth="1"/>
+    <col min="2049" max="2049" width="22.08203125" style="86" customWidth="1"/>
     <col min="2050" max="2050" width="45.25" style="86" customWidth="1"/>
-    <col min="2051" max="2053" width="12.375" style="86" customWidth="1"/>
+    <col min="2051" max="2053" width="12.33203125" style="86" customWidth="1"/>
     <col min="2054" max="2054" width="15.75" style="86" customWidth="1"/>
-    <col min="2055" max="2303" width="49.875" style="86"/>
-    <col min="2304" max="2304" width="6.125" style="86" customWidth="1"/>
-    <col min="2305" max="2305" width="22.125" style="86" customWidth="1"/>
+    <col min="2055" max="2303" width="49.83203125" style="86"/>
+    <col min="2304" max="2304" width="6.08203125" style="86" customWidth="1"/>
+    <col min="2305" max="2305" width="22.08203125" style="86" customWidth="1"/>
     <col min="2306" max="2306" width="45.25" style="86" customWidth="1"/>
-    <col min="2307" max="2309" width="12.375" style="86" customWidth="1"/>
+    <col min="2307" max="2309" width="12.33203125" style="86" customWidth="1"/>
     <col min="2310" max="2310" width="15.75" style="86" customWidth="1"/>
-    <col min="2311" max="2559" width="49.875" style="86"/>
-    <col min="2560" max="2560" width="6.125" style="86" customWidth="1"/>
-    <col min="2561" max="2561" width="22.125" style="86" customWidth="1"/>
+    <col min="2311" max="2559" width="49.83203125" style="86"/>
+    <col min="2560" max="2560" width="6.08203125" style="86" customWidth="1"/>
+    <col min="2561" max="2561" width="22.08203125" style="86" customWidth="1"/>
     <col min="2562" max="2562" width="45.25" style="86" customWidth="1"/>
-    <col min="2563" max="2565" width="12.375" style="86" customWidth="1"/>
+    <col min="2563" max="2565" width="12.33203125" style="86" customWidth="1"/>
     <col min="2566" max="2566" width="15.75" style="86" customWidth="1"/>
-    <col min="2567" max="2815" width="49.875" style="86"/>
-    <col min="2816" max="2816" width="6.125" style="86" customWidth="1"/>
-    <col min="2817" max="2817" width="22.125" style="86" customWidth="1"/>
+    <col min="2567" max="2815" width="49.83203125" style="86"/>
+    <col min="2816" max="2816" width="6.08203125" style="86" customWidth="1"/>
+    <col min="2817" max="2817" width="22.08203125" style="86" customWidth="1"/>
     <col min="2818" max="2818" width="45.25" style="86" customWidth="1"/>
-    <col min="2819" max="2821" width="12.375" style="86" customWidth="1"/>
+    <col min="2819" max="2821" width="12.33203125" style="86" customWidth="1"/>
     <col min="2822" max="2822" width="15.75" style="86" customWidth="1"/>
-    <col min="2823" max="3071" width="49.875" style="86"/>
-    <col min="3072" max="3072" width="6.125" style="86" customWidth="1"/>
-    <col min="3073" max="3073" width="22.125" style="86" customWidth="1"/>
+    <col min="2823" max="3071" width="49.83203125" style="86"/>
+    <col min="3072" max="3072" width="6.08203125" style="86" customWidth="1"/>
+    <col min="3073" max="3073" width="22.08203125" style="86" customWidth="1"/>
     <col min="3074" max="3074" width="45.25" style="86" customWidth="1"/>
-    <col min="3075" max="3077" width="12.375" style="86" customWidth="1"/>
+    <col min="3075" max="3077" width="12.33203125" style="86" customWidth="1"/>
     <col min="3078" max="3078" width="15.75" style="86" customWidth="1"/>
-    <col min="3079" max="3327" width="49.875" style="86"/>
-    <col min="3328" max="3328" width="6.125" style="86" customWidth="1"/>
-    <col min="3329" max="3329" width="22.125" style="86" customWidth="1"/>
+    <col min="3079" max="3327" width="49.83203125" style="86"/>
+    <col min="3328" max="3328" width="6.08203125" style="86" customWidth="1"/>
+    <col min="3329" max="3329" width="22.08203125" style="86" customWidth="1"/>
     <col min="3330" max="3330" width="45.25" style="86" customWidth="1"/>
-    <col min="3331" max="3333" width="12.375" style="86" customWidth="1"/>
+    <col min="3331" max="3333" width="12.33203125" style="86" customWidth="1"/>
     <col min="3334" max="3334" width="15.75" style="86" customWidth="1"/>
-    <col min="3335" max="3583" width="49.875" style="86"/>
-    <col min="3584" max="3584" width="6.125" style="86" customWidth="1"/>
-    <col min="3585" max="3585" width="22.125" style="86" customWidth="1"/>
+    <col min="3335" max="3583" width="49.83203125" style="86"/>
+    <col min="3584" max="3584" width="6.08203125" style="86" customWidth="1"/>
+    <col min="3585" max="3585" width="22.08203125" style="86" customWidth="1"/>
     <col min="3586" max="3586" width="45.25" style="86" customWidth="1"/>
-    <col min="3587" max="3589" width="12.375" style="86" customWidth="1"/>
+    <col min="3587" max="3589" width="12.33203125" style="86" customWidth="1"/>
     <col min="3590" max="3590" width="15.75" style="86" customWidth="1"/>
-    <col min="3591" max="3839" width="49.875" style="86"/>
-    <col min="3840" max="3840" width="6.125" style="86" customWidth="1"/>
-    <col min="3841" max="3841" width="22.125" style="86" customWidth="1"/>
+    <col min="3591" max="3839" width="49.83203125" style="86"/>
+    <col min="3840" max="3840" width="6.08203125" style="86" customWidth="1"/>
+    <col min="3841" max="3841" width="22.08203125" style="86" customWidth="1"/>
     <col min="3842" max="3842" width="45.25" style="86" customWidth="1"/>
-    <col min="3843" max="3845" width="12.375" style="86" customWidth="1"/>
+    <col min="3843" max="3845" width="12.33203125" style="86" customWidth="1"/>
     <col min="3846" max="3846" width="15.75" style="86" customWidth="1"/>
-    <col min="3847" max="4095" width="49.875" style="86"/>
-    <col min="4096" max="4096" width="6.125" style="86" customWidth="1"/>
-    <col min="4097" max="4097" width="22.125" style="86" customWidth="1"/>
+    <col min="3847" max="4095" width="49.83203125" style="86"/>
+    <col min="4096" max="4096" width="6.08203125" style="86" customWidth="1"/>
+    <col min="4097" max="4097" width="22.08203125" style="86" customWidth="1"/>
     <col min="4098" max="4098" width="45.25" style="86" customWidth="1"/>
-    <col min="4099" max="4101" width="12.375" style="86" customWidth="1"/>
+    <col min="4099" max="4101" width="12.33203125" style="86" customWidth="1"/>
     <col min="4102" max="4102" width="15.75" style="86" customWidth="1"/>
-    <col min="4103" max="4351" width="49.875" style="86"/>
-    <col min="4352" max="4352" width="6.125" style="86" customWidth="1"/>
-    <col min="4353" max="4353" width="22.125" style="86" customWidth="1"/>
+    <col min="4103" max="4351" width="49.83203125" style="86"/>
+    <col min="4352" max="4352" width="6.08203125" style="86" customWidth="1"/>
+    <col min="4353" max="4353" width="22.08203125" style="86" customWidth="1"/>
     <col min="4354" max="4354" width="45.25" style="86" customWidth="1"/>
-    <col min="4355" max="4357" width="12.375" style="86" customWidth="1"/>
+    <col min="4355" max="4357" width="12.33203125" style="86" customWidth="1"/>
     <col min="4358" max="4358" width="15.75" style="86" customWidth="1"/>
-    <col min="4359" max="4607" width="49.875" style="86"/>
-    <col min="4608" max="4608" width="6.125" style="86" customWidth="1"/>
-    <col min="4609" max="4609" width="22.125" style="86" customWidth="1"/>
+    <col min="4359" max="4607" width="49.83203125" style="86"/>
+    <col min="4608" max="4608" width="6.08203125" style="86" customWidth="1"/>
+    <col min="4609" max="4609" width="22.08203125" style="86" customWidth="1"/>
     <col min="4610" max="4610" width="45.25" style="86" customWidth="1"/>
-    <col min="4611" max="4613" width="12.375" style="86" customWidth="1"/>
+    <col min="4611" max="4613" width="12.33203125" style="86" customWidth="1"/>
     <col min="4614" max="4614" width="15.75" style="86" customWidth="1"/>
-    <col min="4615" max="4863" width="49.875" style="86"/>
-    <col min="4864" max="4864" width="6.125" style="86" customWidth="1"/>
-    <col min="4865" max="4865" width="22.125" style="86" customWidth="1"/>
+    <col min="4615" max="4863" width="49.83203125" style="86"/>
+    <col min="4864" max="4864" width="6.08203125" style="86" customWidth="1"/>
+    <col min="4865" max="4865" width="22.08203125" style="86" customWidth="1"/>
     <col min="4866" max="4866" width="45.25" style="86" customWidth="1"/>
-    <col min="4867" max="4869" width="12.375" style="86" customWidth="1"/>
+    <col min="4867" max="4869" width="12.33203125" style="86" customWidth="1"/>
     <col min="4870" max="4870" width="15.75" style="86" customWidth="1"/>
-    <col min="4871" max="5119" width="49.875" style="86"/>
-    <col min="5120" max="5120" width="6.125" style="86" customWidth="1"/>
-    <col min="5121" max="5121" width="22.125" style="86" customWidth="1"/>
+    <col min="4871" max="5119" width="49.83203125" style="86"/>
+    <col min="5120" max="5120" width="6.08203125" style="86" customWidth="1"/>
+    <col min="5121" max="5121" width="22.08203125" style="86" customWidth="1"/>
     <col min="5122" max="5122" width="45.25" style="86" customWidth="1"/>
-    <col min="5123" max="5125" width="12.375" style="86" customWidth="1"/>
+    <col min="5123" max="5125" width="12.33203125" style="86" customWidth="1"/>
     <col min="5126" max="5126" width="15.75" style="86" customWidth="1"/>
-    <col min="5127" max="5375" width="49.875" style="86"/>
-    <col min="5376" max="5376" width="6.125" style="86" customWidth="1"/>
-    <col min="5377" max="5377" width="22.125" style="86" customWidth="1"/>
+    <col min="5127" max="5375" width="49.83203125" style="86"/>
+    <col min="5376" max="5376" width="6.08203125" style="86" customWidth="1"/>
+    <col min="5377" max="5377" width="22.08203125" style="86" customWidth="1"/>
     <col min="5378" max="5378" width="45.25" style="86" customWidth="1"/>
-    <col min="5379" max="5381" width="12.375" style="86" customWidth="1"/>
+    <col min="5379" max="5381" width="12.33203125" style="86" customWidth="1"/>
     <col min="5382" max="5382" width="15.75" style="86" customWidth="1"/>
-    <col min="5383" max="5631" width="49.875" style="86"/>
-    <col min="5632" max="5632" width="6.125" style="86" customWidth="1"/>
-    <col min="5633" max="5633" width="22.125" style="86" customWidth="1"/>
+    <col min="5383" max="5631" width="49.83203125" style="86"/>
+    <col min="5632" max="5632" width="6.08203125" style="86" customWidth="1"/>
+    <col min="5633" max="5633" width="22.08203125" style="86" customWidth="1"/>
     <col min="5634" max="5634" width="45.25" style="86" customWidth="1"/>
-    <col min="5635" max="5637" width="12.375" style="86" customWidth="1"/>
+    <col min="5635" max="5637" width="12.33203125" style="86" customWidth="1"/>
     <col min="5638" max="5638" width="15.75" style="86" customWidth="1"/>
-    <col min="5639" max="5887" width="49.875" style="86"/>
-    <col min="5888" max="5888" width="6.125" style="86" customWidth="1"/>
-    <col min="5889" max="5889" width="22.125" style="86" customWidth="1"/>
+    <col min="5639" max="5887" width="49.83203125" style="86"/>
+    <col min="5888" max="5888" width="6.08203125" style="86" customWidth="1"/>
+    <col min="5889" max="5889" width="22.08203125" style="86" customWidth="1"/>
     <col min="5890" max="5890" width="45.25" style="86" customWidth="1"/>
-    <col min="5891" max="5893" width="12.375" style="86" customWidth="1"/>
+    <col min="5891" max="5893" width="12.33203125" style="86" customWidth="1"/>
     <col min="5894" max="5894" width="15.75" style="86" customWidth="1"/>
-    <col min="5895" max="6143" width="49.875" style="86"/>
-    <col min="6144" max="6144" width="6.125" style="86" customWidth="1"/>
-    <col min="6145" max="6145" width="22.125" style="86" customWidth="1"/>
+    <col min="5895" max="6143" width="49.83203125" style="86"/>
+    <col min="6144" max="6144" width="6.08203125" style="86" customWidth="1"/>
+    <col min="6145" max="6145" width="22.08203125" style="86" customWidth="1"/>
     <col min="6146" max="6146" width="45.25" style="86" customWidth="1"/>
-    <col min="6147" max="6149" width="12.375" style="86" customWidth="1"/>
+    <col min="6147" max="6149" width="12.33203125" style="86" customWidth="1"/>
     <col min="6150" max="6150" width="15.75" style="86" customWidth="1"/>
-    <col min="6151" max="6399" width="49.875" style="86"/>
-    <col min="6400" max="6400" width="6.125" style="86" customWidth="1"/>
-    <col min="6401" max="6401" width="22.125" style="86" customWidth="1"/>
+    <col min="6151" max="6399" width="49.83203125" style="86"/>
+    <col min="6400" max="6400" width="6.08203125" style="86" customWidth="1"/>
+    <col min="6401" max="6401" width="22.08203125" style="86" customWidth="1"/>
     <col min="6402" max="6402" width="45.25" style="86" customWidth="1"/>
-    <col min="6403" max="6405" width="12.375" style="86" customWidth="1"/>
+    <col min="6403" max="6405" width="12.33203125" style="86" customWidth="1"/>
     <col min="6406" max="6406" width="15.75" style="86" customWidth="1"/>
-    <col min="6407" max="6655" width="49.875" style="86"/>
-    <col min="6656" max="6656" width="6.125" style="86" customWidth="1"/>
-    <col min="6657" max="6657" width="22.125" style="86" customWidth="1"/>
+    <col min="6407" max="6655" width="49.83203125" style="86"/>
+    <col min="6656" max="6656" width="6.08203125" style="86" customWidth="1"/>
+    <col min="6657" max="6657" width="22.08203125" style="86" customWidth="1"/>
     <col min="6658" max="6658" width="45.25" style="86" customWidth="1"/>
-    <col min="6659" max="6661" width="12.375" style="86" customWidth="1"/>
+    <col min="6659" max="6661" width="12.33203125" style="86" customWidth="1"/>
     <col min="6662" max="6662" width="15.75" style="86" customWidth="1"/>
-    <col min="6663" max="6911" width="49.875" style="86"/>
-    <col min="6912" max="6912" width="6.125" style="86" customWidth="1"/>
-    <col min="6913" max="6913" width="22.125" style="86" customWidth="1"/>
+    <col min="6663" max="6911" width="49.83203125" style="86"/>
+    <col min="6912" max="6912" width="6.08203125" style="86" customWidth="1"/>
+    <col min="6913" max="6913" width="22.08203125" style="86" customWidth="1"/>
     <col min="6914" max="6914" width="45.25" style="86" customWidth="1"/>
-    <col min="6915" max="6917" width="12.375" style="86" customWidth="1"/>
+    <col min="6915" max="6917" width="12.33203125" style="86" customWidth="1"/>
     <col min="6918" max="6918" width="15.75" style="86" customWidth="1"/>
-    <col min="6919" max="7167" width="49.875" style="86"/>
-    <col min="7168" max="7168" width="6.125" style="86" customWidth="1"/>
-    <col min="7169" max="7169" width="22.125" style="86" customWidth="1"/>
+    <col min="6919" max="7167" width="49.83203125" style="86"/>
+    <col min="7168" max="7168" width="6.08203125" style="86" customWidth="1"/>
+    <col min="7169" max="7169" width="22.08203125" style="86" customWidth="1"/>
     <col min="7170" max="7170" width="45.25" style="86" customWidth="1"/>
-    <col min="7171" max="7173" width="12.375" style="86" customWidth="1"/>
+    <col min="7171" max="7173" width="12.33203125" style="86" customWidth="1"/>
     <col min="7174" max="7174" width="15.75" style="86" customWidth="1"/>
-    <col min="7175" max="7423" width="49.875" style="86"/>
-    <col min="7424" max="7424" width="6.125" style="86" customWidth="1"/>
-    <col min="7425" max="7425" width="22.125" style="86" customWidth="1"/>
+    <col min="7175" max="7423" width="49.83203125" style="86"/>
+    <col min="7424" max="7424" width="6.08203125" style="86" customWidth="1"/>
+    <col min="7425" max="7425" width="22.08203125" style="86" customWidth="1"/>
     <col min="7426" max="7426" width="45.25" style="86" customWidth="1"/>
-    <col min="7427" max="7429" width="12.375" style="86" customWidth="1"/>
+    <col min="7427" max="7429" width="12.33203125" style="86" customWidth="1"/>
     <col min="7430" max="7430" width="15.75" style="86" customWidth="1"/>
-    <col min="7431" max="7679" width="49.875" style="86"/>
-    <col min="7680" max="7680" width="6.125" style="86" customWidth="1"/>
-    <col min="7681" max="7681" width="22.125" style="86" customWidth="1"/>
+    <col min="7431" max="7679" width="49.83203125" style="86"/>
+    <col min="7680" max="7680" width="6.08203125" style="86" customWidth="1"/>
+    <col min="7681" max="7681" width="22.08203125" style="86" customWidth="1"/>
     <col min="7682" max="7682" width="45.25" style="86" customWidth="1"/>
-    <col min="7683" max="7685" width="12.375" style="86" customWidth="1"/>
+    <col min="7683" max="7685" width="12.33203125" style="86" customWidth="1"/>
     <col min="7686" max="7686" width="15.75" style="86" customWidth="1"/>
-    <col min="7687" max="7935" width="49.875" style="86"/>
-    <col min="7936" max="7936" width="6.125" style="86" customWidth="1"/>
-    <col min="7937" max="7937" width="22.125" style="86" customWidth="1"/>
+    <col min="7687" max="7935" width="49.83203125" style="86"/>
+    <col min="7936" max="7936" width="6.08203125" style="86" customWidth="1"/>
+    <col min="7937" max="7937" width="22.08203125" style="86" customWidth="1"/>
     <col min="7938" max="7938" width="45.25" style="86" customWidth="1"/>
-    <col min="7939" max="7941" width="12.375" style="86" customWidth="1"/>
+    <col min="7939" max="7941" width="12.33203125" style="86" customWidth="1"/>
     <col min="7942" max="7942" width="15.75" style="86" customWidth="1"/>
-    <col min="7943" max="8191" width="49.875" style="86"/>
-    <col min="8192" max="8192" width="6.125" style="86" customWidth="1"/>
-    <col min="8193" max="8193" width="22.125" style="86" customWidth="1"/>
+    <col min="7943" max="8191" width="49.83203125" style="86"/>
+    <col min="8192" max="8192" width="6.08203125" style="86" customWidth="1"/>
+    <col min="8193" max="8193" width="22.08203125" style="86" customWidth="1"/>
     <col min="8194" max="8194" width="45.25" style="86" customWidth="1"/>
-    <col min="8195" max="8197" width="12.375" style="86" customWidth="1"/>
+    <col min="8195" max="8197" width="12.33203125" style="86" customWidth="1"/>
     <col min="8198" max="8198" width="15.75" style="86" customWidth="1"/>
-    <col min="8199" max="8447" width="49.875" style="86"/>
-    <col min="8448" max="8448" width="6.125" style="86" customWidth="1"/>
-    <col min="8449" max="8449" width="22.125" style="86" customWidth="1"/>
+    <col min="8199" max="8447" width="49.83203125" style="86"/>
+    <col min="8448" max="8448" width="6.08203125" style="86" customWidth="1"/>
+    <col min="8449" max="8449" width="22.08203125" style="86" customWidth="1"/>
     <col min="8450" max="8450" width="45.25" style="86" customWidth="1"/>
-    <col min="8451" max="8453" width="12.375" style="86" customWidth="1"/>
+    <col min="8451" max="8453" width="12.33203125" style="86" customWidth="1"/>
     <col min="8454" max="8454" width="15.75" style="86" customWidth="1"/>
-    <col min="8455" max="8703" width="49.875" style="86"/>
-    <col min="8704" max="8704" width="6.125" style="86" customWidth="1"/>
-    <col min="8705" max="8705" width="22.125" style="86" customWidth="1"/>
+    <col min="8455" max="8703" width="49.83203125" style="86"/>
+    <col min="8704" max="8704" width="6.08203125" style="86" customWidth="1"/>
+    <col min="8705" max="8705" width="22.08203125" style="86" customWidth="1"/>
     <col min="8706" max="8706" width="45.25" style="86" customWidth="1"/>
-    <col min="8707" max="8709" width="12.375" style="86" customWidth="1"/>
+    <col min="8707" max="8709" width="12.33203125" style="86" customWidth="1"/>
     <col min="8710" max="8710" width="15.75" style="86" customWidth="1"/>
-    <col min="8711" max="8959" width="49.875" style="86"/>
-    <col min="8960" max="8960" width="6.125" style="86" customWidth="1"/>
-    <col min="8961" max="8961" width="22.125" style="86" customWidth="1"/>
+    <col min="8711" max="8959" width="49.83203125" style="86"/>
+    <col min="8960" max="8960" width="6.08203125" style="86" customWidth="1"/>
+    <col min="8961" max="8961" width="22.08203125" style="86" customWidth="1"/>
     <col min="8962" max="8962" width="45.25" style="86" customWidth="1"/>
-    <col min="8963" max="8965" width="12.375" style="86" customWidth="1"/>
+    <col min="8963" max="8965" width="12.33203125" style="86" customWidth="1"/>
     <col min="8966" max="8966" width="15.75" style="86" customWidth="1"/>
-    <col min="8967" max="9215" width="49.875" style="86"/>
-    <col min="9216" max="9216" width="6.125" style="86" customWidth="1"/>
-    <col min="9217" max="9217" width="22.125" style="86" customWidth="1"/>
+    <col min="8967" max="9215" width="49.83203125" style="86"/>
+    <col min="9216" max="9216" width="6.08203125" style="86" customWidth="1"/>
+    <col min="9217" max="9217" width="22.08203125" style="86" customWidth="1"/>
     <col min="9218" max="9218" width="45.25" style="86" customWidth="1"/>
-    <col min="9219" max="9221" width="12.375" style="86" customWidth="1"/>
+    <col min="9219" max="9221" width="12.33203125" style="86" customWidth="1"/>
     <col min="9222" max="9222" width="15.75" style="86" customWidth="1"/>
-    <col min="9223" max="9471" width="49.875" style="86"/>
-    <col min="9472" max="9472" width="6.125" style="86" customWidth="1"/>
-    <col min="9473" max="9473" width="22.125" style="86" customWidth="1"/>
+    <col min="9223" max="9471" width="49.83203125" style="86"/>
+    <col min="9472" max="9472" width="6.08203125" style="86" customWidth="1"/>
+    <col min="9473" max="9473" width="22.08203125" style="86" customWidth="1"/>
     <col min="9474" max="9474" width="45.25" style="86" customWidth="1"/>
-    <col min="9475" max="9477" width="12.375" style="86" customWidth="1"/>
+    <col min="9475" max="9477" width="12.33203125" style="86" customWidth="1"/>
     <col min="9478" max="9478" width="15.75" style="86" customWidth="1"/>
-    <col min="9479" max="9727" width="49.875" style="86"/>
-    <col min="9728" max="9728" width="6.125" style="86" customWidth="1"/>
-    <col min="9729" max="9729" width="22.125" style="86" customWidth="1"/>
+    <col min="9479" max="9727" width="49.83203125" style="86"/>
+    <col min="9728" max="9728" width="6.08203125" style="86" customWidth="1"/>
+    <col min="9729" max="9729" width="22.08203125" style="86" customWidth="1"/>
     <col min="9730" max="9730" width="45.25" style="86" customWidth="1"/>
-    <col min="9731" max="9733" width="12.375" style="86" customWidth="1"/>
+    <col min="9731" max="9733" width="12.33203125" style="86" customWidth="1"/>
     <col min="9734" max="9734" width="15.75" style="86" customWidth="1"/>
-    <col min="9735" max="9983" width="49.875" style="86"/>
-    <col min="9984" max="9984" width="6.125" style="86" customWidth="1"/>
-    <col min="9985" max="9985" width="22.125" style="86" customWidth="1"/>
+    <col min="9735" max="9983" width="49.83203125" style="86"/>
+    <col min="9984" max="9984" width="6.08203125" style="86" customWidth="1"/>
+    <col min="9985" max="9985" width="22.08203125" style="86" customWidth="1"/>
     <col min="9986" max="9986" width="45.25" style="86" customWidth="1"/>
-    <col min="9987" max="9989" width="12.375" style="86" customWidth="1"/>
+    <col min="9987" max="9989" width="12.33203125" style="86" customWidth="1"/>
     <col min="9990" max="9990" width="15.75" style="86" customWidth="1"/>
-    <col min="9991" max="10239" width="49.875" style="86"/>
-    <col min="10240" max="10240" width="6.125" style="86" customWidth="1"/>
-    <col min="10241" max="10241" width="22.125" style="86" customWidth="1"/>
+    <col min="9991" max="10239" width="49.83203125" style="86"/>
+    <col min="10240" max="10240" width="6.08203125" style="86" customWidth="1"/>
+    <col min="10241" max="10241" width="22.08203125" style="86" customWidth="1"/>
     <col min="10242" max="10242" width="45.25" style="86" customWidth="1"/>
-    <col min="10243" max="10245" width="12.375" style="86" customWidth="1"/>
+    <col min="10243" max="10245" width="12.33203125" style="86" customWidth="1"/>
     <col min="10246" max="10246" width="15.75" style="86" customWidth="1"/>
-    <col min="10247" max="10495" width="49.875" style="86"/>
-    <col min="10496" max="10496" width="6.125" style="86" customWidth="1"/>
-    <col min="10497" max="10497" width="22.125" style="86" customWidth="1"/>
+    <col min="10247" max="10495" width="49.83203125" style="86"/>
+    <col min="10496" max="10496" width="6.08203125" style="86" customWidth="1"/>
+    <col min="10497" max="10497" width="22.08203125" style="86" customWidth="1"/>
     <col min="10498" max="10498" width="45.25" style="86" customWidth="1"/>
-    <col min="10499" max="10501" width="12.375" style="86" customWidth="1"/>
+    <col min="10499" max="10501" width="12.33203125" style="86" customWidth="1"/>
     <col min="10502" max="10502" width="15.75" style="86" customWidth="1"/>
-    <col min="10503" max="10751" width="49.875" style="86"/>
-    <col min="10752" max="10752" width="6.125" style="86" customWidth="1"/>
-    <col min="10753" max="10753" width="22.125" style="86" customWidth="1"/>
+    <col min="10503" max="10751" width="49.83203125" style="86"/>
+    <col min="10752" max="10752" width="6.08203125" style="86" customWidth="1"/>
+    <col min="10753" max="10753" width="22.08203125" style="86" customWidth="1"/>
     <col min="10754" max="10754" width="45.25" style="86" customWidth="1"/>
-    <col min="10755" max="10757" width="12.375" style="86" customWidth="1"/>
+    <col min="10755" max="10757" width="12.33203125" style="86" customWidth="1"/>
     <col min="10758" max="10758" width="15.75" style="86" customWidth="1"/>
-    <col min="10759" max="11007" width="49.875" style="86"/>
-    <col min="11008" max="11008" width="6.125" style="86" customWidth="1"/>
-    <col min="11009" max="11009" width="22.125" style="86" customWidth="1"/>
+    <col min="10759" max="11007" width="49.83203125" style="86"/>
+    <col min="11008" max="11008" width="6.08203125" style="86" customWidth="1"/>
+    <col min="11009" max="11009" width="22.08203125" style="86" customWidth="1"/>
     <col min="11010" max="11010" width="45.25" style="86" customWidth="1"/>
-    <col min="11011" max="11013" width="12.375" style="86" customWidth="1"/>
+    <col min="11011" max="11013" width="12.33203125" style="86" customWidth="1"/>
     <col min="11014" max="11014" width="15.75" style="86" customWidth="1"/>
-    <col min="11015" max="11263" width="49.875" style="86"/>
-    <col min="11264" max="11264" width="6.125" style="86" customWidth="1"/>
-    <col min="11265" max="11265" width="22.125" style="86" customWidth="1"/>
+    <col min="11015" max="11263" width="49.83203125" style="86"/>
+    <col min="11264" max="11264" width="6.08203125" style="86" customWidth="1"/>
+    <col min="11265" max="11265" width="22.08203125" style="86" customWidth="1"/>
     <col min="11266" max="11266" width="45.25" style="86" customWidth="1"/>
-    <col min="11267" max="11269" width="12.375" style="86" customWidth="1"/>
+    <col min="11267" max="11269" width="12.33203125" style="86" customWidth="1"/>
     <col min="11270" max="11270" width="15.75" style="86" customWidth="1"/>
-    <col min="11271" max="11519" width="49.875" style="86"/>
-    <col min="11520" max="11520" width="6.125" style="86" customWidth="1"/>
-    <col min="11521" max="11521" width="22.125" style="86" customWidth="1"/>
+    <col min="11271" max="11519" width="49.83203125" style="86"/>
+    <col min="11520" max="11520" width="6.08203125" style="86" customWidth="1"/>
+    <col min="11521" max="11521" width="22.08203125" style="86" customWidth="1"/>
     <col min="11522" max="11522" width="45.25" style="86" customWidth="1"/>
-    <col min="11523" max="11525" width="12.375" style="86" customWidth="1"/>
+    <col min="11523" max="11525" width="12.33203125" style="86" customWidth="1"/>
     <col min="11526" max="11526" width="15.75" style="86" customWidth="1"/>
-    <col min="11527" max="11775" width="49.875" style="86"/>
-    <col min="11776" max="11776" width="6.125" style="86" customWidth="1"/>
-    <col min="11777" max="11777" width="22.125" style="86" customWidth="1"/>
+    <col min="11527" max="11775" width="49.83203125" style="86"/>
+    <col min="11776" max="11776" width="6.08203125" style="86" customWidth="1"/>
+    <col min="11777" max="11777" width="22.08203125" style="86" customWidth="1"/>
     <col min="11778" max="11778" width="45.25" style="86" customWidth="1"/>
-    <col min="11779" max="11781" width="12.375" style="86" customWidth="1"/>
+    <col min="11779" max="11781" width="12.33203125" style="86" customWidth="1"/>
     <col min="11782" max="11782" width="15.75" style="86" customWidth="1"/>
-    <col min="11783" max="12031" width="49.875" style="86"/>
-    <col min="12032" max="12032" width="6.125" style="86" customWidth="1"/>
-    <col min="12033" max="12033" width="22.125" style="86" customWidth="1"/>
+    <col min="11783" max="12031" width="49.83203125" style="86"/>
+    <col min="12032" max="12032" width="6.08203125" style="86" customWidth="1"/>
+    <col min="12033" max="12033" width="22.08203125" style="86" customWidth="1"/>
     <col min="12034" max="12034" width="45.25" style="86" customWidth="1"/>
-    <col min="12035" max="12037" width="12.375" style="86" customWidth="1"/>
+    <col min="12035" max="12037" width="12.33203125" style="86" customWidth="1"/>
     <col min="12038" max="12038" width="15.75" style="86" customWidth="1"/>
-    <col min="12039" max="12287" width="49.875" style="86"/>
-    <col min="12288" max="12288" width="6.125" style="86" customWidth="1"/>
-    <col min="12289" max="12289" width="22.125" style="86" customWidth="1"/>
+    <col min="12039" max="12287" width="49.83203125" style="86"/>
+    <col min="12288" max="12288" width="6.08203125" style="86" customWidth="1"/>
+    <col min="12289" max="12289" width="22.08203125" style="86" customWidth="1"/>
     <col min="12290" max="12290" width="45.25" style="86" customWidth="1"/>
-    <col min="12291" max="12293" width="12.375" style="86" customWidth="1"/>
+    <col min="12291" max="12293" width="12.33203125" style="86" customWidth="1"/>
     <col min="12294" max="12294" width="15.75" style="86" customWidth="1"/>
-    <col min="12295" max="12543" width="49.875" style="86"/>
-    <col min="12544" max="12544" width="6.125" style="86" customWidth="1"/>
-    <col min="12545" max="12545" width="22.125" style="86" customWidth="1"/>
+    <col min="12295" max="12543" width="49.83203125" style="86"/>
+    <col min="12544" max="12544" width="6.08203125" style="86" customWidth="1"/>
+    <col min="12545" max="12545" width="22.08203125" style="86" customWidth="1"/>
     <col min="12546" max="12546" width="45.25" style="86" customWidth="1"/>
-    <col min="12547" max="12549" width="12.375" style="86" customWidth="1"/>
+    <col min="12547" max="12549" width="12.33203125" style="86" customWidth="1"/>
     <col min="12550" max="12550" width="15.75" style="86" customWidth="1"/>
-    <col min="12551" max="12799" width="49.875" style="86"/>
-    <col min="12800" max="12800" width="6.125" style="86" customWidth="1"/>
-    <col min="12801" max="12801" width="22.125" style="86" customWidth="1"/>
+    <col min="12551" max="12799" width="49.83203125" style="86"/>
+    <col min="12800" max="12800" width="6.08203125" style="86" customWidth="1"/>
+    <col min="12801" max="12801" width="22.08203125" style="86" customWidth="1"/>
     <col min="12802" max="12802" width="45.25" style="86" customWidth="1"/>
-    <col min="12803" max="12805" width="12.375" style="86" customWidth="1"/>
+    <col min="12803" max="12805" width="12.33203125" style="86" customWidth="1"/>
     <col min="12806" max="12806" width="15.75" style="86" customWidth="1"/>
-    <col min="12807" max="13055" width="49.875" style="86"/>
-    <col min="13056" max="13056" width="6.125" style="86" customWidth="1"/>
-    <col min="13057" max="13057" width="22.125" style="86" customWidth="1"/>
+    <col min="12807" max="13055" width="49.83203125" style="86"/>
+    <col min="13056" max="13056" width="6.08203125" style="86" customWidth="1"/>
+    <col min="13057" max="13057" width="22.08203125" style="86" customWidth="1"/>
     <col min="13058" max="13058" width="45.25" style="86" customWidth="1"/>
-    <col min="13059" max="13061" width="12.375" style="86" customWidth="1"/>
+    <col min="13059" max="13061" width="12.33203125" style="86" customWidth="1"/>
     <col min="13062" max="13062" width="15.75" style="86" customWidth="1"/>
-    <col min="13063" max="13311" width="49.875" style="86"/>
-    <col min="13312" max="13312" width="6.125" style="86" customWidth="1"/>
-    <col min="13313" max="13313" width="22.125" style="86" customWidth="1"/>
+    <col min="13063" max="13311" width="49.83203125" style="86"/>
+    <col min="13312" max="13312" width="6.08203125" style="86" customWidth="1"/>
+    <col min="13313" max="13313" width="22.08203125" style="86" customWidth="1"/>
     <col min="13314" max="13314" width="45.25" style="86" customWidth="1"/>
-    <col min="13315" max="13317" width="12.375" style="86" customWidth="1"/>
+    <col min="13315" max="13317" width="12.33203125" style="86" customWidth="1"/>
     <col min="13318" max="13318" width="15.75" style="86" customWidth="1"/>
-    <col min="13319" max="13567" width="49.875" style="86"/>
-    <col min="13568" max="13568" width="6.125" style="86" customWidth="1"/>
-    <col min="13569" max="13569" width="22.125" style="86" customWidth="1"/>
+    <col min="13319" max="13567" width="49.83203125" style="86"/>
+    <col min="13568" max="13568" width="6.08203125" style="86" customWidth="1"/>
+    <col min="13569" max="13569" width="22.08203125" style="86" customWidth="1"/>
     <col min="13570" max="13570" width="45.25" style="86" customWidth="1"/>
-    <col min="13571" max="13573" width="12.375" style="86" customWidth="1"/>
+    <col min="13571" max="13573" width="12.33203125" style="86" customWidth="1"/>
     <col min="13574" max="13574" width="15.75" style="86" customWidth="1"/>
-    <col min="13575" max="13823" width="49.875" style="86"/>
-    <col min="13824" max="13824" width="6.125" style="86" customWidth="1"/>
-    <col min="13825" max="13825" width="22.125" style="86" customWidth="1"/>
+    <col min="13575" max="13823" width="49.83203125" style="86"/>
+    <col min="13824" max="13824" width="6.08203125" style="86" customWidth="1"/>
+    <col min="13825" max="13825" width="22.08203125" style="86" customWidth="1"/>
     <col min="13826" max="13826" width="45.25" style="86" customWidth="1"/>
-    <col min="13827" max="13829" width="12.375" style="86" customWidth="1"/>
+    <col min="13827" max="13829" width="12.33203125" style="86" customWidth="1"/>
     <col min="13830" max="13830" width="15.75" style="86" customWidth="1"/>
-    <col min="13831" max="14079" width="49.875" style="86"/>
-    <col min="14080" max="14080" width="6.125" style="86" customWidth="1"/>
-    <col min="14081" max="14081" width="22.125" style="86" customWidth="1"/>
+    <col min="13831" max="14079" width="49.83203125" style="86"/>
+    <col min="14080" max="14080" width="6.08203125" style="86" customWidth="1"/>
+    <col min="14081" max="14081" width="22.08203125" style="86" customWidth="1"/>
     <col min="14082" max="14082" width="45.25" style="86" customWidth="1"/>
-    <col min="14083" max="14085" width="12.375" style="86" customWidth="1"/>
+    <col min="14083" max="14085" width="12.33203125" style="86" customWidth="1"/>
     <col min="14086" max="14086" width="15.75" style="86" customWidth="1"/>
-    <col min="14087" max="14335" width="49.875" style="86"/>
-    <col min="14336" max="14336" width="6.125" style="86" customWidth="1"/>
-    <col min="14337" max="14337" width="22.125" style="86" customWidth="1"/>
+    <col min="14087" max="14335" width="49.83203125" style="86"/>
+    <col min="14336" max="14336" width="6.08203125" style="86" customWidth="1"/>
+    <col min="14337" max="14337" width="22.08203125" style="86" customWidth="1"/>
     <col min="14338" max="14338" width="45.25" style="86" customWidth="1"/>
-    <col min="14339" max="14341" width="12.375" style="86" customWidth="1"/>
+    <col min="14339" max="14341" width="12.33203125" style="86" customWidth="1"/>
     <col min="14342" max="14342" width="15.75" style="86" customWidth="1"/>
-    <col min="14343" max="14591" width="49.875" style="86"/>
-    <col min="14592" max="14592" width="6.125" style="86" customWidth="1"/>
-    <col min="14593" max="14593" width="22.125" style="86" customWidth="1"/>
+    <col min="14343" max="14591" width="49.83203125" style="86"/>
+    <col min="14592" max="14592" width="6.08203125" style="86" customWidth="1"/>
+    <col min="14593" max="14593" width="22.08203125" style="86" customWidth="1"/>
     <col min="14594" max="14594" width="45.25" style="86" customWidth="1"/>
-    <col min="14595" max="14597" width="12.375" style="86" customWidth="1"/>
+    <col min="14595" max="14597" width="12.33203125" style="86" customWidth="1"/>
     <col min="14598" max="14598" width="15.75" style="86" customWidth="1"/>
-    <col min="14599" max="14847" width="49.875" style="86"/>
-    <col min="14848" max="14848" width="6.125" style="86" customWidth="1"/>
-    <col min="14849" max="14849" width="22.125" style="86" customWidth="1"/>
+    <col min="14599" max="14847" width="49.83203125" style="86"/>
+    <col min="14848" max="14848" width="6.08203125" style="86" customWidth="1"/>
+    <col min="14849" max="14849" width="22.08203125" style="86" customWidth="1"/>
     <col min="14850" max="14850" width="45.25" style="86" customWidth="1"/>
-    <col min="14851" max="14853" width="12.375" style="86" customWidth="1"/>
+    <col min="14851" max="14853" width="12.33203125" style="86" customWidth="1"/>
     <col min="14854" max="14854" width="15.75" style="86" customWidth="1"/>
-    <col min="14855" max="15103" width="49.875" style="86"/>
-    <col min="15104" max="15104" width="6.125" style="86" customWidth="1"/>
-    <col min="15105" max="15105" width="22.125" style="86" customWidth="1"/>
+    <col min="14855" max="15103" width="49.83203125" style="86"/>
+    <col min="15104" max="15104" width="6.08203125" style="86" customWidth="1"/>
+    <col min="15105" max="15105" width="22.08203125" style="86" customWidth="1"/>
     <col min="15106" max="15106" width="45.25" style="86" customWidth="1"/>
-    <col min="15107" max="15109" width="12.375" style="86" customWidth="1"/>
+    <col min="15107" max="15109" width="12.33203125" style="86" customWidth="1"/>
     <col min="15110" max="15110" width="15.75" style="86" customWidth="1"/>
-    <col min="15111" max="15359" width="49.875" style="86"/>
-    <col min="15360" max="15360" width="6.125" style="86" customWidth="1"/>
-    <col min="15361" max="15361" width="22.125" style="86" customWidth="1"/>
+    <col min="15111" max="15359" width="49.83203125" style="86"/>
+    <col min="15360" max="15360" width="6.08203125" style="86" customWidth="1"/>
+    <col min="15361" max="15361" width="22.08203125" style="86" customWidth="1"/>
     <col min="15362" max="15362" width="45.25" style="86" customWidth="1"/>
-    <col min="15363" max="15365" width="12.375" style="86" customWidth="1"/>
+    <col min="15363" max="15365" width="12.33203125" style="86" customWidth="1"/>
     <col min="15366" max="15366" width="15.75" style="86" customWidth="1"/>
-    <col min="15367" max="15615" width="49.875" style="86"/>
-    <col min="15616" max="15616" width="6.125" style="86" customWidth="1"/>
-    <col min="15617" max="15617" width="22.125" style="86" customWidth="1"/>
+    <col min="15367" max="15615" width="49.83203125" style="86"/>
+    <col min="15616" max="15616" width="6.08203125" style="86" customWidth="1"/>
+    <col min="15617" max="15617" width="22.08203125" style="86" customWidth="1"/>
     <col min="15618" max="15618" width="45.25" style="86" customWidth="1"/>
-    <col min="15619" max="15621" width="12.375" style="86" customWidth="1"/>
+    <col min="15619" max="15621" width="12.33203125" style="86" customWidth="1"/>
     <col min="15622" max="15622" width="15.75" style="86" customWidth="1"/>
-    <col min="15623" max="15871" width="49.875" style="86"/>
-    <col min="15872" max="15872" width="6.125" style="86" customWidth="1"/>
-    <col min="15873" max="15873" width="22.125" style="86" customWidth="1"/>
+    <col min="15623" max="15871" width="49.83203125" style="86"/>
+    <col min="15872" max="15872" width="6.08203125" style="86" customWidth="1"/>
+    <col min="15873" max="15873" width="22.08203125" style="86" customWidth="1"/>
     <col min="15874" max="15874" width="45.25" style="86" customWidth="1"/>
-    <col min="15875" max="15877" width="12.375" style="86" customWidth="1"/>
+    <col min="15875" max="15877" width="12.33203125" style="86" customWidth="1"/>
     <col min="15878" max="15878" width="15.75" style="86" customWidth="1"/>
-    <col min="15879" max="16127" width="49.875" style="86"/>
-    <col min="16128" max="16128" width="6.125" style="86" customWidth="1"/>
-    <col min="16129" max="16129" width="22.125" style="86" customWidth="1"/>
+    <col min="15879" max="16127" width="49.83203125" style="86"/>
+    <col min="16128" max="16128" width="6.08203125" style="86" customWidth="1"/>
+    <col min="16129" max="16129" width="22.08203125" style="86" customWidth="1"/>
     <col min="16130" max="16130" width="45.25" style="86" customWidth="1"/>
-    <col min="16131" max="16133" width="12.375" style="86" customWidth="1"/>
+    <col min="16131" max="16133" width="12.33203125" style="86" customWidth="1"/>
     <col min="16134" max="16134" width="15.75" style="86" customWidth="1"/>
-    <col min="16135" max="16384" width="49.875" style="86"/>
+    <col min="16135" max="16384" width="49.83203125" style="86"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A1" s="323" t="s">
+      <c r="A1" s="349" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="323"/>
-      <c r="C1" s="323"/>
-      <c r="D1" s="323"/>
-      <c r="E1" s="323"/>
-      <c r="F1" s="323"/>
+      <c r="B1" s="349"/>
+      <c r="C1" s="349"/>
+      <c r="D1" s="349"/>
+      <c r="E1" s="349"/>
+      <c r="F1" s="349"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A2" s="323" t="s">
+      <c r="A2" s="349" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="323"/>
-      <c r="C2" s="323"/>
-      <c r="D2" s="323"/>
-      <c r="E2" s="323"/>
-      <c r="F2" s="323"/>
+      <c r="B2" s="349"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
     </row>
     <row r="3" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A3" s="323" t="s">
+      <c r="A3" s="349" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="323"/>
-      <c r="C3" s="323"/>
-      <c r="D3" s="323"/>
-      <c r="E3" s="323"/>
-      <c r="F3" s="323"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
     </row>
     <row r="4" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A4" s="323" t="s">
+      <c r="A4" s="349" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="323"/>
-      <c r="C4" s="323"/>
-      <c r="D4" s="323"/>
-      <c r="E4" s="323"/>
-      <c r="F4" s="323"/>
-    </row>
-    <row r="5" spans="1:7" ht="15">
+      <c r="B4" s="349"/>
+      <c r="C4" s="349"/>
+      <c r="D4" s="349"/>
+      <c r="E4" s="349"/>
+      <c r="F4" s="349"/>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="87"/>
       <c r="B5" s="88"/>
       <c r="C5" s="89"/>
     </row>
     <row r="6" spans="1:7" ht="26.25" customHeight="1">
-      <c r="A6" s="324" t="s">
+      <c r="A6" s="350" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="325"/>
-      <c r="C6" s="325"/>
-      <c r="D6" s="325"/>
-      <c r="E6" s="325"/>
-      <c r="F6" s="325"/>
+      <c r="B6" s="351"/>
+      <c r="C6" s="351"/>
+      <c r="D6" s="351"/>
+      <c r="E6" s="351"/>
+      <c r="F6" s="351"/>
     </row>
     <row r="7" spans="1:7" s="91" customFormat="1" ht="25.5" customHeight="1">
       <c r="A7" s="90"/>
-      <c r="B7" s="322" t="s">
+      <c r="B7" s="348" t="s">
         <v>141</v>
       </c>
-      <c r="C7" s="322"/>
-      <c r="D7" s="322"/>
-      <c r="E7" s="322"/>
-      <c r="F7" s="322"/>
+      <c r="C7" s="348"/>
+      <c r="D7" s="348"/>
+      <c r="E7" s="348"/>
+      <c r="F7" s="348"/>
     </row>
     <row r="8" spans="1:7" s="91" customFormat="1" ht="49.5" customHeight="1">
-      <c r="A8" s="301" t="s">
+      <c r="A8" s="357" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="302"/>
-      <c r="C8" s="302"/>
-      <c r="D8" s="302"/>
-      <c r="E8" s="302"/>
-      <c r="F8" s="302"/>
-    </row>
-    <row r="9" spans="1:7" s="93" customFormat="1" ht="47.25">
+      <c r="B8" s="358"/>
+      <c r="C8" s="358"/>
+      <c r="D8" s="358"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
+    </row>
+    <row r="9" spans="1:7" s="93" customFormat="1" ht="46.5">
       <c r="A9" s="92" t="s">
         <v>3</v>
       </c>
@@ -6993,102 +6993,102 @@
       </c>
     </row>
     <row r="10" spans="1:7" s="91" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A10" s="293" t="s">
+      <c r="A10" s="368" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="294"/>
-      <c r="C10" s="294"/>
-      <c r="D10" s="294"/>
-      <c r="E10" s="294"/>
-      <c r="F10" s="295"/>
-    </row>
-    <row r="11" spans="1:7" s="95" customFormat="1" ht="45">
-      <c r="A11" s="303">
+      <c r="B10" s="369"/>
+      <c r="C10" s="369"/>
+      <c r="D10" s="369"/>
+      <c r="E10" s="369"/>
+      <c r="F10" s="370"/>
+    </row>
+    <row r="11" spans="1:7" s="95" customFormat="1" ht="46.5">
+      <c r="A11" s="359">
         <v>1</v>
       </c>
-      <c r="B11" s="303" t="s">
+      <c r="B11" s="359" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="303">
+      <c r="D11" s="359">
         <v>214</v>
       </c>
-      <c r="E11" s="306">
+      <c r="E11" s="362">
         <v>230000</v>
       </c>
-      <c r="F11" s="309">
+      <c r="F11" s="365">
         <f>E11*D11</f>
         <v>49220000</v>
       </c>
-      <c r="G11" s="289"/>
-    </row>
-    <row r="12" spans="1:7" s="95" customFormat="1" ht="15">
-      <c r="A12" s="304"/>
-      <c r="B12" s="304"/>
+      <c r="G11" s="381"/>
+    </row>
+    <row r="12" spans="1:7" s="95" customFormat="1" ht="31">
+      <c r="A12" s="360"/>
+      <c r="B12" s="360"/>
       <c r="C12" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="304"/>
-      <c r="E12" s="307"/>
-      <c r="F12" s="310"/>
-      <c r="G12" s="290"/>
-    </row>
-    <row r="13" spans="1:7" s="95" customFormat="1" ht="30">
-      <c r="A13" s="304"/>
-      <c r="B13" s="304"/>
+      <c r="D12" s="360"/>
+      <c r="E12" s="363"/>
+      <c r="F12" s="366"/>
+      <c r="G12" s="382"/>
+    </row>
+    <row r="13" spans="1:7" s="95" customFormat="1" ht="46.5">
+      <c r="A13" s="360"/>
+      <c r="B13" s="360"/>
       <c r="C13" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="304"/>
-      <c r="E13" s="307"/>
-      <c r="F13" s="310"/>
-      <c r="G13" s="290"/>
-    </row>
-    <row r="14" spans="1:7" s="95" customFormat="1" ht="30">
-      <c r="A14" s="304"/>
-      <c r="B14" s="304"/>
+      <c r="D13" s="360"/>
+      <c r="E13" s="363"/>
+      <c r="F13" s="366"/>
+      <c r="G13" s="382"/>
+    </row>
+    <row r="14" spans="1:7" s="95" customFormat="1" ht="31">
+      <c r="A14" s="360"/>
+      <c r="B14" s="360"/>
       <c r="C14" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="304"/>
-      <c r="E14" s="307"/>
-      <c r="F14" s="310"/>
-      <c r="G14" s="290"/>
-    </row>
-    <row r="15" spans="1:7" s="95" customFormat="1" ht="15">
-      <c r="A15" s="304"/>
-      <c r="B15" s="304"/>
+      <c r="D14" s="360"/>
+      <c r="E14" s="363"/>
+      <c r="F14" s="366"/>
+      <c r="G14" s="382"/>
+    </row>
+    <row r="15" spans="1:7" s="95" customFormat="1" ht="15.5">
+      <c r="A15" s="360"/>
+      <c r="B15" s="360"/>
       <c r="C15" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="304"/>
-      <c r="E15" s="307"/>
-      <c r="F15" s="310"/>
-      <c r="G15" s="290"/>
-    </row>
-    <row r="16" spans="1:7" s="95" customFormat="1" ht="15">
-      <c r="A16" s="304"/>
-      <c r="B16" s="304"/>
+      <c r="D15" s="360"/>
+      <c r="E15" s="363"/>
+      <c r="F15" s="366"/>
+      <c r="G15" s="382"/>
+    </row>
+    <row r="16" spans="1:7" s="95" customFormat="1" ht="15.5">
+      <c r="A16" s="360"/>
+      <c r="B16" s="360"/>
       <c r="C16" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="304"/>
-      <c r="E16" s="307"/>
-      <c r="F16" s="310"/>
-      <c r="G16" s="290"/>
-    </row>
-    <row r="17" spans="1:7" s="95" customFormat="1" ht="15">
-      <c r="A17" s="305"/>
-      <c r="B17" s="305"/>
+      <c r="D16" s="360"/>
+      <c r="E16" s="363"/>
+      <c r="F16" s="366"/>
+      <c r="G16" s="382"/>
+    </row>
+    <row r="17" spans="1:7" s="95" customFormat="1" ht="15.5">
+      <c r="A17" s="361"/>
+      <c r="B17" s="361"/>
       <c r="C17" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="305"/>
-      <c r="E17" s="308"/>
-      <c r="F17" s="311"/>
-      <c r="G17" s="290"/>
+      <c r="D17" s="361"/>
+      <c r="E17" s="364"/>
+      <c r="F17" s="367"/>
+      <c r="G17" s="382"/>
     </row>
     <row r="18" spans="1:7" s="95" customFormat="1" ht="27" customHeight="1">
       <c r="A18" s="96">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="G18" s="97"/>
     </row>
-    <row r="19" spans="1:7" s="95" customFormat="1" ht="45">
+    <row r="19" spans="1:7" s="95" customFormat="1" ht="46.5">
       <c r="A19" s="96">
         <v>3</v>
       </c>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="G19" s="97"/>
     </row>
-    <row r="20" spans="1:7" s="95" customFormat="1" ht="30">
+    <row r="20" spans="1:7" s="95" customFormat="1" ht="31">
       <c r="A20" s="96">
         <v>4</v>
       </c>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="G20" s="97"/>
     </row>
-    <row r="21" spans="1:7" s="95" customFormat="1" ht="30">
+    <row r="21" spans="1:7" s="95" customFormat="1" ht="31">
       <c r="A21" s="96">
         <v>5</v>
       </c>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="G21" s="97"/>
     </row>
-    <row r="22" spans="1:7" s="95" customFormat="1" ht="15.75">
+    <row r="22" spans="1:7" s="95" customFormat="1" ht="15.5">
       <c r="A22" s="96">
         <v>6</v>
       </c>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G22" s="97"/>
     </row>
-    <row r="23" spans="1:7" s="95" customFormat="1" ht="15.75">
+    <row r="23" spans="1:7" s="95" customFormat="1" ht="15.5">
       <c r="A23" s="96">
         <v>7</v>
       </c>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="G23" s="97"/>
     </row>
-    <row r="24" spans="1:7" s="95" customFormat="1" ht="15.75">
+    <row r="24" spans="1:7" s="95" customFormat="1" ht="15.5">
       <c r="A24" s="96">
         <v>8</v>
       </c>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="G24" s="97"/>
     </row>
-    <row r="25" spans="1:7" s="95" customFormat="1" ht="15.75">
+    <row r="25" spans="1:7" s="95" customFormat="1" ht="15.5">
       <c r="A25" s="96">
         <v>9</v>
       </c>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="G25" s="97"/>
     </row>
-    <row r="26" spans="1:7" s="95" customFormat="1" ht="15.75">
+    <row r="26" spans="1:7" s="95" customFormat="1" ht="15.5">
       <c r="A26" s="96">
         <v>10</v>
       </c>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="G26" s="97"/>
     </row>
-    <row r="27" spans="1:7" s="95" customFormat="1" ht="15.75">
+    <row r="27" spans="1:7" s="95" customFormat="1" ht="15.5">
       <c r="A27" s="96">
         <v>11</v>
       </c>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="G27" s="97"/>
     </row>
-    <row r="28" spans="1:7" s="95" customFormat="1" ht="15.75">
+    <row r="28" spans="1:7" s="95" customFormat="1" ht="15.5">
       <c r="A28" s="96">
         <v>12</v>
       </c>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="G28" s="97"/>
     </row>
-    <row r="29" spans="1:7" s="95" customFormat="1" ht="45">
+    <row r="29" spans="1:7" s="95" customFormat="1" ht="46.5">
       <c r="A29" s="96">
         <v>13</v>
       </c>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="G29" s="97"/>
     </row>
-    <row r="30" spans="1:7" s="95" customFormat="1" ht="15.75">
+    <row r="30" spans="1:7" s="95" customFormat="1" ht="15.5">
       <c r="A30" s="96">
         <v>14</v>
       </c>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="G30" s="97"/>
     </row>
-    <row r="31" spans="1:7" s="95" customFormat="1" ht="15.75">
-      <c r="A31" s="291" t="s">
+    <row r="31" spans="1:7" s="95" customFormat="1" ht="15.5">
+      <c r="A31" s="383" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="292"/>
-      <c r="C31" s="292"/>
+      <c r="B31" s="384"/>
+      <c r="C31" s="384"/>
       <c r="D31" s="101"/>
       <c r="E31" s="102">
         <f>SUM(E11:E30)</f>
@@ -7394,16 +7394,16 @@
       <c r="G31" s="97"/>
     </row>
     <row r="32" spans="1:7" s="91" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A32" s="293" t="s">
+      <c r="A32" s="368" t="s">
         <v>90</v>
       </c>
-      <c r="B32" s="294"/>
-      <c r="C32" s="294"/>
-      <c r="D32" s="294"/>
-      <c r="E32" s="294"/>
-      <c r="F32" s="295"/>
-    </row>
-    <row r="33" spans="1:7" s="93" customFormat="1" ht="15.75">
+      <c r="B32" s="369"/>
+      <c r="C32" s="369"/>
+      <c r="D32" s="369"/>
+      <c r="E32" s="369"/>
+      <c r="F32" s="370"/>
+    </row>
+    <row r="33" spans="1:7" s="93" customFormat="1" ht="15.5">
       <c r="A33" s="104">
         <v>15</v>
       </c>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="G33" s="106"/>
     </row>
-    <row r="34" spans="1:7" s="93" customFormat="1" ht="30">
+    <row r="34" spans="1:7" s="93" customFormat="1" ht="31">
       <c r="A34" s="104">
         <v>16</v>
       </c>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="G35" s="106"/>
     </row>
-    <row r="36" spans="1:7" s="93" customFormat="1" ht="15.75">
+    <row r="36" spans="1:7" s="93" customFormat="1" ht="15.5">
       <c r="A36" s="104">
         <v>18</v>
       </c>
@@ -7492,11 +7492,11 @@
       <c r="G36" s="106"/>
     </row>
     <row r="37" spans="1:7" s="95" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A37" s="291" t="s">
+      <c r="A37" s="383" t="s">
         <v>127</v>
       </c>
-      <c r="B37" s="292"/>
-      <c r="C37" s="292"/>
+      <c r="B37" s="384"/>
+      <c r="C37" s="384"/>
       <c r="D37" s="101"/>
       <c r="E37" s="102">
         <f>SUM(E33:E36)</f>
@@ -7509,16 +7509,16 @@
       <c r="G37" s="97"/>
     </row>
     <row r="38" spans="1:7" s="91" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A38" s="293" t="s">
+      <c r="A38" s="368" t="s">
         <v>134</v>
       </c>
-      <c r="B38" s="294"/>
-      <c r="C38" s="294"/>
-      <c r="D38" s="294"/>
-      <c r="E38" s="294"/>
-      <c r="F38" s="295"/>
-    </row>
-    <row r="39" spans="1:7" s="93" customFormat="1" ht="30">
+      <c r="B38" s="369"/>
+      <c r="C38" s="369"/>
+      <c r="D38" s="369"/>
+      <c r="E38" s="369"/>
+      <c r="F38" s="370"/>
+    </row>
+    <row r="39" spans="1:7" s="93" customFormat="1" ht="31">
       <c r="A39" s="104">
         <v>19</v>
       </c>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="G39" s="106"/>
     </row>
-    <row r="40" spans="1:7" s="95" customFormat="1" ht="15.75">
+    <row r="40" spans="1:7" s="95" customFormat="1" ht="15.5">
       <c r="A40" s="104">
         <v>20</v>
       </c>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="G40" s="106"/>
     </row>
-    <row r="41" spans="1:7" s="95" customFormat="1" ht="15.75">
+    <row r="41" spans="1:7" s="95" customFormat="1" ht="15.5">
       <c r="A41" s="104">
         <v>21</v>
       </c>
@@ -7584,7 +7584,7 @@
       </c>
       <c r="G41" s="106"/>
     </row>
-    <row r="42" spans="1:7" s="95" customFormat="1" ht="15.75">
+    <row r="42" spans="1:7" s="95" customFormat="1" ht="15.5">
       <c r="A42" s="104">
         <v>22</v>
       </c>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="G43" s="106"/>
     </row>
-    <row r="44" spans="1:7" s="95" customFormat="1" ht="15.75">
+    <row r="44" spans="1:7" s="95" customFormat="1" ht="15.5">
       <c r="A44" s="104">
         <v>24</v>
       </c>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="G44" s="106"/>
     </row>
-    <row r="45" spans="1:7" s="95" customFormat="1" ht="15.75">
+    <row r="45" spans="1:7" s="95" customFormat="1" ht="15.5">
       <c r="A45" s="104">
         <v>25</v>
       </c>
@@ -7673,11 +7673,11 @@
       <c r="G45" s="106"/>
     </row>
     <row r="46" spans="1:7" s="95" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A46" s="291" t="s">
+      <c r="A46" s="383" t="s">
         <v>127</v>
       </c>
-      <c r="B46" s="292"/>
-      <c r="C46" s="292"/>
+      <c r="B46" s="384"/>
+      <c r="C46" s="384"/>
       <c r="D46" s="101"/>
       <c r="E46" s="102">
         <f>SUM(E39:E45)</f>
@@ -7690,16 +7690,16 @@
       <c r="G46" s="97"/>
     </row>
     <row r="47" spans="1:7" s="91" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A47" s="293" t="s">
+      <c r="A47" s="368" t="s">
         <v>110</v>
       </c>
-      <c r="B47" s="294"/>
-      <c r="C47" s="294"/>
-      <c r="D47" s="294"/>
-      <c r="E47" s="294"/>
-      <c r="F47" s="295"/>
-    </row>
-    <row r="48" spans="1:7" s="95" customFormat="1" ht="45">
+      <c r="B47" s="369"/>
+      <c r="C47" s="369"/>
+      <c r="D47" s="369"/>
+      <c r="E47" s="369"/>
+      <c r="F47" s="370"/>
+    </row>
+    <row r="48" spans="1:7" s="95" customFormat="1" ht="46.5">
       <c r="A48" s="96">
         <v>26</v>
       </c>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="G48" s="106"/>
     </row>
-    <row r="49" spans="1:7" s="93" customFormat="1" ht="15.75">
+    <row r="49" spans="1:7" s="93" customFormat="1" ht="15.5">
       <c r="A49" s="96">
         <v>27</v>
       </c>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G49" s="106"/>
     </row>
-    <row r="50" spans="1:7" s="93" customFormat="1" ht="15.75">
+    <row r="50" spans="1:7" s="93" customFormat="1" ht="15.5">
       <c r="A50" s="96">
         <v>28</v>
       </c>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="G50" s="106"/>
     </row>
-    <row r="51" spans="1:7" s="93" customFormat="1" ht="15.75">
+    <row r="51" spans="1:7" s="93" customFormat="1" ht="15.5">
       <c r="A51" s="96">
         <v>29</v>
       </c>
@@ -7782,11 +7782,11 @@
       <c r="G51" s="106"/>
     </row>
     <row r="52" spans="1:7" s="95" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A52" s="291" t="s">
+      <c r="A52" s="383" t="s">
         <v>127</v>
       </c>
-      <c r="B52" s="292"/>
-      <c r="C52" s="292"/>
+      <c r="B52" s="384"/>
+      <c r="C52" s="384"/>
       <c r="D52" s="110"/>
       <c r="E52" s="102">
         <f>SUM(E48:E51)</f>
@@ -7799,13 +7799,13 @@
       <c r="G52" s="97"/>
     </row>
     <row r="53" spans="1:7" s="111" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A53" s="319" t="s">
+      <c r="A53" s="378" t="s">
         <v>32</v>
       </c>
-      <c r="B53" s="320"/>
-      <c r="C53" s="320"/>
-      <c r="D53" s="320"/>
-      <c r="E53" s="321"/>
+      <c r="B53" s="379"/>
+      <c r="C53" s="379"/>
+      <c r="D53" s="379"/>
+      <c r="E53" s="380"/>
       <c r="F53" s="129">
         <f>SUM(F52,F46,F37,F31)</f>
         <v>586100000</v>
@@ -7814,11 +7814,11 @@
     <row r="54" spans="1:7" s="93" customFormat="1" ht="16.5">
       <c r="A54" s="112"/>
       <c r="B54" s="112"/>
-      <c r="D54" s="312" t="s">
+      <c r="D54" s="371" t="s">
         <v>143</v>
       </c>
-      <c r="E54" s="312"/>
-      <c r="F54" s="312"/>
+      <c r="E54" s="371"/>
+      <c r="F54" s="371"/>
     </row>
     <row r="55" spans="1:7" s="93" customFormat="1" ht="16.5">
       <c r="A55" s="112"/>
@@ -7888,85 +7888,86 @@
       <c r="A63" s="112"/>
       <c r="B63" s="112"/>
       <c r="C63" s="112"/>
-      <c r="D63" s="313"/>
-      <c r="E63" s="313"/>
-      <c r="F63" s="313"/>
-    </row>
-    <row r="64" spans="1:7" s="91" customFormat="1" ht="15.75">
-      <c r="A64" s="314" t="s">
+      <c r="D63" s="372"/>
+      <c r="E63" s="372"/>
+      <c r="F63" s="372"/>
+    </row>
+    <row r="64" spans="1:7" s="91" customFormat="1" ht="15.5">
+      <c r="A64" s="373" t="s">
         <v>35</v>
       </c>
-      <c r="B64" s="315"/>
+      <c r="B64" s="374"/>
       <c r="C64" s="113"/>
     </row>
-    <row r="65" spans="1:3" s="114" customFormat="1" ht="15">
-      <c r="A65" s="316" t="s">
+    <row r="65" spans="1:3" s="114" customFormat="1" ht="15.5">
+      <c r="A65" s="375" t="s">
         <v>63</v>
       </c>
-      <c r="B65" s="317"/>
-      <c r="C65" s="318"/>
+      <c r="B65" s="376"/>
+      <c r="C65" s="377"/>
     </row>
     <row r="66" spans="1:3" s="114" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A66" s="316" t="s">
+      <c r="A66" s="375" t="s">
         <v>64</v>
       </c>
-      <c r="B66" s="317"/>
-      <c r="C66" s="318"/>
+      <c r="B66" s="376"/>
+      <c r="C66" s="377"/>
     </row>
     <row r="67" spans="1:3" s="114" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A67" s="296" t="s">
+      <c r="A67" s="352" t="s">
         <v>42</v>
       </c>
-      <c r="B67" s="297"/>
-      <c r="C67" s="298"/>
-    </row>
-    <row r="68" spans="1:3" s="91" customFormat="1" ht="15">
-      <c r="A68" s="299"/>
-      <c r="B68" s="300"/>
-      <c r="C68" s="300"/>
-    </row>
-    <row r="69" spans="1:3" s="91" customFormat="1" ht="15"/>
-    <row r="70" spans="1:3" s="91" customFormat="1" ht="15"/>
-    <row r="71" spans="1:3" s="91" customFormat="1" ht="15"/>
-    <row r="72" spans="1:3" s="91" customFormat="1" ht="15"/>
-    <row r="73" spans="1:3" s="91" customFormat="1" ht="15"/>
-    <row r="74" spans="1:3" s="91" customFormat="1" ht="15"/>
-    <row r="75" spans="1:3" s="91" customFormat="1" ht="15"/>
-    <row r="76" spans="1:3" s="91" customFormat="1" ht="15"/>
-    <row r="77" spans="1:3" s="91" customFormat="1" ht="15"/>
-    <row r="78" spans="1:3" s="91" customFormat="1" ht="15"/>
-    <row r="79" spans="1:3" s="91" customFormat="1" ht="15"/>
-    <row r="80" spans="1:3" s="91" customFormat="1" ht="15"/>
-    <row r="81" s="91" customFormat="1" ht="15"/>
-    <row r="82" s="91" customFormat="1" ht="15"/>
-    <row r="83" s="91" customFormat="1" ht="15"/>
-    <row r="84" s="91" customFormat="1" ht="15"/>
-    <row r="85" s="91" customFormat="1" ht="15"/>
-    <row r="86" s="91" customFormat="1" ht="15"/>
-    <row r="87" s="91" customFormat="1" ht="15"/>
-    <row r="88" s="91" customFormat="1" ht="15"/>
-    <row r="89" s="91" customFormat="1" ht="15"/>
-    <row r="90" s="91" customFormat="1" ht="15"/>
-    <row r="91" s="91" customFormat="1" ht="15"/>
-    <row r="92" s="91" customFormat="1" ht="15"/>
-    <row r="93" s="91" customFormat="1" ht="15"/>
-    <row r="94" s="91" customFormat="1" ht="15"/>
-    <row r="95" s="91" customFormat="1" ht="15"/>
-    <row r="96" s="91" customFormat="1" ht="15"/>
-    <row r="97" s="91" customFormat="1" ht="15"/>
-    <row r="98" s="91" customFormat="1" ht="15"/>
-    <row r="99" s="91" customFormat="1" ht="15"/>
-    <row r="100" s="91" customFormat="1" ht="15"/>
-    <row r="101" s="91" customFormat="1" ht="15"/>
-    <row r="102" s="91" customFormat="1" ht="15"/>
+      <c r="B67" s="353"/>
+      <c r="C67" s="354"/>
+    </row>
+    <row r="68" spans="1:3" s="91" customFormat="1" ht="15.5">
+      <c r="A68" s="355"/>
+      <c r="B68" s="356"/>
+      <c r="C68" s="356"/>
+    </row>
+    <row r="69" spans="1:3" s="91" customFormat="1" ht="15.5"/>
+    <row r="70" spans="1:3" s="91" customFormat="1" ht="15.5"/>
+    <row r="71" spans="1:3" s="91" customFormat="1" ht="15.5"/>
+    <row r="72" spans="1:3" s="91" customFormat="1" ht="15.5"/>
+    <row r="73" spans="1:3" s="91" customFormat="1" ht="15.5"/>
+    <row r="74" spans="1:3" s="91" customFormat="1" ht="15.5"/>
+    <row r="75" spans="1:3" s="91" customFormat="1" ht="15.5"/>
+    <row r="76" spans="1:3" s="91" customFormat="1" ht="15.5"/>
+    <row r="77" spans="1:3" s="91" customFormat="1" ht="15.5"/>
+    <row r="78" spans="1:3" s="91" customFormat="1" ht="15.5"/>
+    <row r="79" spans="1:3" s="91" customFormat="1" ht="15.5"/>
+    <row r="80" spans="1:3" s="91" customFormat="1" ht="15.5"/>
+    <row r="81" s="91" customFormat="1" ht="15.5"/>
+    <row r="82" s="91" customFormat="1" ht="15.5"/>
+    <row r="83" s="91" customFormat="1" ht="15.5"/>
+    <row r="84" s="91" customFormat="1" ht="15.5"/>
+    <row r="85" s="91" customFormat="1" ht="15.5"/>
+    <row r="86" s="91" customFormat="1" ht="15.5"/>
+    <row r="87" s="91" customFormat="1" ht="15.5"/>
+    <row r="88" s="91" customFormat="1" ht="15.5"/>
+    <row r="89" s="91" customFormat="1" ht="15.5"/>
+    <row r="90" s="91" customFormat="1" ht="15.5"/>
+    <row r="91" s="91" customFormat="1" ht="15.5"/>
+    <row r="92" s="91" customFormat="1" ht="15.5"/>
+    <row r="93" s="91" customFormat="1" ht="15.5"/>
+    <row r="94" s="91" customFormat="1" ht="15.5"/>
+    <row r="95" s="91" customFormat="1" ht="15.5"/>
+    <row r="96" s="91" customFormat="1" ht="15.5"/>
+    <row r="97" s="91" customFormat="1" ht="15.5"/>
+    <row r="98" s="91" customFormat="1" ht="15.5"/>
+    <row r="99" s="91" customFormat="1" ht="15.5"/>
+    <row r="100" s="91" customFormat="1" ht="15.5"/>
+    <row r="101" s="91" customFormat="1" ht="15.5"/>
+    <row r="102" s="91" customFormat="1" ht="15.5"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G11:G17"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A67:C67"/>
     <mergeCell ref="A68:C68"/>
     <mergeCell ref="A8:F8"/>
@@ -7983,13 +7984,12 @@
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="A53:E53"/>
-    <mergeCell ref="G11:G17"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.74803149606299213" right="0.31496062992125984" top="0.51181102362204722" bottom="0.31496062992125984" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="67" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -8003,713 +8003,713 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H69"/>
-  <sheetFormatPr defaultColWidth="13.375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="13.33203125" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.375" style="49" customWidth="1"/>
-    <col min="3" max="3" width="47.625" style="49" customWidth="1"/>
-    <col min="4" max="4" width="10.875" style="49" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.375" style="49" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.375" style="38" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" style="49" customWidth="1"/>
+    <col min="3" max="3" width="47.58203125" style="49" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" style="49" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="49" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="38" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.75" style="38" bestFit="1" customWidth="1"/>
     <col min="8" max="252" width="8" style="38" customWidth="1"/>
     <col min="253" max="253" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="254" max="254" width="4.125" style="38" customWidth="1"/>
+    <col min="254" max="254" width="4.08203125" style="38" customWidth="1"/>
     <col min="255" max="255" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="256" max="256" width="42.625" style="38" customWidth="1"/>
-    <col min="257" max="257" width="13.375" style="38"/>
+    <col min="256" max="256" width="42.58203125" style="38" customWidth="1"/>
+    <col min="257" max="257" width="13.33203125" style="38"/>
     <col min="258" max="258" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="259" max="259" width="60.375" style="38" customWidth="1"/>
+    <col min="259" max="259" width="60.33203125" style="38" customWidth="1"/>
     <col min="260" max="260" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="261" max="261" width="12.75" style="38" customWidth="1"/>
-    <col min="262" max="262" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="262" max="262" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="263" max="508" width="8" style="38" customWidth="1"/>
     <col min="509" max="509" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="510" max="510" width="4.125" style="38" customWidth="1"/>
+    <col min="510" max="510" width="4.08203125" style="38" customWidth="1"/>
     <col min="511" max="511" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="512" max="512" width="42.625" style="38" customWidth="1"/>
-    <col min="513" max="513" width="13.375" style="38"/>
+    <col min="512" max="512" width="42.58203125" style="38" customWidth="1"/>
+    <col min="513" max="513" width="13.33203125" style="38"/>
     <col min="514" max="514" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="515" max="515" width="60.375" style="38" customWidth="1"/>
+    <col min="515" max="515" width="60.33203125" style="38" customWidth="1"/>
     <col min="516" max="516" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="517" max="517" width="12.75" style="38" customWidth="1"/>
-    <col min="518" max="518" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="518" max="518" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="519" max="764" width="8" style="38" customWidth="1"/>
     <col min="765" max="765" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="766" max="766" width="4.125" style="38" customWidth="1"/>
+    <col min="766" max="766" width="4.08203125" style="38" customWidth="1"/>
     <col min="767" max="767" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="768" max="768" width="42.625" style="38" customWidth="1"/>
-    <col min="769" max="769" width="13.375" style="38"/>
+    <col min="768" max="768" width="42.58203125" style="38" customWidth="1"/>
+    <col min="769" max="769" width="13.33203125" style="38"/>
     <col min="770" max="770" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="771" max="771" width="60.375" style="38" customWidth="1"/>
+    <col min="771" max="771" width="60.33203125" style="38" customWidth="1"/>
     <col min="772" max="772" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="773" max="773" width="12.75" style="38" customWidth="1"/>
-    <col min="774" max="774" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="774" max="774" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="775" max="1020" width="8" style="38" customWidth="1"/>
     <col min="1021" max="1021" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="1022" max="1022" width="4.125" style="38" customWidth="1"/>
+    <col min="1022" max="1022" width="4.08203125" style="38" customWidth="1"/>
     <col min="1023" max="1023" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="1024" max="1024" width="42.625" style="38" customWidth="1"/>
-    <col min="1025" max="1025" width="13.375" style="38"/>
+    <col min="1024" max="1024" width="42.58203125" style="38" customWidth="1"/>
+    <col min="1025" max="1025" width="13.33203125" style="38"/>
     <col min="1026" max="1026" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="1027" max="1027" width="60.375" style="38" customWidth="1"/>
+    <col min="1027" max="1027" width="60.33203125" style="38" customWidth="1"/>
     <col min="1028" max="1028" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="1029" max="1029" width="12.75" style="38" customWidth="1"/>
-    <col min="1030" max="1030" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="1030" max="1030" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="1031" max="1276" width="8" style="38" customWidth="1"/>
     <col min="1277" max="1277" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="1278" max="1278" width="4.125" style="38" customWidth="1"/>
+    <col min="1278" max="1278" width="4.08203125" style="38" customWidth="1"/>
     <col min="1279" max="1279" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="1280" max="1280" width="42.625" style="38" customWidth="1"/>
-    <col min="1281" max="1281" width="13.375" style="38"/>
+    <col min="1280" max="1280" width="42.58203125" style="38" customWidth="1"/>
+    <col min="1281" max="1281" width="13.33203125" style="38"/>
     <col min="1282" max="1282" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="1283" max="1283" width="60.375" style="38" customWidth="1"/>
+    <col min="1283" max="1283" width="60.33203125" style="38" customWidth="1"/>
     <col min="1284" max="1284" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="1285" max="1285" width="12.75" style="38" customWidth="1"/>
-    <col min="1286" max="1286" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="1286" max="1286" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="1287" max="1532" width="8" style="38" customWidth="1"/>
     <col min="1533" max="1533" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="1534" max="1534" width="4.125" style="38" customWidth="1"/>
+    <col min="1534" max="1534" width="4.08203125" style="38" customWidth="1"/>
     <col min="1535" max="1535" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="1536" max="1536" width="42.625" style="38" customWidth="1"/>
-    <col min="1537" max="1537" width="13.375" style="38"/>
+    <col min="1536" max="1536" width="42.58203125" style="38" customWidth="1"/>
+    <col min="1537" max="1537" width="13.33203125" style="38"/>
     <col min="1538" max="1538" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="1539" max="1539" width="60.375" style="38" customWidth="1"/>
+    <col min="1539" max="1539" width="60.33203125" style="38" customWidth="1"/>
     <col min="1540" max="1540" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="1541" max="1541" width="12.75" style="38" customWidth="1"/>
-    <col min="1542" max="1542" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="1542" max="1542" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="1543" max="1788" width="8" style="38" customWidth="1"/>
     <col min="1789" max="1789" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="1790" max="1790" width="4.125" style="38" customWidth="1"/>
+    <col min="1790" max="1790" width="4.08203125" style="38" customWidth="1"/>
     <col min="1791" max="1791" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="1792" max="1792" width="42.625" style="38" customWidth="1"/>
-    <col min="1793" max="1793" width="13.375" style="38"/>
+    <col min="1792" max="1792" width="42.58203125" style="38" customWidth="1"/>
+    <col min="1793" max="1793" width="13.33203125" style="38"/>
     <col min="1794" max="1794" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="1795" max="1795" width="60.375" style="38" customWidth="1"/>
+    <col min="1795" max="1795" width="60.33203125" style="38" customWidth="1"/>
     <col min="1796" max="1796" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="1797" max="1797" width="12.75" style="38" customWidth="1"/>
-    <col min="1798" max="1798" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="1798" max="1798" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="1799" max="2044" width="8" style="38" customWidth="1"/>
     <col min="2045" max="2045" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="2046" max="2046" width="4.125" style="38" customWidth="1"/>
+    <col min="2046" max="2046" width="4.08203125" style="38" customWidth="1"/>
     <col min="2047" max="2047" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="2048" max="2048" width="42.625" style="38" customWidth="1"/>
-    <col min="2049" max="2049" width="13.375" style="38"/>
+    <col min="2048" max="2048" width="42.58203125" style="38" customWidth="1"/>
+    <col min="2049" max="2049" width="13.33203125" style="38"/>
     <col min="2050" max="2050" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="2051" max="2051" width="60.375" style="38" customWidth="1"/>
+    <col min="2051" max="2051" width="60.33203125" style="38" customWidth="1"/>
     <col min="2052" max="2052" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="2053" max="2053" width="12.75" style="38" customWidth="1"/>
-    <col min="2054" max="2054" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="2054" max="2054" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="2055" max="2300" width="8" style="38" customWidth="1"/>
     <col min="2301" max="2301" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="2302" max="2302" width="4.125" style="38" customWidth="1"/>
+    <col min="2302" max="2302" width="4.08203125" style="38" customWidth="1"/>
     <col min="2303" max="2303" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="2304" max="2304" width="42.625" style="38" customWidth="1"/>
-    <col min="2305" max="2305" width="13.375" style="38"/>
+    <col min="2304" max="2304" width="42.58203125" style="38" customWidth="1"/>
+    <col min="2305" max="2305" width="13.33203125" style="38"/>
     <col min="2306" max="2306" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="2307" max="2307" width="60.375" style="38" customWidth="1"/>
+    <col min="2307" max="2307" width="60.33203125" style="38" customWidth="1"/>
     <col min="2308" max="2308" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="2309" max="2309" width="12.75" style="38" customWidth="1"/>
-    <col min="2310" max="2310" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="2310" max="2310" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="2311" max="2556" width="8" style="38" customWidth="1"/>
     <col min="2557" max="2557" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="2558" max="2558" width="4.125" style="38" customWidth="1"/>
+    <col min="2558" max="2558" width="4.08203125" style="38" customWidth="1"/>
     <col min="2559" max="2559" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="2560" max="2560" width="42.625" style="38" customWidth="1"/>
-    <col min="2561" max="2561" width="13.375" style="38"/>
+    <col min="2560" max="2560" width="42.58203125" style="38" customWidth="1"/>
+    <col min="2561" max="2561" width="13.33203125" style="38"/>
     <col min="2562" max="2562" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="2563" max="2563" width="60.375" style="38" customWidth="1"/>
+    <col min="2563" max="2563" width="60.33203125" style="38" customWidth="1"/>
     <col min="2564" max="2564" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="2565" max="2565" width="12.75" style="38" customWidth="1"/>
-    <col min="2566" max="2566" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="2566" max="2566" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="2567" max="2812" width="8" style="38" customWidth="1"/>
     <col min="2813" max="2813" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="2814" max="2814" width="4.125" style="38" customWidth="1"/>
+    <col min="2814" max="2814" width="4.08203125" style="38" customWidth="1"/>
     <col min="2815" max="2815" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="2816" max="2816" width="42.625" style="38" customWidth="1"/>
-    <col min="2817" max="2817" width="13.375" style="38"/>
+    <col min="2816" max="2816" width="42.58203125" style="38" customWidth="1"/>
+    <col min="2817" max="2817" width="13.33203125" style="38"/>
     <col min="2818" max="2818" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="2819" max="2819" width="60.375" style="38" customWidth="1"/>
+    <col min="2819" max="2819" width="60.33203125" style="38" customWidth="1"/>
     <col min="2820" max="2820" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="2821" max="2821" width="12.75" style="38" customWidth="1"/>
-    <col min="2822" max="2822" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="2822" max="2822" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="2823" max="3068" width="8" style="38" customWidth="1"/>
     <col min="3069" max="3069" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="3070" max="3070" width="4.125" style="38" customWidth="1"/>
+    <col min="3070" max="3070" width="4.08203125" style="38" customWidth="1"/>
     <col min="3071" max="3071" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="3072" max="3072" width="42.625" style="38" customWidth="1"/>
-    <col min="3073" max="3073" width="13.375" style="38"/>
+    <col min="3072" max="3072" width="42.58203125" style="38" customWidth="1"/>
+    <col min="3073" max="3073" width="13.33203125" style="38"/>
     <col min="3074" max="3074" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="3075" max="3075" width="60.375" style="38" customWidth="1"/>
+    <col min="3075" max="3075" width="60.33203125" style="38" customWidth="1"/>
     <col min="3076" max="3076" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="3077" max="3077" width="12.75" style="38" customWidth="1"/>
-    <col min="3078" max="3078" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="3078" max="3078" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="3079" max="3324" width="8" style="38" customWidth="1"/>
     <col min="3325" max="3325" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="3326" max="3326" width="4.125" style="38" customWidth="1"/>
+    <col min="3326" max="3326" width="4.08203125" style="38" customWidth="1"/>
     <col min="3327" max="3327" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="3328" max="3328" width="42.625" style="38" customWidth="1"/>
-    <col min="3329" max="3329" width="13.375" style="38"/>
+    <col min="3328" max="3328" width="42.58203125" style="38" customWidth="1"/>
+    <col min="3329" max="3329" width="13.33203125" style="38"/>
     <col min="3330" max="3330" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="3331" max="3331" width="60.375" style="38" customWidth="1"/>
+    <col min="3331" max="3331" width="60.33203125" style="38" customWidth="1"/>
     <col min="3332" max="3332" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="3333" max="3333" width="12.75" style="38" customWidth="1"/>
-    <col min="3334" max="3334" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="3334" max="3334" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="3335" max="3580" width="8" style="38" customWidth="1"/>
     <col min="3581" max="3581" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="3582" max="3582" width="4.125" style="38" customWidth="1"/>
+    <col min="3582" max="3582" width="4.08203125" style="38" customWidth="1"/>
     <col min="3583" max="3583" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="3584" max="3584" width="42.625" style="38" customWidth="1"/>
-    <col min="3585" max="3585" width="13.375" style="38"/>
+    <col min="3584" max="3584" width="42.58203125" style="38" customWidth="1"/>
+    <col min="3585" max="3585" width="13.33203125" style="38"/>
     <col min="3586" max="3586" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="3587" max="3587" width="60.375" style="38" customWidth="1"/>
+    <col min="3587" max="3587" width="60.33203125" style="38" customWidth="1"/>
     <col min="3588" max="3588" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="3589" max="3589" width="12.75" style="38" customWidth="1"/>
-    <col min="3590" max="3590" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="3590" max="3590" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="3591" max="3836" width="8" style="38" customWidth="1"/>
     <col min="3837" max="3837" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="3838" max="3838" width="4.125" style="38" customWidth="1"/>
+    <col min="3838" max="3838" width="4.08203125" style="38" customWidth="1"/>
     <col min="3839" max="3839" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="3840" max="3840" width="42.625" style="38" customWidth="1"/>
-    <col min="3841" max="3841" width="13.375" style="38"/>
+    <col min="3840" max="3840" width="42.58203125" style="38" customWidth="1"/>
+    <col min="3841" max="3841" width="13.33203125" style="38"/>
     <col min="3842" max="3842" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="3843" max="3843" width="60.375" style="38" customWidth="1"/>
+    <col min="3843" max="3843" width="60.33203125" style="38" customWidth="1"/>
     <col min="3844" max="3844" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="3845" max="3845" width="12.75" style="38" customWidth="1"/>
-    <col min="3846" max="3846" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="3846" max="3846" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="3847" max="4092" width="8" style="38" customWidth="1"/>
     <col min="4093" max="4093" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="4094" max="4094" width="4.125" style="38" customWidth="1"/>
+    <col min="4094" max="4094" width="4.08203125" style="38" customWidth="1"/>
     <col min="4095" max="4095" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="4096" max="4096" width="42.625" style="38" customWidth="1"/>
-    <col min="4097" max="4097" width="13.375" style="38"/>
+    <col min="4096" max="4096" width="42.58203125" style="38" customWidth="1"/>
+    <col min="4097" max="4097" width="13.33203125" style="38"/>
     <col min="4098" max="4098" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="4099" max="4099" width="60.375" style="38" customWidth="1"/>
+    <col min="4099" max="4099" width="60.33203125" style="38" customWidth="1"/>
     <col min="4100" max="4100" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="4101" max="4101" width="12.75" style="38" customWidth="1"/>
-    <col min="4102" max="4102" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="4102" max="4102" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="4103" max="4348" width="8" style="38" customWidth="1"/>
     <col min="4349" max="4349" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="4350" max="4350" width="4.125" style="38" customWidth="1"/>
+    <col min="4350" max="4350" width="4.08203125" style="38" customWidth="1"/>
     <col min="4351" max="4351" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="4352" max="4352" width="42.625" style="38" customWidth="1"/>
-    <col min="4353" max="4353" width="13.375" style="38"/>
+    <col min="4352" max="4352" width="42.58203125" style="38" customWidth="1"/>
+    <col min="4353" max="4353" width="13.33203125" style="38"/>
     <col min="4354" max="4354" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="4355" max="4355" width="60.375" style="38" customWidth="1"/>
+    <col min="4355" max="4355" width="60.33203125" style="38" customWidth="1"/>
     <col min="4356" max="4356" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="4357" max="4357" width="12.75" style="38" customWidth="1"/>
-    <col min="4358" max="4358" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="4358" max="4358" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="4359" max="4604" width="8" style="38" customWidth="1"/>
     <col min="4605" max="4605" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="4606" max="4606" width="4.125" style="38" customWidth="1"/>
+    <col min="4606" max="4606" width="4.08203125" style="38" customWidth="1"/>
     <col min="4607" max="4607" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="4608" max="4608" width="42.625" style="38" customWidth="1"/>
-    <col min="4609" max="4609" width="13.375" style="38"/>
+    <col min="4608" max="4608" width="42.58203125" style="38" customWidth="1"/>
+    <col min="4609" max="4609" width="13.33203125" style="38"/>
     <col min="4610" max="4610" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="4611" max="4611" width="60.375" style="38" customWidth="1"/>
+    <col min="4611" max="4611" width="60.33203125" style="38" customWidth="1"/>
     <col min="4612" max="4612" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="4613" max="4613" width="12.75" style="38" customWidth="1"/>
-    <col min="4614" max="4614" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="4614" max="4614" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="4615" max="4860" width="8" style="38" customWidth="1"/>
     <col min="4861" max="4861" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="4862" max="4862" width="4.125" style="38" customWidth="1"/>
+    <col min="4862" max="4862" width="4.08203125" style="38" customWidth="1"/>
     <col min="4863" max="4863" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="4864" max="4864" width="42.625" style="38" customWidth="1"/>
-    <col min="4865" max="4865" width="13.375" style="38"/>
+    <col min="4864" max="4864" width="42.58203125" style="38" customWidth="1"/>
+    <col min="4865" max="4865" width="13.33203125" style="38"/>
     <col min="4866" max="4866" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="4867" max="4867" width="60.375" style="38" customWidth="1"/>
+    <col min="4867" max="4867" width="60.33203125" style="38" customWidth="1"/>
     <col min="4868" max="4868" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="4869" max="4869" width="12.75" style="38" customWidth="1"/>
-    <col min="4870" max="4870" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="4870" max="4870" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="4871" max="5116" width="8" style="38" customWidth="1"/>
     <col min="5117" max="5117" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="5118" max="5118" width="4.125" style="38" customWidth="1"/>
+    <col min="5118" max="5118" width="4.08203125" style="38" customWidth="1"/>
     <col min="5119" max="5119" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="5120" max="5120" width="42.625" style="38" customWidth="1"/>
-    <col min="5121" max="5121" width="13.375" style="38"/>
+    <col min="5120" max="5120" width="42.58203125" style="38" customWidth="1"/>
+    <col min="5121" max="5121" width="13.33203125" style="38"/>
     <col min="5122" max="5122" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="5123" max="5123" width="60.375" style="38" customWidth="1"/>
+    <col min="5123" max="5123" width="60.33203125" style="38" customWidth="1"/>
     <col min="5124" max="5124" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="5125" max="5125" width="12.75" style="38" customWidth="1"/>
-    <col min="5126" max="5126" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="5126" max="5126" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="5127" max="5372" width="8" style="38" customWidth="1"/>
     <col min="5373" max="5373" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="5374" max="5374" width="4.125" style="38" customWidth="1"/>
+    <col min="5374" max="5374" width="4.08203125" style="38" customWidth="1"/>
     <col min="5375" max="5375" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="5376" max="5376" width="42.625" style="38" customWidth="1"/>
-    <col min="5377" max="5377" width="13.375" style="38"/>
+    <col min="5376" max="5376" width="42.58203125" style="38" customWidth="1"/>
+    <col min="5377" max="5377" width="13.33203125" style="38"/>
     <col min="5378" max="5378" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="5379" max="5379" width="60.375" style="38" customWidth="1"/>
+    <col min="5379" max="5379" width="60.33203125" style="38" customWidth="1"/>
     <col min="5380" max="5380" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="5381" max="5381" width="12.75" style="38" customWidth="1"/>
-    <col min="5382" max="5382" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="5382" max="5382" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="5383" max="5628" width="8" style="38" customWidth="1"/>
     <col min="5629" max="5629" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="5630" max="5630" width="4.125" style="38" customWidth="1"/>
+    <col min="5630" max="5630" width="4.08203125" style="38" customWidth="1"/>
     <col min="5631" max="5631" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="5632" max="5632" width="42.625" style="38" customWidth="1"/>
-    <col min="5633" max="5633" width="13.375" style="38"/>
+    <col min="5632" max="5632" width="42.58203125" style="38" customWidth="1"/>
+    <col min="5633" max="5633" width="13.33203125" style="38"/>
     <col min="5634" max="5634" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="5635" max="5635" width="60.375" style="38" customWidth="1"/>
+    <col min="5635" max="5635" width="60.33203125" style="38" customWidth="1"/>
     <col min="5636" max="5636" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="5637" max="5637" width="12.75" style="38" customWidth="1"/>
-    <col min="5638" max="5638" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="5638" max="5638" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="5639" max="5884" width="8" style="38" customWidth="1"/>
     <col min="5885" max="5885" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="5886" max="5886" width="4.125" style="38" customWidth="1"/>
+    <col min="5886" max="5886" width="4.08203125" style="38" customWidth="1"/>
     <col min="5887" max="5887" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="5888" max="5888" width="42.625" style="38" customWidth="1"/>
-    <col min="5889" max="5889" width="13.375" style="38"/>
+    <col min="5888" max="5888" width="42.58203125" style="38" customWidth="1"/>
+    <col min="5889" max="5889" width="13.33203125" style="38"/>
     <col min="5890" max="5890" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="5891" max="5891" width="60.375" style="38" customWidth="1"/>
+    <col min="5891" max="5891" width="60.33203125" style="38" customWidth="1"/>
     <col min="5892" max="5892" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="5893" max="5893" width="12.75" style="38" customWidth="1"/>
-    <col min="5894" max="5894" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="5894" max="5894" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="5895" max="6140" width="8" style="38" customWidth="1"/>
     <col min="6141" max="6141" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="6142" max="6142" width="4.125" style="38" customWidth="1"/>
+    <col min="6142" max="6142" width="4.08203125" style="38" customWidth="1"/>
     <col min="6143" max="6143" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="6144" max="6144" width="42.625" style="38" customWidth="1"/>
-    <col min="6145" max="6145" width="13.375" style="38"/>
+    <col min="6144" max="6144" width="42.58203125" style="38" customWidth="1"/>
+    <col min="6145" max="6145" width="13.33203125" style="38"/>
     <col min="6146" max="6146" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="6147" max="6147" width="60.375" style="38" customWidth="1"/>
+    <col min="6147" max="6147" width="60.33203125" style="38" customWidth="1"/>
     <col min="6148" max="6148" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="6149" max="6149" width="12.75" style="38" customWidth="1"/>
-    <col min="6150" max="6150" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="6150" max="6150" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="6151" max="6396" width="8" style="38" customWidth="1"/>
     <col min="6397" max="6397" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="6398" max="6398" width="4.125" style="38" customWidth="1"/>
+    <col min="6398" max="6398" width="4.08203125" style="38" customWidth="1"/>
     <col min="6399" max="6399" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="6400" max="6400" width="42.625" style="38" customWidth="1"/>
-    <col min="6401" max="6401" width="13.375" style="38"/>
+    <col min="6400" max="6400" width="42.58203125" style="38" customWidth="1"/>
+    <col min="6401" max="6401" width="13.33203125" style="38"/>
     <col min="6402" max="6402" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="6403" max="6403" width="60.375" style="38" customWidth="1"/>
+    <col min="6403" max="6403" width="60.33203125" style="38" customWidth="1"/>
     <col min="6404" max="6404" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="6405" max="6405" width="12.75" style="38" customWidth="1"/>
-    <col min="6406" max="6406" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="6406" max="6406" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="6407" max="6652" width="8" style="38" customWidth="1"/>
     <col min="6653" max="6653" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="6654" max="6654" width="4.125" style="38" customWidth="1"/>
+    <col min="6654" max="6654" width="4.08203125" style="38" customWidth="1"/>
     <col min="6655" max="6655" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="6656" max="6656" width="42.625" style="38" customWidth="1"/>
-    <col min="6657" max="6657" width="13.375" style="38"/>
+    <col min="6656" max="6656" width="42.58203125" style="38" customWidth="1"/>
+    <col min="6657" max="6657" width="13.33203125" style="38"/>
     <col min="6658" max="6658" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="6659" max="6659" width="60.375" style="38" customWidth="1"/>
+    <col min="6659" max="6659" width="60.33203125" style="38" customWidth="1"/>
     <col min="6660" max="6660" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="6661" max="6661" width="12.75" style="38" customWidth="1"/>
-    <col min="6662" max="6662" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="6662" max="6662" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="6663" max="6908" width="8" style="38" customWidth="1"/>
     <col min="6909" max="6909" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="6910" max="6910" width="4.125" style="38" customWidth="1"/>
+    <col min="6910" max="6910" width="4.08203125" style="38" customWidth="1"/>
     <col min="6911" max="6911" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="6912" max="6912" width="42.625" style="38" customWidth="1"/>
-    <col min="6913" max="6913" width="13.375" style="38"/>
+    <col min="6912" max="6912" width="42.58203125" style="38" customWidth="1"/>
+    <col min="6913" max="6913" width="13.33203125" style="38"/>
     <col min="6914" max="6914" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="6915" max="6915" width="60.375" style="38" customWidth="1"/>
+    <col min="6915" max="6915" width="60.33203125" style="38" customWidth="1"/>
     <col min="6916" max="6916" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="6917" max="6917" width="12.75" style="38" customWidth="1"/>
-    <col min="6918" max="6918" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="6918" max="6918" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="6919" max="7164" width="8" style="38" customWidth="1"/>
     <col min="7165" max="7165" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="7166" max="7166" width="4.125" style="38" customWidth="1"/>
+    <col min="7166" max="7166" width="4.08203125" style="38" customWidth="1"/>
     <col min="7167" max="7167" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="7168" max="7168" width="42.625" style="38" customWidth="1"/>
-    <col min="7169" max="7169" width="13.375" style="38"/>
+    <col min="7168" max="7168" width="42.58203125" style="38" customWidth="1"/>
+    <col min="7169" max="7169" width="13.33203125" style="38"/>
     <col min="7170" max="7170" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="7171" max="7171" width="60.375" style="38" customWidth="1"/>
+    <col min="7171" max="7171" width="60.33203125" style="38" customWidth="1"/>
     <col min="7172" max="7172" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="7173" max="7173" width="12.75" style="38" customWidth="1"/>
-    <col min="7174" max="7174" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="7174" max="7174" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="7175" max="7420" width="8" style="38" customWidth="1"/>
     <col min="7421" max="7421" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="7422" max="7422" width="4.125" style="38" customWidth="1"/>
+    <col min="7422" max="7422" width="4.08203125" style="38" customWidth="1"/>
     <col min="7423" max="7423" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="7424" max="7424" width="42.625" style="38" customWidth="1"/>
-    <col min="7425" max="7425" width="13.375" style="38"/>
+    <col min="7424" max="7424" width="42.58203125" style="38" customWidth="1"/>
+    <col min="7425" max="7425" width="13.33203125" style="38"/>
     <col min="7426" max="7426" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="7427" max="7427" width="60.375" style="38" customWidth="1"/>
+    <col min="7427" max="7427" width="60.33203125" style="38" customWidth="1"/>
     <col min="7428" max="7428" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="7429" max="7429" width="12.75" style="38" customWidth="1"/>
-    <col min="7430" max="7430" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="7430" max="7430" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="7431" max="7676" width="8" style="38" customWidth="1"/>
     <col min="7677" max="7677" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="7678" max="7678" width="4.125" style="38" customWidth="1"/>
+    <col min="7678" max="7678" width="4.08203125" style="38" customWidth="1"/>
     <col min="7679" max="7679" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="7680" max="7680" width="42.625" style="38" customWidth="1"/>
-    <col min="7681" max="7681" width="13.375" style="38"/>
+    <col min="7680" max="7680" width="42.58203125" style="38" customWidth="1"/>
+    <col min="7681" max="7681" width="13.33203125" style="38"/>
     <col min="7682" max="7682" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="7683" max="7683" width="60.375" style="38" customWidth="1"/>
+    <col min="7683" max="7683" width="60.33203125" style="38" customWidth="1"/>
     <col min="7684" max="7684" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="7685" max="7685" width="12.75" style="38" customWidth="1"/>
-    <col min="7686" max="7686" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="7686" max="7686" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="7687" max="7932" width="8" style="38" customWidth="1"/>
     <col min="7933" max="7933" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="7934" max="7934" width="4.125" style="38" customWidth="1"/>
+    <col min="7934" max="7934" width="4.08203125" style="38" customWidth="1"/>
     <col min="7935" max="7935" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="7936" max="7936" width="42.625" style="38" customWidth="1"/>
-    <col min="7937" max="7937" width="13.375" style="38"/>
+    <col min="7936" max="7936" width="42.58203125" style="38" customWidth="1"/>
+    <col min="7937" max="7937" width="13.33203125" style="38"/>
     <col min="7938" max="7938" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="7939" max="7939" width="60.375" style="38" customWidth="1"/>
+    <col min="7939" max="7939" width="60.33203125" style="38" customWidth="1"/>
     <col min="7940" max="7940" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="7941" max="7941" width="12.75" style="38" customWidth="1"/>
-    <col min="7942" max="7942" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="7942" max="7942" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="7943" max="8188" width="8" style="38" customWidth="1"/>
     <col min="8189" max="8189" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="8190" max="8190" width="4.125" style="38" customWidth="1"/>
+    <col min="8190" max="8190" width="4.08203125" style="38" customWidth="1"/>
     <col min="8191" max="8191" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="8192" max="8192" width="42.625" style="38" customWidth="1"/>
-    <col min="8193" max="8193" width="13.375" style="38"/>
+    <col min="8192" max="8192" width="42.58203125" style="38" customWidth="1"/>
+    <col min="8193" max="8193" width="13.33203125" style="38"/>
     <col min="8194" max="8194" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="8195" max="8195" width="60.375" style="38" customWidth="1"/>
+    <col min="8195" max="8195" width="60.33203125" style="38" customWidth="1"/>
     <col min="8196" max="8196" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="8197" max="8197" width="12.75" style="38" customWidth="1"/>
-    <col min="8198" max="8198" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="8198" max="8198" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="8199" max="8444" width="8" style="38" customWidth="1"/>
     <col min="8445" max="8445" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="8446" max="8446" width="4.125" style="38" customWidth="1"/>
+    <col min="8446" max="8446" width="4.08203125" style="38" customWidth="1"/>
     <col min="8447" max="8447" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="8448" max="8448" width="42.625" style="38" customWidth="1"/>
-    <col min="8449" max="8449" width="13.375" style="38"/>
+    <col min="8448" max="8448" width="42.58203125" style="38" customWidth="1"/>
+    <col min="8449" max="8449" width="13.33203125" style="38"/>
     <col min="8450" max="8450" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="8451" max="8451" width="60.375" style="38" customWidth="1"/>
+    <col min="8451" max="8451" width="60.33203125" style="38" customWidth="1"/>
     <col min="8452" max="8452" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="8453" max="8453" width="12.75" style="38" customWidth="1"/>
-    <col min="8454" max="8454" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="8454" max="8454" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="8455" max="8700" width="8" style="38" customWidth="1"/>
     <col min="8701" max="8701" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="8702" max="8702" width="4.125" style="38" customWidth="1"/>
+    <col min="8702" max="8702" width="4.08203125" style="38" customWidth="1"/>
     <col min="8703" max="8703" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="8704" max="8704" width="42.625" style="38" customWidth="1"/>
-    <col min="8705" max="8705" width="13.375" style="38"/>
+    <col min="8704" max="8704" width="42.58203125" style="38" customWidth="1"/>
+    <col min="8705" max="8705" width="13.33203125" style="38"/>
     <col min="8706" max="8706" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="8707" max="8707" width="60.375" style="38" customWidth="1"/>
+    <col min="8707" max="8707" width="60.33203125" style="38" customWidth="1"/>
     <col min="8708" max="8708" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="8709" max="8709" width="12.75" style="38" customWidth="1"/>
-    <col min="8710" max="8710" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="8710" max="8710" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="8711" max="8956" width="8" style="38" customWidth="1"/>
     <col min="8957" max="8957" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="8958" max="8958" width="4.125" style="38" customWidth="1"/>
+    <col min="8958" max="8958" width="4.08203125" style="38" customWidth="1"/>
     <col min="8959" max="8959" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="8960" max="8960" width="42.625" style="38" customWidth="1"/>
-    <col min="8961" max="8961" width="13.375" style="38"/>
+    <col min="8960" max="8960" width="42.58203125" style="38" customWidth="1"/>
+    <col min="8961" max="8961" width="13.33203125" style="38"/>
     <col min="8962" max="8962" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="8963" max="8963" width="60.375" style="38" customWidth="1"/>
+    <col min="8963" max="8963" width="60.33203125" style="38" customWidth="1"/>
     <col min="8964" max="8964" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="8965" max="8965" width="12.75" style="38" customWidth="1"/>
-    <col min="8966" max="8966" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="8966" max="8966" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="8967" max="9212" width="8" style="38" customWidth="1"/>
     <col min="9213" max="9213" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="9214" max="9214" width="4.125" style="38" customWidth="1"/>
+    <col min="9214" max="9214" width="4.08203125" style="38" customWidth="1"/>
     <col min="9215" max="9215" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="9216" max="9216" width="42.625" style="38" customWidth="1"/>
-    <col min="9217" max="9217" width="13.375" style="38"/>
+    <col min="9216" max="9216" width="42.58203125" style="38" customWidth="1"/>
+    <col min="9217" max="9217" width="13.33203125" style="38"/>
     <col min="9218" max="9218" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="9219" max="9219" width="60.375" style="38" customWidth="1"/>
+    <col min="9219" max="9219" width="60.33203125" style="38" customWidth="1"/>
     <col min="9220" max="9220" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="9221" max="9221" width="12.75" style="38" customWidth="1"/>
-    <col min="9222" max="9222" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="9222" max="9222" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="9223" max="9468" width="8" style="38" customWidth="1"/>
     <col min="9469" max="9469" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="9470" max="9470" width="4.125" style="38" customWidth="1"/>
+    <col min="9470" max="9470" width="4.08203125" style="38" customWidth="1"/>
     <col min="9471" max="9471" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="9472" max="9472" width="42.625" style="38" customWidth="1"/>
-    <col min="9473" max="9473" width="13.375" style="38"/>
+    <col min="9472" max="9472" width="42.58203125" style="38" customWidth="1"/>
+    <col min="9473" max="9473" width="13.33203125" style="38"/>
     <col min="9474" max="9474" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="9475" max="9475" width="60.375" style="38" customWidth="1"/>
+    <col min="9475" max="9475" width="60.33203125" style="38" customWidth="1"/>
     <col min="9476" max="9476" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="9477" max="9477" width="12.75" style="38" customWidth="1"/>
-    <col min="9478" max="9478" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="9478" max="9478" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="9479" max="9724" width="8" style="38" customWidth="1"/>
     <col min="9725" max="9725" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="9726" max="9726" width="4.125" style="38" customWidth="1"/>
+    <col min="9726" max="9726" width="4.08203125" style="38" customWidth="1"/>
     <col min="9727" max="9727" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="9728" max="9728" width="42.625" style="38" customWidth="1"/>
-    <col min="9729" max="9729" width="13.375" style="38"/>
+    <col min="9728" max="9728" width="42.58203125" style="38" customWidth="1"/>
+    <col min="9729" max="9729" width="13.33203125" style="38"/>
     <col min="9730" max="9730" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="9731" max="9731" width="60.375" style="38" customWidth="1"/>
+    <col min="9731" max="9731" width="60.33203125" style="38" customWidth="1"/>
     <col min="9732" max="9732" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="9733" max="9733" width="12.75" style="38" customWidth="1"/>
-    <col min="9734" max="9734" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="9734" max="9734" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="9735" max="9980" width="8" style="38" customWidth="1"/>
     <col min="9981" max="9981" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="9982" max="9982" width="4.125" style="38" customWidth="1"/>
+    <col min="9982" max="9982" width="4.08203125" style="38" customWidth="1"/>
     <col min="9983" max="9983" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="9984" max="9984" width="42.625" style="38" customWidth="1"/>
-    <col min="9985" max="9985" width="13.375" style="38"/>
+    <col min="9984" max="9984" width="42.58203125" style="38" customWidth="1"/>
+    <col min="9985" max="9985" width="13.33203125" style="38"/>
     <col min="9986" max="9986" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="9987" max="9987" width="60.375" style="38" customWidth="1"/>
+    <col min="9987" max="9987" width="60.33203125" style="38" customWidth="1"/>
     <col min="9988" max="9988" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="9989" max="9989" width="12.75" style="38" customWidth="1"/>
-    <col min="9990" max="9990" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="9990" max="9990" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="9991" max="10236" width="8" style="38" customWidth="1"/>
     <col min="10237" max="10237" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="10238" max="10238" width="4.125" style="38" customWidth="1"/>
+    <col min="10238" max="10238" width="4.08203125" style="38" customWidth="1"/>
     <col min="10239" max="10239" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="10240" max="10240" width="42.625" style="38" customWidth="1"/>
-    <col min="10241" max="10241" width="13.375" style="38"/>
+    <col min="10240" max="10240" width="42.58203125" style="38" customWidth="1"/>
+    <col min="10241" max="10241" width="13.33203125" style="38"/>
     <col min="10242" max="10242" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="10243" max="10243" width="60.375" style="38" customWidth="1"/>
+    <col min="10243" max="10243" width="60.33203125" style="38" customWidth="1"/>
     <col min="10244" max="10244" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="10245" max="10245" width="12.75" style="38" customWidth="1"/>
-    <col min="10246" max="10246" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="10246" max="10246" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="10247" max="10492" width="8" style="38" customWidth="1"/>
     <col min="10493" max="10493" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="10494" max="10494" width="4.125" style="38" customWidth="1"/>
+    <col min="10494" max="10494" width="4.08203125" style="38" customWidth="1"/>
     <col min="10495" max="10495" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="10496" max="10496" width="42.625" style="38" customWidth="1"/>
-    <col min="10497" max="10497" width="13.375" style="38"/>
+    <col min="10496" max="10496" width="42.58203125" style="38" customWidth="1"/>
+    <col min="10497" max="10497" width="13.33203125" style="38"/>
     <col min="10498" max="10498" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="10499" max="10499" width="60.375" style="38" customWidth="1"/>
+    <col min="10499" max="10499" width="60.33203125" style="38" customWidth="1"/>
     <col min="10500" max="10500" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="10501" max="10501" width="12.75" style="38" customWidth="1"/>
-    <col min="10502" max="10502" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="10502" max="10502" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="10503" max="10748" width="8" style="38" customWidth="1"/>
     <col min="10749" max="10749" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="10750" max="10750" width="4.125" style="38" customWidth="1"/>
+    <col min="10750" max="10750" width="4.08203125" style="38" customWidth="1"/>
     <col min="10751" max="10751" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="10752" max="10752" width="42.625" style="38" customWidth="1"/>
-    <col min="10753" max="10753" width="13.375" style="38"/>
+    <col min="10752" max="10752" width="42.58203125" style="38" customWidth="1"/>
+    <col min="10753" max="10753" width="13.33203125" style="38"/>
     <col min="10754" max="10754" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="10755" max="10755" width="60.375" style="38" customWidth="1"/>
+    <col min="10755" max="10755" width="60.33203125" style="38" customWidth="1"/>
     <col min="10756" max="10756" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="10757" max="10757" width="12.75" style="38" customWidth="1"/>
-    <col min="10758" max="10758" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="10758" max="10758" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="10759" max="11004" width="8" style="38" customWidth="1"/>
     <col min="11005" max="11005" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="11006" max="11006" width="4.125" style="38" customWidth="1"/>
+    <col min="11006" max="11006" width="4.08203125" style="38" customWidth="1"/>
     <col min="11007" max="11007" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="11008" max="11008" width="42.625" style="38" customWidth="1"/>
-    <col min="11009" max="11009" width="13.375" style="38"/>
+    <col min="11008" max="11008" width="42.58203125" style="38" customWidth="1"/>
+    <col min="11009" max="11009" width="13.33203125" style="38"/>
     <col min="11010" max="11010" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="11011" max="11011" width="60.375" style="38" customWidth="1"/>
+    <col min="11011" max="11011" width="60.33203125" style="38" customWidth="1"/>
     <col min="11012" max="11012" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="11013" max="11013" width="12.75" style="38" customWidth="1"/>
-    <col min="11014" max="11014" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="11014" max="11014" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="11015" max="11260" width="8" style="38" customWidth="1"/>
     <col min="11261" max="11261" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="11262" max="11262" width="4.125" style="38" customWidth="1"/>
+    <col min="11262" max="11262" width="4.08203125" style="38" customWidth="1"/>
     <col min="11263" max="11263" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="11264" max="11264" width="42.625" style="38" customWidth="1"/>
-    <col min="11265" max="11265" width="13.375" style="38"/>
+    <col min="11264" max="11264" width="42.58203125" style="38" customWidth="1"/>
+    <col min="11265" max="11265" width="13.33203125" style="38"/>
     <col min="11266" max="11266" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="11267" max="11267" width="60.375" style="38" customWidth="1"/>
+    <col min="11267" max="11267" width="60.33203125" style="38" customWidth="1"/>
     <col min="11268" max="11268" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="11269" max="11269" width="12.75" style="38" customWidth="1"/>
-    <col min="11270" max="11270" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="11270" max="11270" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="11271" max="11516" width="8" style="38" customWidth="1"/>
     <col min="11517" max="11517" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="11518" max="11518" width="4.125" style="38" customWidth="1"/>
+    <col min="11518" max="11518" width="4.08203125" style="38" customWidth="1"/>
     <col min="11519" max="11519" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="11520" max="11520" width="42.625" style="38" customWidth="1"/>
-    <col min="11521" max="11521" width="13.375" style="38"/>
+    <col min="11520" max="11520" width="42.58203125" style="38" customWidth="1"/>
+    <col min="11521" max="11521" width="13.33203125" style="38"/>
     <col min="11522" max="11522" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="11523" max="11523" width="60.375" style="38" customWidth="1"/>
+    <col min="11523" max="11523" width="60.33203125" style="38" customWidth="1"/>
     <col min="11524" max="11524" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="11525" max="11525" width="12.75" style="38" customWidth="1"/>
-    <col min="11526" max="11526" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="11526" max="11526" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="11527" max="11772" width="8" style="38" customWidth="1"/>
     <col min="11773" max="11773" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="11774" max="11774" width="4.125" style="38" customWidth="1"/>
+    <col min="11774" max="11774" width="4.08203125" style="38" customWidth="1"/>
     <col min="11775" max="11775" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="11776" max="11776" width="42.625" style="38" customWidth="1"/>
-    <col min="11777" max="11777" width="13.375" style="38"/>
+    <col min="11776" max="11776" width="42.58203125" style="38" customWidth="1"/>
+    <col min="11777" max="11777" width="13.33203125" style="38"/>
     <col min="11778" max="11778" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="11779" max="11779" width="60.375" style="38" customWidth="1"/>
+    <col min="11779" max="11779" width="60.33203125" style="38" customWidth="1"/>
     <col min="11780" max="11780" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="11781" max="11781" width="12.75" style="38" customWidth="1"/>
-    <col min="11782" max="11782" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="11782" max="11782" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="11783" max="12028" width="8" style="38" customWidth="1"/>
     <col min="12029" max="12029" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="12030" max="12030" width="4.125" style="38" customWidth="1"/>
+    <col min="12030" max="12030" width="4.08203125" style="38" customWidth="1"/>
     <col min="12031" max="12031" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="12032" max="12032" width="42.625" style="38" customWidth="1"/>
-    <col min="12033" max="12033" width="13.375" style="38"/>
+    <col min="12032" max="12032" width="42.58203125" style="38" customWidth="1"/>
+    <col min="12033" max="12033" width="13.33203125" style="38"/>
     <col min="12034" max="12034" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="12035" max="12035" width="60.375" style="38" customWidth="1"/>
+    <col min="12035" max="12035" width="60.33203125" style="38" customWidth="1"/>
     <col min="12036" max="12036" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="12037" max="12037" width="12.75" style="38" customWidth="1"/>
-    <col min="12038" max="12038" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="12038" max="12038" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="12039" max="12284" width="8" style="38" customWidth="1"/>
     <col min="12285" max="12285" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="12286" max="12286" width="4.125" style="38" customWidth="1"/>
+    <col min="12286" max="12286" width="4.08203125" style="38" customWidth="1"/>
     <col min="12287" max="12287" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="12288" max="12288" width="42.625" style="38" customWidth="1"/>
-    <col min="12289" max="12289" width="13.375" style="38"/>
+    <col min="12288" max="12288" width="42.58203125" style="38" customWidth="1"/>
+    <col min="12289" max="12289" width="13.33203125" style="38"/>
     <col min="12290" max="12290" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="12291" max="12291" width="60.375" style="38" customWidth="1"/>
+    <col min="12291" max="12291" width="60.33203125" style="38" customWidth="1"/>
     <col min="12292" max="12292" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="12293" max="12293" width="12.75" style="38" customWidth="1"/>
-    <col min="12294" max="12294" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="12294" max="12294" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="12295" max="12540" width="8" style="38" customWidth="1"/>
     <col min="12541" max="12541" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="12542" max="12542" width="4.125" style="38" customWidth="1"/>
+    <col min="12542" max="12542" width="4.08203125" style="38" customWidth="1"/>
     <col min="12543" max="12543" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="12544" max="12544" width="42.625" style="38" customWidth="1"/>
-    <col min="12545" max="12545" width="13.375" style="38"/>
+    <col min="12544" max="12544" width="42.58203125" style="38" customWidth="1"/>
+    <col min="12545" max="12545" width="13.33203125" style="38"/>
     <col min="12546" max="12546" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="12547" max="12547" width="60.375" style="38" customWidth="1"/>
+    <col min="12547" max="12547" width="60.33203125" style="38" customWidth="1"/>
     <col min="12548" max="12548" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="12549" max="12549" width="12.75" style="38" customWidth="1"/>
-    <col min="12550" max="12550" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="12550" max="12550" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="12551" max="12796" width="8" style="38" customWidth="1"/>
     <col min="12797" max="12797" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="12798" max="12798" width="4.125" style="38" customWidth="1"/>
+    <col min="12798" max="12798" width="4.08203125" style="38" customWidth="1"/>
     <col min="12799" max="12799" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="12800" max="12800" width="42.625" style="38" customWidth="1"/>
-    <col min="12801" max="12801" width="13.375" style="38"/>
+    <col min="12800" max="12800" width="42.58203125" style="38" customWidth="1"/>
+    <col min="12801" max="12801" width="13.33203125" style="38"/>
     <col min="12802" max="12802" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="12803" max="12803" width="60.375" style="38" customWidth="1"/>
+    <col min="12803" max="12803" width="60.33203125" style="38" customWidth="1"/>
     <col min="12804" max="12804" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="12805" max="12805" width="12.75" style="38" customWidth="1"/>
-    <col min="12806" max="12806" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="12806" max="12806" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="12807" max="13052" width="8" style="38" customWidth="1"/>
     <col min="13053" max="13053" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="13054" max="13054" width="4.125" style="38" customWidth="1"/>
+    <col min="13054" max="13054" width="4.08203125" style="38" customWidth="1"/>
     <col min="13055" max="13055" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="13056" max="13056" width="42.625" style="38" customWidth="1"/>
-    <col min="13057" max="13057" width="13.375" style="38"/>
+    <col min="13056" max="13056" width="42.58203125" style="38" customWidth="1"/>
+    <col min="13057" max="13057" width="13.33203125" style="38"/>
     <col min="13058" max="13058" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="13059" max="13059" width="60.375" style="38" customWidth="1"/>
+    <col min="13059" max="13059" width="60.33203125" style="38" customWidth="1"/>
     <col min="13060" max="13060" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="13061" max="13061" width="12.75" style="38" customWidth="1"/>
-    <col min="13062" max="13062" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="13062" max="13062" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="13063" max="13308" width="8" style="38" customWidth="1"/>
     <col min="13309" max="13309" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="13310" max="13310" width="4.125" style="38" customWidth="1"/>
+    <col min="13310" max="13310" width="4.08203125" style="38" customWidth="1"/>
     <col min="13311" max="13311" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="13312" max="13312" width="42.625" style="38" customWidth="1"/>
-    <col min="13313" max="13313" width="13.375" style="38"/>
+    <col min="13312" max="13312" width="42.58203125" style="38" customWidth="1"/>
+    <col min="13313" max="13313" width="13.33203125" style="38"/>
     <col min="13314" max="13314" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="13315" max="13315" width="60.375" style="38" customWidth="1"/>
+    <col min="13315" max="13315" width="60.33203125" style="38" customWidth="1"/>
     <col min="13316" max="13316" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="13317" max="13317" width="12.75" style="38" customWidth="1"/>
-    <col min="13318" max="13318" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="13318" max="13318" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="13319" max="13564" width="8" style="38" customWidth="1"/>
     <col min="13565" max="13565" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="13566" max="13566" width="4.125" style="38" customWidth="1"/>
+    <col min="13566" max="13566" width="4.08203125" style="38" customWidth="1"/>
     <col min="13567" max="13567" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="13568" max="13568" width="42.625" style="38" customWidth="1"/>
-    <col min="13569" max="13569" width="13.375" style="38"/>
+    <col min="13568" max="13568" width="42.58203125" style="38" customWidth="1"/>
+    <col min="13569" max="13569" width="13.33203125" style="38"/>
     <col min="13570" max="13570" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="13571" max="13571" width="60.375" style="38" customWidth="1"/>
+    <col min="13571" max="13571" width="60.33203125" style="38" customWidth="1"/>
     <col min="13572" max="13572" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="13573" max="13573" width="12.75" style="38" customWidth="1"/>
-    <col min="13574" max="13574" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="13574" max="13574" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="13575" max="13820" width="8" style="38" customWidth="1"/>
     <col min="13821" max="13821" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="13822" max="13822" width="4.125" style="38" customWidth="1"/>
+    <col min="13822" max="13822" width="4.08203125" style="38" customWidth="1"/>
     <col min="13823" max="13823" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="13824" max="13824" width="42.625" style="38" customWidth="1"/>
-    <col min="13825" max="13825" width="13.375" style="38"/>
+    <col min="13824" max="13824" width="42.58203125" style="38" customWidth="1"/>
+    <col min="13825" max="13825" width="13.33203125" style="38"/>
     <col min="13826" max="13826" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="13827" max="13827" width="60.375" style="38" customWidth="1"/>
+    <col min="13827" max="13827" width="60.33203125" style="38" customWidth="1"/>
     <col min="13828" max="13828" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="13829" max="13829" width="12.75" style="38" customWidth="1"/>
-    <col min="13830" max="13830" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="13830" max="13830" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="13831" max="14076" width="8" style="38" customWidth="1"/>
     <col min="14077" max="14077" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="14078" max="14078" width="4.125" style="38" customWidth="1"/>
+    <col min="14078" max="14078" width="4.08203125" style="38" customWidth="1"/>
     <col min="14079" max="14079" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="14080" max="14080" width="42.625" style="38" customWidth="1"/>
-    <col min="14081" max="14081" width="13.375" style="38"/>
+    <col min="14080" max="14080" width="42.58203125" style="38" customWidth="1"/>
+    <col min="14081" max="14081" width="13.33203125" style="38"/>
     <col min="14082" max="14082" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="14083" max="14083" width="60.375" style="38" customWidth="1"/>
+    <col min="14083" max="14083" width="60.33203125" style="38" customWidth="1"/>
     <col min="14084" max="14084" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="14085" max="14085" width="12.75" style="38" customWidth="1"/>
-    <col min="14086" max="14086" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="14086" max="14086" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="14087" max="14332" width="8" style="38" customWidth="1"/>
     <col min="14333" max="14333" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="14334" max="14334" width="4.125" style="38" customWidth="1"/>
+    <col min="14334" max="14334" width="4.08203125" style="38" customWidth="1"/>
     <col min="14335" max="14335" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="14336" max="14336" width="42.625" style="38" customWidth="1"/>
-    <col min="14337" max="14337" width="13.375" style="38"/>
+    <col min="14336" max="14336" width="42.58203125" style="38" customWidth="1"/>
+    <col min="14337" max="14337" width="13.33203125" style="38"/>
     <col min="14338" max="14338" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="14339" max="14339" width="60.375" style="38" customWidth="1"/>
+    <col min="14339" max="14339" width="60.33203125" style="38" customWidth="1"/>
     <col min="14340" max="14340" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="14341" max="14341" width="12.75" style="38" customWidth="1"/>
-    <col min="14342" max="14342" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="14342" max="14342" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="14343" max="14588" width="8" style="38" customWidth="1"/>
     <col min="14589" max="14589" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="14590" max="14590" width="4.125" style="38" customWidth="1"/>
+    <col min="14590" max="14590" width="4.08203125" style="38" customWidth="1"/>
     <col min="14591" max="14591" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="14592" max="14592" width="42.625" style="38" customWidth="1"/>
-    <col min="14593" max="14593" width="13.375" style="38"/>
+    <col min="14592" max="14592" width="42.58203125" style="38" customWidth="1"/>
+    <col min="14593" max="14593" width="13.33203125" style="38"/>
     <col min="14594" max="14594" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="14595" max="14595" width="60.375" style="38" customWidth="1"/>
+    <col min="14595" max="14595" width="60.33203125" style="38" customWidth="1"/>
     <col min="14596" max="14596" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="14597" max="14597" width="12.75" style="38" customWidth="1"/>
-    <col min="14598" max="14598" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="14598" max="14598" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="14599" max="14844" width="8" style="38" customWidth="1"/>
     <col min="14845" max="14845" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="14846" max="14846" width="4.125" style="38" customWidth="1"/>
+    <col min="14846" max="14846" width="4.08203125" style="38" customWidth="1"/>
     <col min="14847" max="14847" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="14848" max="14848" width="42.625" style="38" customWidth="1"/>
-    <col min="14849" max="14849" width="13.375" style="38"/>
+    <col min="14848" max="14848" width="42.58203125" style="38" customWidth="1"/>
+    <col min="14849" max="14849" width="13.33203125" style="38"/>
     <col min="14850" max="14850" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="14851" max="14851" width="60.375" style="38" customWidth="1"/>
+    <col min="14851" max="14851" width="60.33203125" style="38" customWidth="1"/>
     <col min="14852" max="14852" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="14853" max="14853" width="12.75" style="38" customWidth="1"/>
-    <col min="14854" max="14854" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="14854" max="14854" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="14855" max="15100" width="8" style="38" customWidth="1"/>
     <col min="15101" max="15101" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="15102" max="15102" width="4.125" style="38" customWidth="1"/>
+    <col min="15102" max="15102" width="4.08203125" style="38" customWidth="1"/>
     <col min="15103" max="15103" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="15104" max="15104" width="42.625" style="38" customWidth="1"/>
-    <col min="15105" max="15105" width="13.375" style="38"/>
+    <col min="15104" max="15104" width="42.58203125" style="38" customWidth="1"/>
+    <col min="15105" max="15105" width="13.33203125" style="38"/>
     <col min="15106" max="15106" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="15107" max="15107" width="60.375" style="38" customWidth="1"/>
+    <col min="15107" max="15107" width="60.33203125" style="38" customWidth="1"/>
     <col min="15108" max="15108" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="15109" max="15109" width="12.75" style="38" customWidth="1"/>
-    <col min="15110" max="15110" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="15110" max="15110" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="15111" max="15356" width="8" style="38" customWidth="1"/>
     <col min="15357" max="15357" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="15358" max="15358" width="4.125" style="38" customWidth="1"/>
+    <col min="15358" max="15358" width="4.08203125" style="38" customWidth="1"/>
     <col min="15359" max="15359" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="15360" max="15360" width="42.625" style="38" customWidth="1"/>
-    <col min="15361" max="15361" width="13.375" style="38"/>
+    <col min="15360" max="15360" width="42.58203125" style="38" customWidth="1"/>
+    <col min="15361" max="15361" width="13.33203125" style="38"/>
     <col min="15362" max="15362" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="15363" max="15363" width="60.375" style="38" customWidth="1"/>
+    <col min="15363" max="15363" width="60.33203125" style="38" customWidth="1"/>
     <col min="15364" max="15364" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="15365" max="15365" width="12.75" style="38" customWidth="1"/>
-    <col min="15366" max="15366" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="15366" max="15366" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="15367" max="15612" width="8" style="38" customWidth="1"/>
     <col min="15613" max="15613" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="15614" max="15614" width="4.125" style="38" customWidth="1"/>
+    <col min="15614" max="15614" width="4.08203125" style="38" customWidth="1"/>
     <col min="15615" max="15615" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="15616" max="15616" width="42.625" style="38" customWidth="1"/>
-    <col min="15617" max="15617" width="13.375" style="38"/>
+    <col min="15616" max="15616" width="42.58203125" style="38" customWidth="1"/>
+    <col min="15617" max="15617" width="13.33203125" style="38"/>
     <col min="15618" max="15618" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="15619" max="15619" width="60.375" style="38" customWidth="1"/>
+    <col min="15619" max="15619" width="60.33203125" style="38" customWidth="1"/>
     <col min="15620" max="15620" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="15621" max="15621" width="12.75" style="38" customWidth="1"/>
-    <col min="15622" max="15622" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="15622" max="15622" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="15623" max="15868" width="8" style="38" customWidth="1"/>
     <col min="15869" max="15869" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="15870" max="15870" width="4.125" style="38" customWidth="1"/>
+    <col min="15870" max="15870" width="4.08203125" style="38" customWidth="1"/>
     <col min="15871" max="15871" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="15872" max="15872" width="42.625" style="38" customWidth="1"/>
-    <col min="15873" max="15873" width="13.375" style="38"/>
+    <col min="15872" max="15872" width="42.58203125" style="38" customWidth="1"/>
+    <col min="15873" max="15873" width="13.33203125" style="38"/>
     <col min="15874" max="15874" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="15875" max="15875" width="60.375" style="38" customWidth="1"/>
+    <col min="15875" max="15875" width="60.33203125" style="38" customWidth="1"/>
     <col min="15876" max="15876" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="15877" max="15877" width="12.75" style="38" customWidth="1"/>
-    <col min="15878" max="15878" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="15878" max="15878" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="15879" max="16124" width="8" style="38" customWidth="1"/>
     <col min="16125" max="16125" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="16126" max="16126" width="4.125" style="38" customWidth="1"/>
+    <col min="16126" max="16126" width="4.08203125" style="38" customWidth="1"/>
     <col min="16127" max="16127" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="16128" max="16128" width="42.625" style="38" customWidth="1"/>
-    <col min="16129" max="16129" width="13.375" style="38"/>
+    <col min="16128" max="16128" width="42.58203125" style="38" customWidth="1"/>
+    <col min="16129" max="16129" width="13.33203125" style="38"/>
     <col min="16130" max="16130" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="16131" max="16131" width="60.375" style="38" customWidth="1"/>
+    <col min="16131" max="16131" width="60.33203125" style="38" customWidth="1"/>
     <col min="16132" max="16132" width="10" style="38" bestFit="1" customWidth="1"/>
     <col min="16133" max="16133" width="12.75" style="38" customWidth="1"/>
-    <col min="16134" max="16134" width="8.875" style="38" bestFit="1" customWidth="1"/>
+    <col min="16134" max="16134" width="8.83203125" style="38" bestFit="1" customWidth="1"/>
     <col min="16135" max="16380" width="8" style="38" customWidth="1"/>
     <col min="16381" max="16381" width="5.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="16382" max="16382" width="4.125" style="38" customWidth="1"/>
+    <col min="16382" max="16382" width="4.08203125" style="38" customWidth="1"/>
     <col min="16383" max="16383" width="21.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="16384" max="16384" width="42.625" style="38" customWidth="1"/>
+    <col min="16384" max="16384" width="42.58203125" style="38" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="39" customFormat="1" ht="60" customHeight="1">
@@ -8719,31 +8719,31 @@
       <c r="E1" s="123"/>
     </row>
     <row r="2" spans="1:8" s="116" customFormat="1" ht="42.75" customHeight="1">
-      <c r="A2" s="358" t="s">
+      <c r="A2" s="386" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="358"/>
-      <c r="C2" s="358"/>
+      <c r="B2" s="386"/>
+      <c r="C2" s="386"/>
       <c r="D2" s="117"/>
       <c r="E2" s="117"/>
     </row>
     <row r="3" spans="1:8" s="118" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A3" s="359" t="s">
+      <c r="A3" s="387" t="s">
         <v>144</v>
       </c>
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-    </row>
-    <row r="4" spans="1:8" s="118" customFormat="1" ht="19.5">
-      <c r="A4" s="360" t="s">
+      <c r="B3" s="387"/>
+      <c r="C3" s="387"/>
+      <c r="D3" s="387"/>
+      <c r="E3" s="387"/>
+    </row>
+    <row r="4" spans="1:8" s="118" customFormat="1" ht="19">
+      <c r="A4" s="388" t="s">
         <v>151</v>
       </c>
-      <c r="B4" s="360"/>
-      <c r="C4" s="360"/>
-      <c r="D4" s="360"/>
-      <c r="E4" s="360"/>
+      <c r="B4" s="388"/>
+      <c r="C4" s="388"/>
+      <c r="D4" s="388"/>
+      <c r="E4" s="388"/>
     </row>
     <row r="5" spans="1:8" s="119" customFormat="1" ht="15.75" customHeight="1">
       <c r="B5" s="120"/>
@@ -8770,28 +8770,28 @@
       <c r="E7" s="126"/>
     </row>
     <row r="8" spans="1:8" s="122" customFormat="1" ht="77.25" customHeight="1">
-      <c r="A8" s="361" t="s">
+      <c r="A8" s="389" t="s">
         <v>147</v>
       </c>
-      <c r="B8" s="361"/>
-      <c r="C8" s="361"/>
-      <c r="D8" s="361"/>
-      <c r="E8" s="361"/>
-      <c r="F8" s="361"/>
+      <c r="B8" s="389"/>
+      <c r="C8" s="389"/>
+      <c r="D8" s="389"/>
+      <c r="E8" s="389"/>
+      <c r="F8" s="389"/>
     </row>
     <row r="9" spans="1:8" s="39" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A9" s="329" t="s">
+      <c r="A9" s="393" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="330"/>
-      <c r="C9" s="330"/>
-      <c r="D9" s="330"/>
-      <c r="E9" s="330"/>
-      <c r="F9" s="331"/>
+      <c r="B9" s="394"/>
+      <c r="C9" s="394"/>
+      <c r="D9" s="394"/>
+      <c r="E9" s="394"/>
+      <c r="F9" s="395"/>
       <c r="G9" s="48"/>
       <c r="H9" s="48"/>
     </row>
-    <row r="10" spans="1:8" s="41" customFormat="1" ht="31.5">
+    <row r="10" spans="1:8" s="41" customFormat="1" ht="31">
       <c r="A10" s="40" t="s">
         <v>3</v>
       </c>
@@ -8812,85 +8812,85 @@
       </c>
     </row>
     <row r="11" spans="1:8" s="41" customFormat="1" ht="51" customHeight="1">
-      <c r="A11" s="340">
+      <c r="A11" s="410">
         <v>1</v>
       </c>
-      <c r="B11" s="343" t="s">
+      <c r="B11" s="413" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="346">
+      <c r="D11" s="416">
         <v>214</v>
       </c>
-      <c r="E11" s="349">
+      <c r="E11" s="419">
         <v>238000</v>
       </c>
-      <c r="F11" s="352">
+      <c r="F11" s="422">
         <f>E11*D11</f>
         <v>50932000</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="41" customFormat="1" ht="24" customHeight="1">
-      <c r="A12" s="341"/>
-      <c r="B12" s="344"/>
+      <c r="A12" s="411"/>
+      <c r="B12" s="414"/>
       <c r="C12" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="347"/>
-      <c r="E12" s="350"/>
-      <c r="F12" s="353"/>
+      <c r="D12" s="417"/>
+      <c r="E12" s="420"/>
+      <c r="F12" s="423"/>
     </row>
     <row r="13" spans="1:8" s="41" customFormat="1" ht="37.5" customHeight="1">
-      <c r="A13" s="341"/>
-      <c r="B13" s="344"/>
+      <c r="A13" s="411"/>
+      <c r="B13" s="414"/>
       <c r="C13" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="347"/>
-      <c r="E13" s="350"/>
-      <c r="F13" s="353"/>
+      <c r="D13" s="417"/>
+      <c r="E13" s="420"/>
+      <c r="F13" s="423"/>
     </row>
     <row r="14" spans="1:8" s="41" customFormat="1" ht="33.75" customHeight="1">
-      <c r="A14" s="341"/>
-      <c r="B14" s="344"/>
+      <c r="A14" s="411"/>
+      <c r="B14" s="414"/>
       <c r="C14" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="347"/>
-      <c r="E14" s="350"/>
-      <c r="F14" s="353"/>
+      <c r="D14" s="417"/>
+      <c r="E14" s="420"/>
+      <c r="F14" s="423"/>
     </row>
     <row r="15" spans="1:8" s="41" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A15" s="341"/>
-      <c r="B15" s="344"/>
+      <c r="A15" s="411"/>
+      <c r="B15" s="414"/>
       <c r="C15" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="347"/>
-      <c r="E15" s="350"/>
-      <c r="F15" s="353"/>
+      <c r="D15" s="417"/>
+      <c r="E15" s="420"/>
+      <c r="F15" s="423"/>
     </row>
     <row r="16" spans="1:8" s="41" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A16" s="341"/>
-      <c r="B16" s="344"/>
+      <c r="A16" s="411"/>
+      <c r="B16" s="414"/>
       <c r="C16" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="347"/>
-      <c r="E16" s="350"/>
-      <c r="F16" s="353"/>
+      <c r="D16" s="417"/>
+      <c r="E16" s="420"/>
+      <c r="F16" s="423"/>
     </row>
     <row r="17" spans="1:8" s="41" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A17" s="342"/>
-      <c r="B17" s="345"/>
+      <c r="A17" s="412"/>
+      <c r="B17" s="415"/>
       <c r="C17" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="348"/>
-      <c r="E17" s="351"/>
-      <c r="F17" s="354"/>
+      <c r="D17" s="418"/>
+      <c r="E17" s="421"/>
+      <c r="F17" s="424"/>
       <c r="G17" s="45"/>
     </row>
     <row r="18" spans="1:8" s="41" customFormat="1" ht="16.5">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="G18" s="45"/>
     </row>
-    <row r="19" spans="1:8" s="41" customFormat="1" ht="45">
+    <row r="19" spans="1:8" s="41" customFormat="1" ht="46.5">
       <c r="A19" s="43">
         <v>3</v>
       </c>
@@ -8937,7 +8937,7 @@
       </c>
       <c r="G19" s="45"/>
     </row>
-    <row r="20" spans="1:8" s="41" customFormat="1" ht="30">
+    <row r="20" spans="1:8" s="41" customFormat="1" ht="31">
       <c r="A20" s="43">
         <v>4</v>
       </c>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="G20" s="45"/>
     </row>
-    <row r="21" spans="1:8" s="41" customFormat="1" ht="45">
+    <row r="21" spans="1:8" s="41" customFormat="1" ht="46.5">
       <c r="A21" s="43">
         <v>5</v>
       </c>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="G21" s="45"/>
     </row>
-    <row r="22" spans="1:8" s="41" customFormat="1" ht="30">
+    <row r="22" spans="1:8" s="41" customFormat="1" ht="31">
       <c r="A22" s="43">
         <v>6</v>
       </c>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="G28" s="45"/>
     </row>
-    <row r="29" spans="1:8" s="41" customFormat="1" ht="45">
+    <row r="29" spans="1:8" s="41" customFormat="1" ht="46.5">
       <c r="A29" s="43">
         <v>13</v>
       </c>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="G30" s="45"/>
     </row>
-    <row r="31" spans="1:8" s="47" customFormat="1" ht="15.75">
-      <c r="A31" s="355" t="s">
+    <row r="31" spans="1:8" s="47" customFormat="1">
+      <c r="A31" s="425" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="356"/>
-      <c r="C31" s="356"/>
+      <c r="B31" s="426"/>
+      <c r="C31" s="426"/>
       <c r="D31" s="75"/>
       <c r="E31" s="76">
         <f>SUM(E11:E30)</f>
@@ -9196,14 +9196,14 @@
       <c r="G31" s="78"/>
     </row>
     <row r="32" spans="1:8" s="39" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A32" s="329" t="s">
+      <c r="A32" s="393" t="s">
         <v>90</v>
       </c>
-      <c r="B32" s="330"/>
-      <c r="C32" s="330"/>
-      <c r="D32" s="330"/>
-      <c r="E32" s="330"/>
-      <c r="F32" s="331"/>
+      <c r="B32" s="394"/>
+      <c r="C32" s="394"/>
+      <c r="D32" s="394"/>
+      <c r="E32" s="394"/>
+      <c r="F32" s="395"/>
       <c r="G32" s="45"/>
       <c r="H32" s="48"/>
     </row>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="G33" s="45"/>
     </row>
-    <row r="34" spans="1:8" s="41" customFormat="1" ht="30">
+    <row r="34" spans="1:8" s="41" customFormat="1" ht="31">
       <c r="A34" s="43">
         <v>16</v>
       </c>
@@ -9295,12 +9295,12 @@
       </c>
       <c r="G36" s="45"/>
     </row>
-    <row r="37" spans="1:8" s="47" customFormat="1" ht="15.75">
-      <c r="A37" s="355" t="s">
+    <row r="37" spans="1:8" s="47" customFormat="1">
+      <c r="A37" s="425" t="s">
         <v>127</v>
       </c>
-      <c r="B37" s="356"/>
-      <c r="C37" s="356"/>
+      <c r="B37" s="426"/>
+      <c r="C37" s="426"/>
       <c r="D37" s="75"/>
       <c r="E37" s="76">
         <f>SUM(E33:E36)</f>
@@ -9313,14 +9313,14 @@
       <c r="G37" s="78"/>
     </row>
     <row r="38" spans="1:8" s="39" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A38" s="329" t="s">
+      <c r="A38" s="393" t="s">
         <v>134</v>
       </c>
-      <c r="B38" s="330"/>
-      <c r="C38" s="330"/>
-      <c r="D38" s="330"/>
-      <c r="E38" s="330"/>
-      <c r="F38" s="331"/>
+      <c r="B38" s="394"/>
+      <c r="C38" s="394"/>
+      <c r="D38" s="394"/>
+      <c r="E38" s="394"/>
+      <c r="F38" s="395"/>
       <c r="G38" s="45"/>
       <c r="H38" s="48"/>
     </row>
@@ -9434,7 +9434,7 @@
       </c>
       <c r="G43" s="45"/>
     </row>
-    <row r="44" spans="1:8" s="47" customFormat="1" ht="30">
+    <row r="44" spans="1:8" s="47" customFormat="1" ht="31">
       <c r="A44" s="43">
         <v>24</v>
       </c>
@@ -9478,12 +9478,12 @@
       </c>
       <c r="G45" s="45"/>
     </row>
-    <row r="46" spans="1:8" s="47" customFormat="1" ht="15.75">
-      <c r="A46" s="355" t="s">
+    <row r="46" spans="1:8" s="47" customFormat="1">
+      <c r="A46" s="425" t="s">
         <v>127</v>
       </c>
-      <c r="B46" s="356"/>
-      <c r="C46" s="356"/>
+      <c r="B46" s="426"/>
+      <c r="C46" s="426"/>
       <c r="D46" s="75"/>
       <c r="E46" s="76">
         <f>SUM(E39:E45)</f>
@@ -9496,18 +9496,18 @@
       <c r="G46" s="78"/>
     </row>
     <row r="47" spans="1:8" s="39" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A47" s="329" t="s">
+      <c r="A47" s="393" t="s">
         <v>110</v>
       </c>
-      <c r="B47" s="330"/>
-      <c r="C47" s="330"/>
-      <c r="D47" s="330"/>
-      <c r="E47" s="330"/>
-      <c r="F47" s="331"/>
+      <c r="B47" s="394"/>
+      <c r="C47" s="394"/>
+      <c r="D47" s="394"/>
+      <c r="E47" s="394"/>
+      <c r="F47" s="395"/>
       <c r="G47" s="45"/>
       <c r="H47" s="48"/>
     </row>
-    <row r="48" spans="1:8" s="47" customFormat="1" ht="45">
+    <row r="48" spans="1:8" s="47" customFormat="1" ht="46.5">
       <c r="A48" s="73">
         <v>26</v>
       </c>
@@ -9589,12 +9589,12 @@
       </c>
       <c r="G51" s="45"/>
     </row>
-    <row r="52" spans="1:7" s="47" customFormat="1" ht="15.75">
-      <c r="A52" s="362" t="s">
+    <row r="52" spans="1:7" s="47" customFormat="1">
+      <c r="A52" s="390" t="s">
         <v>127</v>
       </c>
-      <c r="B52" s="363"/>
-      <c r="C52" s="363"/>
+      <c r="B52" s="391"/>
+      <c r="C52" s="391"/>
       <c r="D52" s="83"/>
       <c r="E52" s="84">
         <f>SUM(E48:E51)</f>
@@ -9607,13 +9607,13 @@
       <c r="G52" s="78"/>
     </row>
     <row r="53" spans="1:7" s="69" customFormat="1" ht="16.5">
-      <c r="A53" s="365" t="s">
+      <c r="A53" s="396" t="s">
         <v>32</v>
       </c>
-      <c r="B53" s="366"/>
-      <c r="C53" s="366"/>
-      <c r="D53" s="366"/>
-      <c r="E53" s="367"/>
+      <c r="B53" s="397"/>
+      <c r="C53" s="397"/>
+      <c r="D53" s="397"/>
+      <c r="E53" s="398"/>
       <c r="F53" s="77">
         <f>SUM(F52,F46,F37,F31)</f>
         <v>669782000</v>
@@ -9625,20 +9625,20 @@
     <row r="55" spans="1:7" s="41" customFormat="1" ht="16.5">
       <c r="A55" s="85"/>
       <c r="B55" s="85"/>
-      <c r="D55" s="364" t="s">
+      <c r="D55" s="392" t="s">
         <v>140</v>
       </c>
-      <c r="E55" s="364"/>
-      <c r="F55" s="364"/>
+      <c r="E55" s="392"/>
+      <c r="F55" s="392"/>
     </row>
     <row r="56" spans="1:7" s="41" customFormat="1" ht="16.5">
       <c r="A56" s="85"/>
       <c r="B56" s="85"/>
-      <c r="D56" s="357" t="s">
+      <c r="D56" s="385" t="s">
         <v>150</v>
       </c>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="385"/>
+      <c r="F56" s="385"/>
     </row>
     <row r="57" spans="1:7" s="41" customFormat="1" ht="16.5">
       <c r="A57" s="85"/>
@@ -9682,82 +9682,71 @@
       <c r="E62" s="128"/>
       <c r="F62" s="128"/>
     </row>
-    <row r="63" spans="1:7" s="71" customFormat="1" ht="15.75">
-      <c r="A63" s="332" t="s">
+    <row r="63" spans="1:7" s="71" customFormat="1">
+      <c r="A63" s="402" t="s">
         <v>35</v>
       </c>
-      <c r="B63" s="333"/>
+      <c r="B63" s="403"/>
       <c r="C63" s="70"/>
       <c r="D63" s="70"/>
       <c r="E63" s="70"/>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="334" t="s">
+      <c r="A64" s="404" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="335"/>
-      <c r="C64" s="335"/>
-      <c r="D64" s="335"/>
-      <c r="E64" s="335"/>
-      <c r="F64" s="336"/>
+      <c r="B64" s="405"/>
+      <c r="C64" s="405"/>
+      <c r="D64" s="405"/>
+      <c r="E64" s="405"/>
+      <c r="F64" s="406"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="334" t="s">
+      <c r="A65" s="404" t="s">
         <v>149</v>
       </c>
-      <c r="B65" s="335"/>
-      <c r="C65" s="335"/>
-      <c r="D65" s="335"/>
-      <c r="E65" s="335"/>
-      <c r="F65" s="336"/>
+      <c r="B65" s="405"/>
+      <c r="C65" s="405"/>
+      <c r="D65" s="405"/>
+      <c r="E65" s="405"/>
+      <c r="F65" s="406"/>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="337" t="s">
+      <c r="A66" s="407" t="s">
         <v>67</v>
       </c>
-      <c r="B66" s="338"/>
-      <c r="C66" s="338"/>
-      <c r="D66" s="338"/>
-      <c r="E66" s="338"/>
-      <c r="F66" s="339"/>
+      <c r="B66" s="408"/>
+      <c r="C66" s="408"/>
+      <c r="D66" s="408"/>
+      <c r="E66" s="408"/>
+      <c r="F66" s="409"/>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="334"/>
-      <c r="B67" s="335"/>
-      <c r="C67" s="335"/>
-      <c r="D67" s="335"/>
-      <c r="E67" s="335"/>
-      <c r="F67" s="336"/>
+      <c r="A67" s="404"/>
+      <c r="B67" s="405"/>
+      <c r="C67" s="405"/>
+      <c r="D67" s="405"/>
+      <c r="E67" s="405"/>
+      <c r="F67" s="406"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="326"/>
-      <c r="B68" s="327"/>
-      <c r="C68" s="327"/>
-      <c r="D68" s="327"/>
-      <c r="E68" s="327"/>
-      <c r="F68" s="328"/>
+      <c r="A68" s="399"/>
+      <c r="B68" s="400"/>
+      <c r="C68" s="400"/>
+      <c r="D68" s="400"/>
+      <c r="E68" s="400"/>
+      <c r="F68" s="401"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="326"/>
-      <c r="B69" s="327"/>
-      <c r="C69" s="327"/>
-      <c r="D69" s="327"/>
-      <c r="E69" s="327"/>
-      <c r="F69" s="328"/>
+      <c r="A69" s="399"/>
+      <c r="B69" s="400"/>
+      <c r="C69" s="400"/>
+      <c r="D69" s="400"/>
+      <c r="E69" s="400"/>
+      <c r="F69" s="401"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A69:F69"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A63:B63"/>
@@ -9774,12 +9763,23 @@
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A46:C46"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A53:E53"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:B7">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.3" top="0.5" bottom="0.3" header="0.3" footer="0.3"/>
-  <pageSetup scale="74" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="75" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>